--- a/data/Bao_Cao_Tham_Dinh_Trinh_Lanh_Dao.xlsx
+++ b/data/Bao_Cao_Tham_Dinh_Trinh_Lanh_Dao.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -779,7 +779,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Lâm Đồng, ngày 08 tháng 09 năm 2026</t>
+          <t>Lâm Đồng, ngày 09 tháng 09 năm 2026</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Hồ sơ: Bang_Tham_Dinh_Du_Toan (3) - Bản Mới | Người thực hiện: Nguyễn Anh Hiếu</t>
+          <t>Hồ sơ: Bang_Tham_Dinh_Du_Toan (3) - Bản Mới - Bản Mới | Người thực hiện: Nguyễn Anh Hiếu</t>
         </is>
       </c>
     </row>
@@ -826,14 +826,14 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Tổng số: 112 mục (Đã chốt: 13 mục)</t>
+          <t>Tổng số: 112 mục (Đã chốt: 15 mục)</t>
         </is>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Trình: 38.145.576.000 đ  --&gt;  Thẩm định: 38.283.656.500 đ</t>
+          <t>Trình: 38.145.576.000 đ  --&gt;  Thẩm định: 32.385.281.416 đ</t>
         </is>
       </c>
       <c r="E9" s="9" t="n"/>
@@ -841,7 +841,7 @@
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>TIẾT KIỆM CHO NHÀ MÁY: -699.499.500 đ  (1.83%)</t>
+          <t>TIẾT KIỆM CHO NHÀ MÁY: -5.937.874.584 đ  (15.57%)</t>
         </is>
       </c>
       <c r="I9" s="9" t="n"/>
@@ -1470,22 +1470,38 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>2.46.35.037.CHN.00.000</t>
+          <t>3.96.13.021.GER.00.000</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
+          <t>Cảm biến đo khối lượng (Loadcell), model: RTNC3/10T</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
+          <t>Cảm biến đo khối lượng (Loadcell):
+- Model: RTNC3/10T
+- Odering number: K-RTN-8-C3-10-N-12-N-N-8
+- Maximum capacity (Emax): 10000kg
+- Minimum capacity (Emin): 0kg
+- Minimum interval (Vmin): 500g
+- Rated output (Cn): 2.85mV/V ± 0.00285
+- Input resistance: 4450 ± 100Ω
+- Output resistance: 4010 ± 2Ω
+- Rated range of the excitation voltage: 5 ~ 30V
+- Insulation resistance: &gt;20GΩ
+- Operating temperature: -10 ~ 40oC
+- Breaking load: 40000kg
+- Number of wires: 5 (included Shield wire)
+- Cable length: 5m
+- Protection class: IP68
+- Manufacturer: Hottinger Baldwin Messtechnik GmbH (HBM), Germany</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>Swagelok/ Đức</t>
+          <t>HBK/ Đức</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
@@ -1494,19 +1510,19 @@
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H23" s="17" t="n">
-        <v>19300000</v>
+        <v>117600000</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>18522000</v>
+        <v>113232916.5</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>648270000</v>
+        <v>113232916.5</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>27230000</v>
+        <v>4367083.5</v>
       </c>
       <c r="L23" s="19" t="inlineStr">
         <is>
@@ -1520,23 +1536,22 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>3.96.13.320.USA.00.000</t>
+          <t>2.46.35.037.CHN.00.000</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.</t>
+          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
-NSX: MERRICK</t>
+          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Merrick/ Mỹ</t>
+          <t>Swagelok/ Đức</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -1545,19 +1560,19 @@
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>56105000</v>
+        <v>19300000</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>23000000</v>
+        <v>18522000</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>46000000</v>
+        <v>648270000</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>66210000</v>
+        <v>27230000</v>
       </c>
       <c r="L24" s="19" t="inlineStr">
         <is>
@@ -1571,15 +1586,126 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
+          <t>3.96.13.320.USA.00.000</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
+NSX: MERRICK</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>Merrick/ Mỹ</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>56105000</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="J25" s="17" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="K25" s="18" t="n">
+        <v>66210000</v>
+      </c>
+      <c r="L25" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Lining Plate (Compound Armour Plate)
+Tấm lót thân máy nghiền
+Bao gồm 106 chi tiết (tấm)
+Chế tạo bằng thép Kalmetall W100/Kalenborn
+- Vật liệu: Thép 2 thành phần Kalmetall W100 - Kalenborn
+- Độ dày: 16mm ( 8+8 )
+- Độ dày: 10mm ( 6+4 )
+- Thép nền S235JRG2
+- Lớp phủ hợp kim Chromium Carbides: %C~5; %Cr~30; %Fe + others Balance 
+- Độ cứng ~ 700HV trên toàn bộ lớp phủ
+- Chống mài mòn theo ASTM G65: 0,0060 mm3/m</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>ML/ Ba Lan</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>2618304000</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="J26" s="17" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>5234008000</v>
+      </c>
+      <c r="L26" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Bơm (SP-Circulation pump):
 TP400 PP, P4-400V/50
@@ -1596,90 +1722,90 @@
 IEC60034-1</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>Grundfos/ Eu</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G25" s="17" t="n">
+      <c r="G27" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="17" t="n">
+      <c r="H27" s="17" t="n">
         <v>770000000</v>
       </c>
-      <c r="I25" s="17" t="n">
+      <c r="I27" s="17" t="n">
         <v>750000000</v>
       </c>
-      <c r="J25" s="17" t="n">
+      <c r="J27" s="17" t="n">
         <v>1500000000</v>
       </c>
-      <c r="K25" s="18" t="n">
+      <c r="K27" s="18" t="n">
         <v>40000000</v>
       </c>
-      <c r="L25" s="19" t="inlineStr">
+      <c r="L27" s="19" t="inlineStr">
         <is>
           <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>TỔNG CỘNG CÁC MỤC ĐÃ CHỐT THẨM ĐỊNH:</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n"/>
-      <c r="C26" s="21" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="21" t="n"/>
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="21" t="n"/>
-      <c r="I26" s="21" t="n"/>
-      <c r="J26" s="22" t="n">
-        <v>2837206500</v>
-      </c>
-      <c r="K26" s="23" t="n">
-        <v>699499500</v>
-      </c>
-      <c r="L26" s="21" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B28" s="21" t="n"/>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="21" t="n"/>
+      <c r="G28" s="21" t="n"/>
+      <c r="H28" s="21" t="n"/>
+      <c r="I28" s="21" t="n"/>
+      <c r="J28" s="22" t="n">
+        <v>2953039416.5</v>
+      </c>
+      <c r="K28" s="23" t="n">
+        <v>5937874583.5</v>
+      </c>
+      <c r="L28" s="21" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>NGƯỜI LẬP BÁO CÁO / THƯ KÝ TỔ TTĐ</t>
         </is>
       </c>
-      <c r="J29" s="24" t="inlineStr">
+      <c r="J31" s="24" t="inlineStr">
         <is>
           <t>TỔ TRƯỞNG TỔ THẨM ĐỊNH DỰ TOÁN</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="25" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>(Ký và ghi rõ họ tên)</t>
         </is>
       </c>
-      <c r="J30" s="25" t="inlineStr">
+      <c r="J32" s="25" t="inlineStr">
         <is>
           <t>(Ký và ghi rõ họ tên)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="26" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>Nguyễn Anh Hiếu</t>
         </is>
       </c>
-      <c r="J35" s="26" t="inlineStr">
+      <c r="J37" s="26" t="inlineStr">
         <is>
           <t>...................................................</t>
         </is>
@@ -1689,6 +1815,7 @@
   <mergeCells count="13">
     <mergeCell ref="H9:L9"/>
     <mergeCell ref="D9:G9"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="D8:G8"/>
     <mergeCell ref="A8:C8"/>
@@ -1699,7 +1826,6 @@
     <mergeCell ref="A6:L6"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="H8:L8"/>
-    <mergeCell ref="A26:I26"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId1"/>
@@ -1715,6 +1841,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1755,7 +1883,7 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Hồ sơ: Bang_Tham_Dinh_Du_Toan (3) - Bản Mới | Cập nhật: 08/09/2026 13:27</t>
+          <t>Hồ sơ: Bang_Tham_Dinh_Du_Toan (3) - Bản Mới - Bản Mới | Cập nhật: 09/09/2026 09:12</t>
         </is>
       </c>
     </row>
@@ -2520,20 +2648,20 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>3.96.13.021.GER.00.000</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>Cảm biến đo khối lượng (Loadcell), model: RTNC3/10T</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>Cảm biến đo khối lượng (Loadcell):
 - Model: RTNC3/10T
@@ -2554,42 +2682,42 @@
 - Manufacturer: Hottinger Baldwin Messtechnik GmbH (HBM), Germany</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>HBK/ Đức</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="H16" s="31" t="n">
         <v>117600000</v>
       </c>
-      <c r="I16" s="17" t="n">
+      <c r="I16" s="31" t="n">
         <v>117600000</v>
       </c>
-      <c r="J16" s="17" t="n">
-        <v>117600000</v>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v>117600000</v>
-      </c>
-      <c r="L16" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N16" s="16" t="inlineStr">
-        <is>
-          <t>3.96.13.021.GER.00.000 | Thay thế 01 cảm biến đo khối lượng (Loadcell) bồn chứa khí CO2 – Tổ máy S3 bị hư hỏng | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+      <c r="J16" s="31" t="n">
+        <v>113232916.5</v>
+      </c>
+      <c r="K16" s="31" t="n">
+        <v>113232916.5</v>
+      </c>
+      <c r="L16" s="23" t="n">
+        <v>4367083.5</v>
+      </c>
+      <c r="M16" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N16" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -6829,20 +6957,20 @@
       </c>
     </row>
     <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="14" t="n">
+      <c r="A86" s="28" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="15" t="inlineStr">
+      <c r="B86" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C86" s="16" t="inlineStr">
+      <c r="C86" s="30" t="inlineStr">
         <is>
           <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than</t>
         </is>
       </c>
-      <c r="D86" s="16" t="inlineStr">
+      <c r="D86" s="30" t="inlineStr">
         <is>
           <t>Lining Plate (Compound Armour Plate)
 Tấm lót thân máy nghiền
@@ -6857,42 +6985,42 @@
 - Chống mài mòn theo ASTM G65: 0,0060 mm3/m</t>
         </is>
       </c>
-      <c r="E86" s="15" t="inlineStr">
+      <c r="E86" s="29" t="inlineStr">
         <is>
           <t>ML/ Ba Lan</t>
         </is>
       </c>
-      <c r="F86" s="14" t="inlineStr">
+      <c r="F86" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G86" s="17" t="n">
+      <c r="G86" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H86" s="17" t="n">
+      <c r="H86" s="31" t="n">
         <v>2618304000</v>
       </c>
-      <c r="I86" s="17" t="n">
+      <c r="I86" s="31" t="n">
         <v>5236608000</v>
       </c>
-      <c r="J86" s="17" t="n">
-        <v>2618304000</v>
-      </c>
-      <c r="K86" s="17" t="n">
-        <v>5236608000</v>
-      </c>
-      <c r="L86" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N86" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay thế mới tấm lining ở vách thùng nghiền, phía sau con lăn, cửa manhole các máy nghiền bị mài mòn nặng | Vật tư đã chuẩn hóa ERP, không tồn kho. Vật tư chưa đề xuất mua sắm trong KHSXKD 2026.</t>
+      <c r="J86" s="31" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="K86" s="31" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="L86" s="23" t="n">
+        <v>5234008000</v>
+      </c>
+      <c r="M86" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N86" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -8066,10 +8194,10 @@
         <v>90000000</v>
       </c>
       <c r="J106" s="17" t="n">
-        <v>750000000</v>
+        <v>90000000</v>
       </c>
       <c r="K106" s="17" t="n">
-        <v>750000000</v>
+        <v>90000000</v>
       </c>
       <c r="L106" s="17" t="n">
         <v>0</v>
@@ -8693,10 +8821,10 @@
       </c>
       <c r="J117" s="35" t="n"/>
       <c r="K117" s="36" t="n">
-        <v>38283656500</v>
+        <v>32385281416.5</v>
       </c>
       <c r="L117" s="37" t="n">
-        <v>699499500</v>
+        <v>5937874583.5</v>
       </c>
       <c r="M117" s="35" t="n"/>
       <c r="N117" s="35" t="n"/>
@@ -8716,9 +8844,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N102" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N102" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8730,7 +8860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8846,29 +8976,25 @@
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (13,559,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx fn (file Báo giá DTL 19.8.2026. xlsx fn.pdf, Trang 1). Ngoài ra còn có: CÔNG TY CỔ PHẦN CÔNG NGHỆ CƠ ĐIỆN EME báo giá 15,592,850 đ (+</t>
+          <t>Đơn giá trình (13,559,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 1). Ngoài ra còn có: CÔNG TY CỔ PHẦN CÔNG NGHỆ CƠ ĐIỆN EME báo giá 15,592,850 đ (+15.0%)</t>
         </is>
       </c>
       <c r="G5" s="40" t="inlineStr">
         <is>
-          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ: 115/2023, Ttr 2562/KHVT) theo hóa đơn số 00000041, 42, 43, 44, 45, 46 ngày 30.08.2024 (ngày ký 2024-10-31 00:00:00, do Nhập kho vật tư (HĐ: 115/</t>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 6.015.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 115/2023. Ttr 2562/KHVT) theo hóa đơn số 00000041. 42. 43. 44. 45. 46 ngày 30.08.2024 ngày 2024-10-31. SL: 117 Cái); Các đợt nhập khác: 17.670.00</t>
         </is>
       </c>
       <c r="H5" s="40" t="inlineStr">
         <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 07/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [908531], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong</t>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [908531], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
         </is>
       </c>
       <c r="I5" s="40" t="inlineStr">
         <is>
-          <t>Đã tra cứu từ khóa [IUX 760 MI] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 14:29 ngày 07/09/2026 nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
-        </is>
-      </c>
-      <c r="J5" s="40" t="inlineStr">
-        <is>
-          <t>Hiện tại không có giá bán cố định công khai cho thiết bị Module đầu vào Input IUX 760 M-I (Partno: 908531) của hãng Minimax trên thị trường bán lẻ. [1] (https://anhnghison.com/san-pham/heat-detector-heat-sensing-908531-m</t>
-        </is>
-      </c>
+          <t>Đã tra cứu từ khóa [Module đầu vào input IUX 760 MI] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+        </is>
+      </c>
+      <c r="J5" s="40" t="inlineStr"/>
       <c r="K5" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 6.015.000 đ
@@ -8892,36 +9018,32 @@
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr"/>
-      <c r="E6" s="42" t="inlineStr">
-        <is>
-          <t>Mở liên kết trực tuyến ↗</t>
+      <c r="E6" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (14,208,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file BÁO GIÁ THĂNG LONG 19.8.2026 D.pdf, Trang 1). Ngoài ra còn có: DTL 19.8.2026. xlsx fn báo giá 15,10</t>
+          <t>Đơn giá trình (14,208,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 1). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 15,100,000 đ (+6.3%)</t>
         </is>
       </c>
       <c r="G6" s="40" t="inlineStr">
         <is>
-          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (QĐ:161) theo hóa đơn số 0000221 ngày 26.03.2021 (ngày ký 2021-04-14 00:00:00, do Nhập kho vật tư (QĐ:161) theo hóa đơn số 0000221 ngày 26.03.2021 cu</t>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 7.000.000 đ/Cái (HĐ: Nhập kho vật tư (QĐ:161) theo hóa đơn số 0000221 ngày 26.03.2021 ngày 2021-04-14. SL: 1 Cái)</t>
         </is>
       </c>
       <c r="H6" s="40" t="inlineStr">
         <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 07/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [58100-953], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện tr</t>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [58100-953], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
         </is>
       </c>
       <c r="I6" s="40" t="inlineStr">
         <is>
-          <t>Đã tra cứu từ khóa [58100-953] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 14:43 ngày 07/09/2026 nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
-        </is>
-      </c>
-      <c r="J6" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu "Nút nhấn khẩn cấp - Discovery manual call point, Part no: 58100-953 - Nút nhấn khẩn cấp, Part no: 58100-953, Nguồn cấp: 17 - 28VDC , IP67. NSX: Apollo" trên trang https://www.acornfiresecurity.com/apollo-disc</t>
-        </is>
-      </c>
+          <t>Đã tra cứu từ khóa [Nút nhấn khẩn cấp - Discovery manual call point, Part no: 58100-953] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+        </is>
+      </c>
+      <c r="J6" s="40" t="inlineStr"/>
       <c r="K6" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 7.000.000 đ
@@ -8959,7 +9081,7 @@
       </c>
       <c r="F7" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (56,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu.pdf, Trang 1). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG</t>
+          <t>Đơn giá trình (56,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 1). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
         </is>
       </c>
       <c r="G7" s="40" t="inlineStr">
@@ -9020,7 +9142,7 @@
       </c>
       <c r="F8" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (64,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu.pdf, Trang 2). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG</t>
+          <t>Đơn giá trình (64,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 2). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
         </is>
       </c>
       <c r="G8" s="40" t="inlineStr">
@@ -9077,7 +9199,7 @@
       </c>
       <c r="F9" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (1,500,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file BÁO GIÁ THĂNG LONG 19.8.2026 D.pdf, Trang 1). Ngoài ra còn có: CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG</t>
+          <t>Đơn giá trình (1,500,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 1). Ngoài ra còn có: CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HI</t>
         </is>
       </c>
       <c r="G9" s="40" t="inlineStr">
@@ -9134,7 +9256,7 @@
       </c>
       <c r="F10" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (61,250,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file BÁO GIÁ THĂNG LONG 19.8.2026 D.pdf, Trang 1). Ngoài ra còn có: DTL 19.8.2026. xlsx fn báo giá 65,00</t>
+          <t>Đơn giá trình (61,250,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 1). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 65,000,000 đ (+6.1%)</t>
         </is>
       </c>
       <c r="G10" s="40" t="inlineStr">
@@ -9196,7 +9318,7 @@
       </c>
       <c r="F11" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (452,147,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx fn (file Báo giá DTL 19.8.2026. xlsx fn.pdf, Trang 1). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 468,</t>
+          <t>Đơn giá trình (452,147,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 1). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 468,000,00</t>
         </is>
       </c>
       <c r="G11" s="40" t="inlineStr">
@@ -9261,27 +9383,27 @@
       </c>
       <c r="F12" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (1,004,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file BÁO GIÁ THĂNG LONG 19.8.2026 D.pdf, Trang 2). Ngoài ra còn có: CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG</t>
+          <t>Đơn giá trình (1,004,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 2). Ngoài ra còn có: CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HI</t>
         </is>
       </c>
       <c r="G12" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Vật tư có 10 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 4.353.280 đ/Cái (dao động từ 30.000 đ đến 18.374.000 đ). Đơn giá trình đợt này là 1.004.000 đ/Cái (-76.9% so vớ</t>
         </is>
       </c>
       <c r="H12" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 08/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [PL A3C], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong</t>
         </is>
       </c>
       <c r="I12" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Đã tra cứu từ khóa [PL A3C] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 17:34 ngày 08/09/2026 nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
         </is>
       </c>
       <c r="J12" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t xml:space="preserve">Đã tra cứu từ khóa [PL A3C] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại </t>
         </is>
       </c>
       <c r="K12" s="41" t="inlineStr">
@@ -9326,7 +9448,7 @@
       </c>
       <c r="F13" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (1,315,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file BÁO GIÁ THĂNG LONG 19.8.2026 D.pdf, Trang 2). Ngoài ra còn có: CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG</t>
+          <t>Đơn giá trình (1,315,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 2). Ngoài ra còn có: CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HI</t>
         </is>
       </c>
       <c r="G13" s="40" t="inlineStr">
@@ -9387,7 +9509,7 @@
       </c>
       <c r="F14" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (1,508,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file BÁO GIÁ THĂNG LONG 19.8.2026 D.pdf, Trang 2). Ngoài ra còn có: DTL 19.8.2026. xlsx fn báo giá 2,350,</t>
+          <t>Đơn giá trình (1,508,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 2). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 2,350,000 đ (+55.8%);</t>
         </is>
       </c>
       <c r="G14" s="40" t="inlineStr">
@@ -9419,13 +9541,29 @@
       </c>
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t>2.46.35.037.CHN.00.000</t>
+          <t>3.96.13.021.GER.00.000</t>
         </is>
       </c>
       <c r="C15" s="40" t="inlineStr">
         <is>
-          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m
-(Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m)</t>
+          <t>Cảm biến đo khối lượng (Loadcell), model: RTNC3/10T
+(Cảm biến đo khối lượng (Loadcell):
+- Model: RTNC3/10T
+- Odering number: K-RTN-8-C3-10-N-12-N-N-8
+- Maximum capacity (Emax): 10000kg
+- Minimum capacity (Emin): 0kg
+- Minimum interval (Vmin): 500g
+- Rated output (Cn): 2.85mV/V ± 0.00285
+- Input resistance: 4450 ± 100Ω
+- Output resistance: 4010 ± 2Ω
+- Rated range of the excitation voltage: 5 ~ 30V
+- Insulation resistance: &gt;20GΩ
+- Operating temperature: -10 ~ 40oC
+- Breaking load: 40000kg
+- Number of wires: 5 (included Shield wire)
+- Cable length: 5m
+- Protection class: IP68
+- Manufacturer: Hottinger Baldwin Messtechnik GmbH (HBM), Germany)</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
@@ -9440,33 +9578,29 @@
       </c>
       <c r="F15" s="40" t="inlineStr">
         <is>
-          <t>Báo giá đề nghị nộp kèm: 19.300.000 đ</t>
+          <t>Đơn giá trình (117,600,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 2). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 120,000,000 đ (+2.0</t>
         </is>
       </c>
       <c r="G15" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Vật tư có 2 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 113.232.916 đ/Cái (dao động từ 57.465.833 đ đến 169.000.000 đ). Đơn giá trình đợt này là 117.600.000 đ/Cái (+3.9</t>
         </is>
       </c>
       <c r="H15" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [RTNC3], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
         </is>
       </c>
       <c r="I15" s="40" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Đã tra cứu từ khóa [Cảm biến đo khối lượng (Loadcell), model: RTNC3/10T] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+        </is>
+      </c>
+      <c r="J15" s="40" t="inlineStr"/>
       <c r="K15" s="41" t="inlineStr">
         <is>
-          <t>Đơn giá chốt: 18.522.000 đ
-(Tiết kiệm: 27.230.000 đ)</t>
+          <t>Đơn giá chốt: 113.232.916 đ
+(Tiết kiệm: 4.367.084 đ)</t>
         </is>
       </c>
     </row>
@@ -9476,68 +9610,188 @@
       </c>
       <c r="B16" s="39" t="inlineStr">
         <is>
+          <t>2.46.35.037.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m
+(Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m)</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E16" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (19,300,000 đ) không trùng với báo giá nào. Trong đó đơn giá thấp nhất thu thập được là 18,522,000 đ của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf).</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có 2 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 21.200.000 đ/Cái (dao động từ 17.500.000 đ đến 24.900.000 đ). Đơn giá trình đợt này là 19.300.000 đ/Cái (-9.0% s</t>
+        </is>
+      </c>
+      <c r="H16" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [SS-T6-S-065-20] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 17:27 ngày 08/09/2026; ghi nhận mức giá trúng thầu tham chiếu là 27.390.000 đ (Mã TBMT: IB2400452305, Bên mời thầu: NHÀ MÁY NHIỆ</t>
+        </is>
+      </c>
+      <c r="J16" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 18.522.000 đ
+(Tiết kiệm: 27.230.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="38" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="39" t="inlineStr">
+        <is>
           <t>3.96.13.320.USA.00.000</t>
         </is>
       </c>
-      <c r="C16" s="40" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
 (Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
 NSX: MERRICK)</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>[Lưu trong hồ sơ PDF]</t>
         </is>
       </c>
-      <c r="E16" s="40" t="inlineStr">
+      <c r="E17" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="40" t="inlineStr">
-        <is>
-          <t>Báo giá đề nghị nộp kèm: 56.105.000 đ</t>
-        </is>
-      </c>
-      <c r="G16" s="40" t="inlineStr">
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (56,105,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 4). Ngoài ra còn có: CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN H</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="40" t="inlineStr">
+      <c r="H17" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="40" t="inlineStr">
+      <c r="I17" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J16" s="40" t="inlineStr">
+      <c r="J17" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K16" s="41" t="inlineStr">
+      <c r="K17" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 23.000.000 đ
 (Tiết kiệm: 66.210.000 đ)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="38" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C18" s="40" t="inlineStr">
+        <is>
+          <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than
+(Lining Plate (Compound Armour Plate)
+Tấm lót thân máy nghiền
+Bao gồm 106 chi tiết (tấm)
+Chế tạo bằng thép Kalmetall W100/Kalenborn
+- Vật liệu: Thép 2 thành phần Kalmetall W100 - Kalenborn
+- Độ dày: 16mm ( 8+8 )
+- Độ dày: 10mm ( 6+4 )
+- Thép nền S235JRG2
+- Lớp phủ hợp kim Chromium Carbides: %C~5; %Cr~30; %Fe + others Balance 
+- Độ cứng ~ 700HV trên toàn bộ lớp phủ
+- Chống mài mòn theo ASTM G65: 0,0060 mm3/m)</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>CẢNH BÁO: Đơn giá trình (2,618,304,000 đ) lấy từ Báo giá của DTL 19.8.2026. xlsx nhưng KHÔNG PHẢI là đơn giá thấp nhất! Đơn giá thấp nhất là 1,300,000 đ của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO G</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 1.845.000.000 đ/Bộ (HĐ: Nhập kho vật tư (HĐ: 32/2025) theo hóa đơn số 00000181 ngày 26.11.2025 ngày 2025-12-04. SL: 3 Bộ); Các đợt nhập khác: 1.293.213.000 đ</t>
+        </is>
+      </c>
+      <c r="H18" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Lining Plate (Compound Armour], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I18" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+        </is>
+      </c>
+      <c r="J18" s="40" t="inlineStr"/>
+      <c r="K18" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 1.300.000 đ
+(Tiết kiệm: 5.234.008.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW
 (Bơm (SP-Circulation pump):
@@ -9555,38 +9809,38 @@
 IEC60034-1)</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>[Lưu trong hồ sơ PDF]</t>
         </is>
       </c>
-      <c r="E17" s="40" t="inlineStr">
+      <c r="E19" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="40" t="inlineStr">
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">CẢNH BÁO: Đơn giá trình (770,000,000 đ) lấy từ Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG nhưng KHÔNG PHẢI là đơn giá thấp nhất! Đơn giá thấp nhất là 750,000,000 đ của 08-27-26. BV-VT 4. . 1,620,000,000 </t>
         </is>
       </c>
-      <c r="G17" s="40" t="inlineStr">
+      <c r="G19" s="40" t="inlineStr">
         <is>
           <t>Vật tư chưa có lịch sử mua sắm/nhập kho trong CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4.</t>
         </is>
       </c>
-      <c r="H17" s="40" t="inlineStr">
+      <c r="H19" s="40" t="inlineStr">
         <is>
           <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [TP400 PP], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
         </is>
       </c>
-      <c r="I17" s="40" t="inlineStr">
+      <c r="I19" s="40" t="inlineStr">
         <is>
           <t>Đã tra cứu từ khóa [Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
         </is>
       </c>
-      <c r="J17" s="40" t="inlineStr"/>
-      <c r="K17" s="41" t="inlineStr">
+      <c r="J19" s="40" t="inlineStr"/>
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 750.000.000 đ
 (Tiết kiệm: 40.000.000 đ)</t>
@@ -9595,11 +9849,10 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
 </file>
--- a/data/Bao_Cao_Tham_Dinh_Trinh_Lanh_Dao.xlsx
+++ b/data/Bao_Cao_Tham_Dinh_Trinh_Lanh_Dao.xlsx
@@ -438,6 +438,181 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2438400" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2476500" cy="1200150"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1895475" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1847850" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2247900" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1295400" cy="1285875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -730,7 +905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -779,7 +954,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Lâm Đồng, ngày 09 tháng 09 năm 2026</t>
+          <t>Lâm Đồng, ngày 10 tháng 09 năm 2026</t>
         </is>
       </c>
     </row>
@@ -826,14 +1001,14 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Tổng số: 112 mục (Đã chốt: 15 mục)</t>
+          <t>Tổng số: 112 mục (Đã chốt: 41 mục)</t>
         </is>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Trình: 38.145.576.000 đ  --&gt;  Thẩm định: 32.385.281.416 đ</t>
+          <t>Trình: 38.145.576.000 đ  --&gt;  Thẩm định: 34.779.577.092 đ</t>
         </is>
       </c>
       <c r="E9" s="9" t="n"/>
@@ -841,7 +1016,7 @@
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>TIẾT KIỆM CHO NHÀ MÁY: -5.937.874.584 đ  (15.57%)</t>
+          <t>TIẾT KIỆM CHO NHÀ MÁY: -3.425.998.908 đ  (8.98%)</t>
         </is>
       </c>
       <c r="I9" s="9" t="n"/>
@@ -956,13 +1131,13 @@
         <v>13559000</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>6015000</v>
+        <v>11842500</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>24060000</v>
+        <v>47370000</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>30176000</v>
+        <v>6866000</v>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
@@ -1536,43 +1711,45 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>2.46.35.037.CHN.00.000</t>
+          <t>Chưa có mã vật tư</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
+          <t>Thanh cái đồng V phân phối mạ bạc</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
+          <t>Thanh cái đồng V phân phối mạ bạc
+Kích thước: 28x40x6mm
+Chiều dài: 920mm</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Swagelok/ Đức</t>
+          <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Cái</t>
+          <t>Thanh</t>
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>19300000</v>
+        <v>48000000</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>18522000</v>
+        <v>1390909</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>648270000</v>
+        <v>5563636</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>27230000</v>
+        <v>186436364</v>
       </c>
       <c r="L24" s="19" t="inlineStr">
         <is>
@@ -1586,23 +1763,22 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>3.96.13.320.USA.00.000</t>
+          <t>2.46.35.037.CHN.00.000</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.</t>
+          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
-NSX: MERRICK</t>
+          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>Merrick/ Mỹ</t>
+          <t>Swagelok/ Đức</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -1611,19 +1787,19 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>56105000</v>
+        <v>19300000</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>23000000</v>
+        <v>18522000</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>46000000</v>
+        <v>648270000</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>66210000</v>
+        <v>27230000</v>
       </c>
       <c r="L25" s="19" t="inlineStr">
         <is>
@@ -1637,15 +1813,1401 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
+          <t>2.46.35.019.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>Swagelok/ Đức</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>19000000</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>12350000</v>
+      </c>
+      <c r="J26" s="17" t="n">
+        <v>24700000</v>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>13300000</v>
+      </c>
+      <c r="L26" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>4.82.22.013.USA.00.000</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>Swagelok/ Đức</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>1319000</v>
+      </c>
+      <c r="J27" s="17" t="n">
+        <v>2638000</v>
+      </c>
+      <c r="K27" s="18" t="n">
+        <v>762000</v>
+      </c>
+      <c r="L27" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>4.82.22.025.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>Swagelok/ Đức</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>644760</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>64476000</v>
+      </c>
+      <c r="K28" s="18" t="n">
+        <v>195524000</v>
+      </c>
+      <c r="L28" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>5.33.70.184.GER.99.000</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>Bộ điều khiển định vị Positioner:
+- Model: TZIDC-V18345- 2020521001
+-Type: Double acting 
+-Sofw.Rev: 3 
+-Supply press: 1,4 ~ 6 bar 
+-Input: Analog 4 ~ 20 mA
+ -Loss of electric: Fail freeze
+- Option: Analog feedback, FSK, Position indicator 
+-NSX: ABB</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>ABB/ Đức</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>83484000</v>
+      </c>
+      <c r="J29" s="17" t="n">
+        <v>417420000</v>
+      </c>
+      <c r="K29" s="18" t="n">
+        <v>7580000</v>
+      </c>
+      <c r="L29" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>3.96.13.144.USA.00.000</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến nhiệt độ - Model: S14405PD3S350B0
+- NSX: MINCO 
+- Element: Platinum 
+- Element length: 6.4 mm 
+- Cable dimension "C": 1778 mm 
+- Cable dimension "L": 8890 mm 
+- Single duplex: Duplex 
+- Sheath: 2.9 mm OD 
+- Type: RTD PT100, 3 Wire 
+- Range: 0 - 260 °C</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>Minco/ Mỹ</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>27923445</v>
+      </c>
+      <c r="J30" s="17" t="n">
+        <v>27923445</v>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>2076555</v>
+      </c>
+      <c r="L30" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm)</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
+Model: LST400 Y0/S15/N1/P6/A1/H1/SC6/B2/CR/M5
+Range: 0.5m to 15m Signal: 4 - 20 mA 
+Supply power: 115 to 230 V AC or 24 V DC.
+NSX: ABB</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>ABB/ Đức</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>189000000</v>
+      </c>
+      <c r="I31" s="17" t="n">
+        <v>58423000</v>
+      </c>
+      <c r="J31" s="17" t="n">
+        <v>58423000</v>
+      </c>
+      <c r="K31" s="18" t="n">
+        <v>130577000</v>
+      </c>
+      <c r="L31" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
+Model: MA3145-230-2-R
+- Điện áp hoạt động tối đa (Max working voltage): ≥ 270 VAC.
+- Điện áp định mức (Voltage rating): 230 VAC.
+- Dòng cắt sét / Khả năng chịu dòng ngắn mạch (Circuit breaker / Surge capacity): ≥ 40 kA.
+NSX: Cooper Crouse-Hinds MTL / Eaton</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>Eaton/ Slovenia</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>21609600</v>
+      </c>
+      <c r="J32" s="17" t="n">
+        <v>64828800</v>
+      </c>
+      <c r="K32" s="18" t="n">
+        <v>40171200</v>
+      </c>
+      <c r="L32" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>3.34.40.009.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Công tắc lưu lượng (Flow Switch)</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>Công tắc lưu lượng (Flow Switch)
+Model: WP/FS-25VFL
+Switch : SPDT Snap Acting Micro
+Rating : 5A 250VAC 
+NSX: Dag Process Instruments Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>Dag Process Instruments Pvt. Ltd/ Ấn Độ</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="J33" s="17" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="K33" s="18" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="L33" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>3.96.13.165.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor
+- Model: PR30-10AC
+Đường kính cạnh phát hiện: 30mm
+- Điện áp hoạt động: 100-240 Vac
+- Ngõ ra điều khiển: NC
+- Protection: IP67</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Autonics/ China</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>1219000</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>911127</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>1822254</v>
+      </c>
+      <c r="K34" s="18" t="n">
+        <v>615746</v>
+      </c>
+      <c r="L34" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>3.96.13.114.KOR.99.000</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor
+- Model: PR18-8AO
+- Đường kính đầu dò: 18mm
+- Điện áp hoạt động: 100-240 Vac
+- Ngõ ra điều khiển: NO
+- Protection: IP67</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>Autonics/ China</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>577200</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>577200</v>
+      </c>
+      <c r="K35" s="18" t="n">
+        <v>572800</v>
+      </c>
+      <c r="L35" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>3.34.20.134.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A12713</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A12713</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>Schnerder/ Czech Republic</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>5784000</v>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>420000</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>420000</v>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>5364000</v>
+      </c>
+      <c r="L36" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>4.90.80.030.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>Joint cover (bao che giữa các khớp nối đường ray cáp điện):
+- Material: PVC
+- Maker: Eunchang T&amp;C</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>235</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>66000</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>26000</v>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>6110000</v>
+      </c>
+      <c r="K37" s="18" t="n">
+        <v>9400000</v>
+      </c>
+      <c r="L37" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>4.90.80.027.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>Nắp che phía cuối đường ray cáp điện (End cap)</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
+- Maker: Eunchang T&amp;C</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>68000</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>21000</v>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>672000</v>
+      </c>
+      <c r="K38" s="18" t="n">
+        <v>1504000</v>
+      </c>
+      <c r="L38" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>2.08.37.001.KOR.97.000</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>Trolley-bar (thanh ray cấp nguồn)</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>Trolley-bar (thanh ray cấp nguồn):
+- Iđm: 60A;
+- Uđm: 400VAC;
+- Length: 3m / cây
+- Material: Copper
+- Maker: EunchangT&amp;C</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>Cây</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>909000</v>
+      </c>
+      <c r="I39" s="17" t="n">
+        <v>890000</v>
+      </c>
+      <c r="J39" s="17" t="n">
+        <v>24920000</v>
+      </c>
+      <c r="K39" s="18" t="n">
+        <v>532000</v>
+      </c>
+      <c r="L39" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>3.34.20.133.CHN.99.000</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A6913</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A6913
+Control station composition: 06 push buttons + 01 emergency stop
+Product compatibility: 
+ZB2BE102 for emergency stop, XEN-G1191 for each direction
+Color: Yellow</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>Schnerder/ Czech Republic</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>13319000</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>3290400</v>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>3290400</v>
+      </c>
+      <c r="K40" s="18" t="n">
+        <v>10028600</v>
+      </c>
+      <c r="L40" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 3 tấn</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 3 tấn
+Kích thước: rộng 25mm x dài 60mm</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>MT/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>610000</v>
+      </c>
+      <c r="I41" s="17" t="n">
+        <v>314600</v>
+      </c>
+      <c r="J41" s="17" t="n">
+        <v>314600</v>
+      </c>
+      <c r="K41" s="18" t="n">
+        <v>295400</v>
+      </c>
+      <c r="L41" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>2.50.05.003.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>Cáp inox 304 
+Kích thước: Ø 3 mm</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>Cáp inox 304 
+Kích thước: Ø 3 mm</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>Mét</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H42" s="17" t="n">
+        <v>37000</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>24000</v>
+      </c>
+      <c r="J42" s="17" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="K42" s="18" t="n">
+        <v>780000</v>
+      </c>
+      <c r="L42" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>Phe cài trục ngoài cho đường kính 28mm</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>Phe cài trục ngoài cho đường kính 28mm.
+Vật liệu: Inox 304</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>56000</v>
+      </c>
+      <c r="I43" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J43" s="17" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K43" s="18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L43" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>2.06.60.080.TPE.00.000</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>Kẹp cố định đầu ray
+Loại: CH2260
+Size: 80x51x3mm</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Kẹp cố định đầu ray
+Loại: CH2260
+Size: 80x51x3mm
+Vật liệu: Inox 304
+Hãng: ITS Đài loan</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>ITS/ Đài Loan</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="17" t="n">
+        <v>2254000</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>578078</v>
+      </c>
+      <c r="J44" s="17" t="n">
+        <v>1156156</v>
+      </c>
+      <c r="K44" s="18" t="n">
+        <v>3351844</v>
+      </c>
+      <c r="L44" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>3.15.44.076.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>Cáp điện dẹt cho cầu trục
+Quy cách: 16mm2 x 4C
+Ruột mềm</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>Cáp điện dẹt cho cầu trục
+Quy cách: 16mm2 x 4C
+Ruột mềm
+Điện áp: 450/750V
+Cách điện: PVC, dẻo
+NSX: Imatek</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>Imatek/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>Mét</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>711000</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>76000</v>
+      </c>
+      <c r="J45" s="17" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="K45" s="18" t="n">
+        <v>31750000</v>
+      </c>
+      <c r="L45" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>3.20.22.003.TPE.00.000</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>Khóa cáp 
+Dùng cho cáp: 3mm</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>Khóa cáp 
+Dùng cho cáp: 3mm</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>14000</v>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>770000</v>
+      </c>
+      <c r="K46" s="18" t="n">
+        <v>330000</v>
+      </c>
+      <c r="L46" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>3.34.20.130.CHN.99.000</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Pendant control station (Tay bấm điều khiển tời điện): 
+- Type: XAC-A6713</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>Pendant control station (Tay bấm điều khiển tời điện): 
+- Type: XAC-A6713
+Control station composition: 06, push buttons + 01 emergency stop</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>Schnerder/ Czech Republic</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="17" t="n">
+        <v>7406000</v>
+      </c>
+      <c r="I47" s="17" t="n">
+        <v>3310185</v>
+      </c>
+      <c r="J47" s="17" t="n">
+        <v>3310185</v>
+      </c>
+      <c r="K47" s="18" t="n">
+        <v>4095815</v>
+      </c>
+      <c r="L47" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 7 tấn</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 7 tấn:
+ + Kích thước: 60 x 175x 3mm
+ + Vật liệu: thép</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="17" t="n">
+        <v>656000</v>
+      </c>
+      <c r="I48" s="17" t="n">
+        <v>585000</v>
+      </c>
+      <c r="J48" s="17" t="n">
+        <v>585000</v>
+      </c>
+      <c r="K48" s="18" t="n">
+        <v>71000</v>
+      </c>
+      <c r="L48" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>Sơn dầu Jotun chống sét Green 437</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>Sơn dầu Jotun chống sét Green 437</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>625000</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="18" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="L49" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>3.82.63.103.LTU.00.000</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO HBS 01 - FPN</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO:
+- Hãng: ABB
+- Mã: HBS 01 - FPN
+- PR (Product Revision): M</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>ABB/ Lithuania</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H50" s="17" t="n">
+        <v>21120000</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>19360000</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>580800000</v>
+      </c>
+      <c r="K50" s="18" t="n">
+        <v>52800000</v>
+      </c>
+      <c r="L50" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>3.94.00.808.MLT.00.000</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO HBS01-FPH</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO:
+- Hãng: ABB
+- Mã: HBS 01 - FPH
+- PR (Product Revision): M</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>ABB/ Lithuania</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="H51" s="17" t="n">
+        <v>21120000</v>
+      </c>
+      <c r="I51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="18" t="n">
+        <v>549120000</v>
+      </c>
+      <c r="L51" s="19" t="inlineStr">
+        <is>
+          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Lining Plate (Compound Armour Plate)
 Tấm lót thân máy nghiền
@@ -1660,52 +3222,52 @@
 - Chống mài mòn theo ASTM G65: 0,0060 mm3/m</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>ML/ Ba Lan</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F52" s="14" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G26" s="17" t="n">
+      <c r="G52" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="17" t="n">
+      <c r="H52" s="17" t="n">
         <v>2618304000</v>
       </c>
-      <c r="I26" s="17" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="J26" s="17" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="K26" s="18" t="n">
-        <v>5234008000</v>
-      </c>
-      <c r="L26" s="19" t="inlineStr">
+      <c r="I52" s="17" t="n">
+        <v>1845000000</v>
+      </c>
+      <c r="J52" s="17" t="n">
+        <v>3690000000</v>
+      </c>
+      <c r="K52" s="18" t="n">
+        <v>1546608000</v>
+      </c>
+      <c r="L52" s="19" t="inlineStr">
         <is>
           <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>Bơm (SP-Circulation pump):
 TP400 PP, P4-400V/50
@@ -1722,90 +3284,90 @@
 IEC60034-1</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E53" s="15" t="inlineStr">
         <is>
           <t>Grundfos/ Eu</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F53" s="14" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G27" s="17" t="n">
+      <c r="G53" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="17" t="n">
+      <c r="H53" s="17" t="n">
         <v>770000000</v>
       </c>
-      <c r="I27" s="17" t="n">
+      <c r="I53" s="17" t="n">
         <v>750000000</v>
       </c>
-      <c r="J27" s="17" t="n">
+      <c r="J53" s="17" t="n">
         <v>1500000000</v>
       </c>
-      <c r="K27" s="18" t="n">
+      <c r="K53" s="18" t="n">
         <v>40000000</v>
       </c>
-      <c r="L27" s="19" t="inlineStr">
+      <c r="L53" s="19" t="inlineStr">
         <is>
           <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>TỔNG CỘNG CÁC MỤC ĐÃ CHỐT THẨM ĐỊNH:</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n"/>
-      <c r="C28" s="21" t="n"/>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="21" t="n"/>
-      <c r="G28" s="21" t="n"/>
-      <c r="H28" s="21" t="n"/>
-      <c r="I28" s="21" t="n"/>
-      <c r="J28" s="22" t="n">
-        <v>2953039416.5</v>
-      </c>
-      <c r="K28" s="23" t="n">
-        <v>5937874583.5</v>
-      </c>
-      <c r="L28" s="21" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B54" s="21" t="n"/>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="21" t="n"/>
+      <c r="I54" s="21" t="n"/>
+      <c r="J54" s="22" t="n">
+        <v>7946260092.5</v>
+      </c>
+      <c r="K54" s="23" t="n">
+        <v>3425998907.5</v>
+      </c>
+      <c r="L54" s="21" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="24" t="inlineStr">
         <is>
           <t>NGƯỜI LẬP BÁO CÁO / THƯ KÝ TỔ TTĐ</t>
         </is>
       </c>
-      <c r="J31" s="24" t="inlineStr">
+      <c r="J57" s="24" t="inlineStr">
         <is>
           <t>TỔ TRƯỞNG TỔ THẨM ĐỊNH DỰ TOÁN</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="25" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="25" t="inlineStr">
         <is>
           <t>(Ký và ghi rõ họ tên)</t>
         </is>
       </c>
-      <c r="J32" s="25" t="inlineStr">
+      <c r="J58" s="25" t="inlineStr">
         <is>
           <t>(Ký và ghi rõ họ tên)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="26" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="26" t="inlineStr">
         <is>
           <t>Nguyễn Anh Hiếu</t>
         </is>
       </c>
-      <c r="J37" s="26" t="inlineStr">
+      <c r="J63" s="26" t="inlineStr">
         <is>
           <t>...................................................</t>
         </is>
@@ -1815,7 +3377,6 @@
   <mergeCells count="13">
     <mergeCell ref="H9:L9"/>
     <mergeCell ref="D9:G9"/>
-    <mergeCell ref="A28:I28"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="D8:G8"/>
     <mergeCell ref="A8:C8"/>
@@ -1826,6 +3387,7 @@
     <mergeCell ref="A6:L6"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="H8:L8"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId1"/>
@@ -1843,6 +3405,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1883,7 +3471,7 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Hồ sơ: Bang_Tham_Dinh_Du_Toan (3) - Bản Mới - Bản Mới | Cập nhật: 09/09/2026 09:12</t>
+          <t>Hồ sơ: Bang_Tham_Dinh_Du_Toan (3) - Bản Mới - Bản Mới | Cập nhật: 10/09/2026 16:18</t>
         </is>
       </c>
     </row>
@@ -2000,13 +3588,13 @@
         <v>54236000</v>
       </c>
       <c r="J5" s="31" t="n">
-        <v>6015000</v>
+        <v>11842500</v>
       </c>
       <c r="K5" s="31" t="n">
-        <v>24060000</v>
+        <v>47370000</v>
       </c>
       <c r="L5" s="23" t="n">
-        <v>30176000</v>
+        <v>6866000</v>
       </c>
       <c r="M5" s="32" t="inlineStr">
         <is>
@@ -2988,62 +4576,62 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="28" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>Thanh cái đồng V phân phối mạ bạc</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>Thanh cái đồng V phân phối mạ bạc
 Kích thước: 28x40x6mm
 Chiều dài: 920mm</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>Thanh</t>
         </is>
       </c>
-      <c r="G21" s="17" t="n">
+      <c r="G21" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="17" t="n">
+      <c r="H21" s="31" t="n">
         <v>48000000</v>
       </c>
-      <c r="I21" s="17" t="n">
+      <c r="I21" s="31" t="n">
         <v>192000000</v>
       </c>
-      <c r="J21" s="17" t="n">
-        <v>48000000</v>
-      </c>
-      <c r="K21" s="17" t="n">
-        <v>192000000</v>
-      </c>
-      <c r="L21" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N21" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư | Thay thế cho vật tư hư hỏng theo BBKT 37/2026/VH-VT4 | Vật tư mua mới, không đề xuất trong KHSXKD 2026</t>
+      <c r="J21" s="31" t="n">
+        <v>1390909</v>
+      </c>
+      <c r="K21" s="31" t="n">
+        <v>5563636</v>
+      </c>
+      <c r="L21" s="23" t="n">
+        <v>186436364</v>
+      </c>
+      <c r="M21" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N21" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -3167,176 +4755,176 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>2.46.35.019.CHN.00.000</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>Swagelok/ Đức</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G24" s="17" t="n">
+      <c r="G24" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="17" t="n">
+      <c r="H24" s="31" t="n">
         <v>19000000</v>
       </c>
-      <c r="I24" s="17" t="n">
+      <c r="I24" s="31" t="n">
         <v>38000000</v>
       </c>
-      <c r="J24" s="17" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="K24" s="17" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="L24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N24" s="16" t="inlineStr">
-        <is>
-          <t>2.46.35.019.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="J24" s="31" t="n">
+        <v>12350000</v>
+      </c>
+      <c r="K24" s="31" t="n">
+        <v>24700000</v>
+      </c>
+      <c r="L24" s="23" t="n">
+        <v>13300000</v>
+      </c>
+      <c r="M24" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N24" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="28" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>4.82.22.013.USA.00.000</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
         <is>
           <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="30" t="inlineStr">
         <is>
           <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>Swagelok/ Đức</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G25" s="17" t="n">
+      <c r="G25" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="17" t="n">
+      <c r="H25" s="31" t="n">
         <v>1700000</v>
       </c>
-      <c r="I25" s="17" t="n">
+      <c r="I25" s="31" t="n">
         <v>3400000</v>
       </c>
-      <c r="J25" s="17" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="K25" s="17" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="L25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N25" s="16" t="inlineStr">
-        <is>
-          <t>4.82.22.013.USA.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="J25" s="31" t="n">
+        <v>1319000</v>
+      </c>
+      <c r="K25" s="31" t="n">
+        <v>2638000</v>
+      </c>
+      <c r="L25" s="23" t="n">
+        <v>762000</v>
+      </c>
+      <c r="M25" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N25" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>4.82.22.025.CHN.00.000</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
         <is>
           <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>Swagelok/ Đức</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G26" s="17" t="n">
+      <c r="G26" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="H26" s="17" t="n">
+      <c r="H26" s="31" t="n">
         <v>2600000</v>
       </c>
-      <c r="I26" s="17" t="n">
+      <c r="I26" s="31" t="n">
         <v>260000000</v>
       </c>
-      <c r="J26" s="17" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="K26" s="17" t="n">
-        <v>260000000</v>
-      </c>
-      <c r="L26" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N26" s="16" t="inlineStr">
-        <is>
-          <t>4.82.22.025.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+      <c r="J26" s="31" t="n">
+        <v>644760</v>
+      </c>
+      <c r="K26" s="31" t="n">
+        <v>64476000</v>
+      </c>
+      <c r="L26" s="23" t="n">
+        <v>195524000</v>
+      </c>
+      <c r="M26" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N26" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -3399,20 +4987,20 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="28" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>5.33.70.184.GER.99.000</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
         <is>
           <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="30" t="inlineStr">
         <is>
           <t>Bộ điều khiển định vị Positioner:
 - Model: TZIDC-V18345- 2020521001
@@ -3425,60 +5013,60 @@
 -NSX: ABB</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" s="29" t="inlineStr">
         <is>
           <t>ABB/ Đức</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="F28" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G28" s="17" t="n">
+      <c r="G28" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="17" t="n">
+      <c r="H28" s="31" t="n">
         <v>85000000</v>
       </c>
-      <c r="I28" s="17" t="n">
+      <c r="I28" s="31" t="n">
         <v>425000000</v>
       </c>
-      <c r="J28" s="17" t="n">
-        <v>85000000</v>
-      </c>
-      <c r="K28" s="17" t="n">
-        <v>425000000</v>
-      </c>
-      <c r="L28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N28" s="16" t="inlineStr">
-        <is>
-          <t>5.33.70.184.GER.99.000 | Thay thế các bộ positioner điều khiển damper gió SA bị xì khí nén của tổ máy S2 | Vật tư được đề xuất trong KHSXKD năm 2026,nhưng phát sinh hư hỏng thêm 2 bộ vượt nhu cầu dự kiến, nên đề xuất mua sắm bổ sung. Tên vật tư được đặt lại theo quy tắc chuẩn hóa.</t>
+      <c r="J28" s="31" t="n">
+        <v>83484000</v>
+      </c>
+      <c r="K28" s="31" t="n">
+        <v>417420000</v>
+      </c>
+      <c r="L28" s="23" t="n">
+        <v>7580000</v>
+      </c>
+      <c r="M28" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N28" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="28" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>3.96.13.144.USA.00.000</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>Cảm biến nhiệt độ - Model: S14405PD3S350B0
 - NSX: MINCO 
@@ -3492,119 +5080,119 @@
 - Range: 0 - 260 °C</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>Minco/ Mỹ</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F29" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G29" s="17" t="n">
+      <c r="G29" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="17" t="n">
+      <c r="H29" s="31" t="n">
         <v>30000000</v>
       </c>
-      <c r="I29" s="17" t="n">
+      <c r="I29" s="31" t="n">
         <v>30000000</v>
       </c>
-      <c r="J29" s="17" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="K29" s="17" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="L29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N29" s="16" t="inlineStr">
-        <is>
-          <t>3.96.13.144.USA.00.000 | BBKT- 1008/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến nhiệt độ số 2 gối chặn BFPT B S2 báo lỗi.Vật tư có trong KH SXKD 2026 (mã KH TXBS.26.562). | Mua sắm dự phòng hết tồn kho thiết bị giám sát quan trọng.</t>
+      <c r="J29" s="31" t="n">
+        <v>27923445</v>
+      </c>
+      <c r="K29" s="31" t="n">
+        <v>27923445</v>
+      </c>
+      <c r="L29" s="23" t="n">
+        <v>2076555</v>
+      </c>
+      <c r="M29" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N29" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="28" t="n">
+      <c r="A30" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>3.96.13.320.USA.00.000</t>
         </is>
       </c>
-      <c r="C30" s="30" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.</t>
         </is>
       </c>
-      <c r="D30" s="30" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
 NSX: MERRICK</t>
         </is>
       </c>
-      <c r="E30" s="29" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Merrick/ Mỹ</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="F30" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G30" s="31" t="n">
+      <c r="G30" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="31" t="n">
+      <c r="H30" s="17" t="n">
         <v>56105000</v>
       </c>
-      <c r="I30" s="31" t="n">
+      <c r="I30" s="17" t="n">
         <v>112210000</v>
       </c>
-      <c r="J30" s="31" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="K30" s="31" t="n">
-        <v>46000000</v>
-      </c>
-      <c r="L30" s="23" t="n">
-        <v>66210000</v>
-      </c>
-      <c r="M30" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N30" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J30" s="17" t="n">
+        <v>56105000</v>
+      </c>
+      <c r="K30" s="17" t="n">
+        <v>112210000</v>
+      </c>
+      <c r="L30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>3.96.13.320.USA.00.000 | BBKT- 1033/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến khối lượng than – máy cấp A tổ máy S3 báo sai giá trị.Vật tư không có trong KH SXKD 2026. | Mua sắm dự phòng hết tồn kho thiết bị giám sát quan trọng.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="28" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
         <is>
           <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="30" t="inlineStr">
         <is>
           <t>LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
 Model: LST400 Y0/S15/N1/P6/A1/H1/SC6/B2/CR/M5
@@ -3613,42 +5201,42 @@
 NSX: ABB</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E31" s="29" t="inlineStr">
         <is>
           <t>ABB/ Đức</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G31" s="17" t="n">
+      <c r="G31" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="17" t="n">
+      <c r="H31" s="31" t="n">
         <v>189000000</v>
       </c>
-      <c r="I31" s="17" t="n">
+      <c r="I31" s="31" t="n">
         <v>189000000</v>
       </c>
-      <c r="J31" s="17" t="n">
-        <v>189000000</v>
-      </c>
-      <c r="K31" s="17" t="n">
-        <v>189000000</v>
-      </c>
-      <c r="L31" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N31" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã VT | BBKT- 955/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến báo mức nước tổng kênh tuần hoàn tổ máy S1 báo sai giá trị. | Vật tư không có trong KH SXKD 2026.</t>
+      <c r="J31" s="31" t="n">
+        <v>58423000</v>
+      </c>
+      <c r="K31" s="31" t="n">
+        <v>58423000</v>
+      </c>
+      <c r="L31" s="23" t="n">
+        <v>130577000</v>
+      </c>
+      <c r="M31" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N31" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -4444,20 +6032,20 @@
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="14" t="n">
+      <c r="A45" s="28" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C45" s="30" t="inlineStr">
         <is>
           <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="30" t="inlineStr">
         <is>
           <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
 Model: MA3145-230-2-R
@@ -4467,42 +6055,42 @@
 NSX: Cooper Crouse-Hinds MTL / Eaton</t>
         </is>
       </c>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="E45" s="29" t="inlineStr">
         <is>
           <t>Eaton/ Slovenia</t>
         </is>
       </c>
-      <c r="F45" s="14" t="inlineStr">
+      <c r="F45" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G45" s="17" t="n">
+      <c r="G45" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="17" t="n">
+      <c r="H45" s="31" t="n">
         <v>35000000</v>
       </c>
-      <c r="I45" s="17" t="n">
+      <c r="I45" s="31" t="n">
         <v>105000000</v>
       </c>
-      <c r="J45" s="17" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="K45" s="17" t="n">
-        <v>105000000</v>
-      </c>
-      <c r="L45" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N45" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã VT | BBKT- 1089/2026/VH-VT4_ Kiểm tra, khắc phục các con đo lưu lượng nước biển S3 không. hiển thị. | Vật tư không có trong KH SXKD 2026.</t>
+      <c r="J45" s="31" t="n">
+        <v>21609600</v>
+      </c>
+      <c r="K45" s="31" t="n">
+        <v>64828800</v>
+      </c>
+      <c r="L45" s="23" t="n">
+        <v>40171200</v>
+      </c>
+      <c r="M45" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N45" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -4567,20 +6155,20 @@
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="14" t="n">
+      <c r="A47" s="28" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="29" t="inlineStr">
         <is>
           <t>3.34.40.009.IND.00.000</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C47" s="30" t="inlineStr">
         <is>
           <t>Công tắc lưu lượng (Flow Switch)</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D47" s="30" t="inlineStr">
         <is>
           <t>Công tắc lưu lượng (Flow Switch)
 Model: WP/FS-25VFL
@@ -4589,42 +6177,42 @@
 NSX: Dag Process Instruments Pvt. Ltd</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr">
+      <c r="E47" s="29" t="inlineStr">
         <is>
           <t>Dag Process Instruments Pvt. Ltd/ Ấn Độ</t>
         </is>
       </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="F47" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G47" s="17" t="n">
+      <c r="G47" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="17" t="n">
+      <c r="H47" s="31" t="n">
         <v>38000000</v>
       </c>
-      <c r="I47" s="17" t="n">
+      <c r="I47" s="31" t="n">
         <v>38000000</v>
       </c>
-      <c r="J47" s="17" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="K47" s="17" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="L47" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N47" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã VT | BBKT- 1122/2026/VH-VT4_ Kiểm tra, lỗi tín hiệu lưu lượng gió chèn 1B – ESP -  S1 báo lỗi. | Vật tư không có trong KH SXKD 2026.</t>
+      <c r="J47" s="31" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="K47" s="31" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="L47" s="23" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="M47" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N47" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -4692,20 +6280,20 @@
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="14" t="n">
+      <c r="A49" s="28" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" s="29" t="inlineStr">
         <is>
           <t>3.96.13.165.KOR.00.000</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C49" s="30" t="inlineStr">
         <is>
           <t>Cảm biến tiệm cận/proximity sensor</t>
         </is>
       </c>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="D49" s="30" t="inlineStr">
         <is>
           <t>Cảm biến tiệm cận/proximity sensor
 - Model: PR30-10AC
@@ -4715,60 +6303,60 @@
 - Protection: IP67</t>
         </is>
       </c>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="E49" s="29" t="inlineStr">
         <is>
           <t>Autonics/ China</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="F49" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G49" s="17" t="n">
+      <c r="G49" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="17" t="n">
+      <c r="H49" s="31" t="n">
         <v>1219000</v>
       </c>
-      <c r="I49" s="17" t="n">
+      <c r="I49" s="31" t="n">
         <v>2438000</v>
       </c>
-      <c r="J49" s="17" t="n">
-        <v>1219000</v>
-      </c>
-      <c r="K49" s="17" t="n">
-        <v>2438000</v>
-      </c>
-      <c r="L49" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N49" s="16" t="inlineStr">
-        <is>
-          <t>3.96.13.165.KOR.00.000 | Sửa chữa Tời điện số 15 tấn A Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương, kích thước theo file BBKT đính kèm</t>
+      <c r="J49" s="31" t="n">
+        <v>911127</v>
+      </c>
+      <c r="K49" s="31" t="n">
+        <v>1822254</v>
+      </c>
+      <c r="L49" s="23" t="n">
+        <v>615746</v>
+      </c>
+      <c r="M49" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N49" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="14" t="n">
+      <c r="A50" s="28" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="29" t="inlineStr">
         <is>
           <t>3.96.13.114.KOR.99.000</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C50" s="30" t="inlineStr">
         <is>
           <t>Cảm biến tiệm cận/proximity sensor</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="30" t="inlineStr">
         <is>
           <t>Cảm biến tiệm cận/proximity sensor
 - Model: PR18-8AO
@@ -4778,42 +6366,42 @@
 - Protection: IP67</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
+      <c r="E50" s="29" t="inlineStr">
         <is>
           <t>Autonics/ China</t>
         </is>
       </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="F50" s="28" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G50" s="17" t="n">
+      <c r="G50" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="17" t="n">
+      <c r="H50" s="31" t="n">
         <v>1150000</v>
       </c>
-      <c r="I50" s="17" t="n">
+      <c r="I50" s="31" t="n">
         <v>1150000</v>
       </c>
-      <c r="J50" s="17" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="K50" s="17" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="L50" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N50" s="16" t="inlineStr">
-        <is>
-          <t>3.96.13.114.KOR.99.000 | Sửa chữa Tời điện số 15 tấn A Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J50" s="31" t="n">
+        <v>577200</v>
+      </c>
+      <c r="K50" s="31" t="n">
+        <v>577200</v>
+      </c>
+      <c r="L50" s="23" t="n">
+        <v>572800</v>
+      </c>
+      <c r="M50" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N50" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -4859,10 +6447,10 @@
         <v>597060000</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>535000</v>
+        <v>465000</v>
       </c>
       <c r="K51" s="17" t="n">
-        <v>686940000</v>
+        <v>597060000</v>
       </c>
       <c r="L51" s="17" t="n">
         <v>0</v>
@@ -4879,62 +6467,62 @@
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="14" t="n">
+      <c r="A52" s="28" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
         <is>
           <t>3.34.20.134.CHN.00.000</t>
         </is>
       </c>
-      <c r="C52" s="16" t="inlineStr">
+      <c r="C52" s="30" t="inlineStr">
         <is>
           <t>Pendant control station:
 Type: XAC-A12713</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="30" t="inlineStr">
         <is>
           <t>Pendant control station:
 Type: XAC-A12713</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr">
+      <c r="E52" s="29" t="inlineStr">
         <is>
           <t>Schnerder/ Czech Republic</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="F52" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G52" s="17" t="n">
+      <c r="G52" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="17" t="n">
+      <c r="H52" s="31" t="n">
         <v>5784000</v>
       </c>
-      <c r="I52" s="17" t="n">
+      <c r="I52" s="31" t="n">
         <v>5784000</v>
       </c>
-      <c r="J52" s="17" t="n">
-        <v>5784000</v>
-      </c>
-      <c r="K52" s="17" t="n">
-        <v>5784000</v>
-      </c>
-      <c r="L52" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N52" s="16" t="inlineStr">
-        <is>
-          <t>3.34.20.134.CHN.00.000 | Sửa chữa tời điện Tời điện số 15 tấn B Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J52" s="31" t="n">
+        <v>420000</v>
+      </c>
+      <c r="K52" s="31" t="n">
+        <v>420000</v>
+      </c>
+      <c r="L52" s="23" t="n">
+        <v>5364000</v>
+      </c>
+      <c r="M52" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N52" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -5001,139 +6589,139 @@
       </c>
     </row>
     <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="14" t="n">
+      <c r="A54" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>4.90.80.030.KOR.00.000</t>
         </is>
       </c>
-      <c r="C54" s="16" t="inlineStr">
+      <c r="C54" s="30" t="inlineStr">
         <is>
           <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)</t>
         </is>
       </c>
-      <c r="D54" s="16" t="inlineStr">
+      <c r="D54" s="30" t="inlineStr">
         <is>
           <t>Joint cover (bao che giữa các khớp nối đường ray cáp điện):
 - Material: PVC
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="E54" s="15" t="inlineStr">
+      <c r="E54" s="29" t="inlineStr">
         <is>
           <t>Eunchang/ Hàn Quốc</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F54" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G54" s="17" t="n">
+      <c r="G54" s="31" t="n">
         <v>235</v>
       </c>
-      <c r="H54" s="17" t="n">
+      <c r="H54" s="31" t="n">
         <v>66000</v>
       </c>
-      <c r="I54" s="17" t="n">
+      <c r="I54" s="31" t="n">
         <v>15510000</v>
       </c>
-      <c r="J54" s="17" t="n">
-        <v>66000</v>
-      </c>
-      <c r="K54" s="17" t="n">
-        <v>15510000</v>
-      </c>
-      <c r="L54" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N54" s="16" t="inlineStr">
-        <is>
-          <t>4.90.80.030.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 435/2026/VH-VT4; 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J54" s="31" t="n">
+        <v>26000</v>
+      </c>
+      <c r="K54" s="31" t="n">
+        <v>6110000</v>
+      </c>
+      <c r="L54" s="23" t="n">
+        <v>9400000</v>
+      </c>
+      <c r="M54" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N54" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="14" t="n">
+      <c r="A55" s="28" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B55" s="29" t="inlineStr">
         <is>
           <t>4.90.80.027.KOR.00.000</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
+      <c r="C55" s="30" t="inlineStr">
         <is>
           <t>Nắp che phía cuối đường ray cáp điện (End cap)</t>
         </is>
       </c>
-      <c r="D55" s="16" t="inlineStr">
+      <c r="D55" s="30" t="inlineStr">
         <is>
           <t>Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="E55" s="15" t="inlineStr">
+      <c r="E55" s="29" t="inlineStr">
         <is>
           <t>Eunchang/ Hàn Quốc</t>
         </is>
       </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="F55" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G55" s="17" t="n">
+      <c r="G55" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="H55" s="17" t="n">
+      <c r="H55" s="31" t="n">
         <v>68000</v>
       </c>
-      <c r="I55" s="17" t="n">
+      <c r="I55" s="31" t="n">
         <v>2176000</v>
       </c>
-      <c r="J55" s="17" t="n">
-        <v>68000</v>
-      </c>
-      <c r="K55" s="17" t="n">
-        <v>2176000</v>
-      </c>
-      <c r="L55" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N55" s="16" t="inlineStr">
-        <is>
-          <t>4.90.80.027.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 435/2026/VH-VT4; 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J55" s="31" t="n">
+        <v>21000</v>
+      </c>
+      <c r="K55" s="31" t="n">
+        <v>672000</v>
+      </c>
+      <c r="L55" s="23" t="n">
+        <v>1504000</v>
+      </c>
+      <c r="M55" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N55" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="14" t="n">
+      <c r="A56" s="28" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B56" s="29" t="inlineStr">
         <is>
           <t>2.08.37.001.KOR.97.000</t>
         </is>
       </c>
-      <c r="C56" s="16" t="inlineStr">
+      <c r="C56" s="30" t="inlineStr">
         <is>
           <t>Trolley-bar (thanh ray cấp nguồn)</t>
         </is>
       </c>
-      <c r="D56" s="16" t="inlineStr">
+      <c r="D56" s="30" t="inlineStr">
         <is>
           <t>Trolley-bar (thanh ray cấp nguồn):
 - Iđm: 60A;
@@ -5143,42 +6731,42 @@
 - Maker: EunchangT&amp;C</t>
         </is>
       </c>
-      <c r="E56" s="15" t="inlineStr">
+      <c r="E56" s="29" t="inlineStr">
         <is>
           <t>Eunchang/ Hàn Quốc</t>
         </is>
       </c>
-      <c r="F56" s="14" t="inlineStr">
+      <c r="F56" s="28" t="inlineStr">
         <is>
           <t>Cây</t>
         </is>
       </c>
-      <c r="G56" s="17" t="n">
+      <c r="G56" s="31" t="n">
         <v>28</v>
       </c>
-      <c r="H56" s="17" t="n">
+      <c r="H56" s="31" t="n">
         <v>909000</v>
       </c>
-      <c r="I56" s="17" t="n">
+      <c r="I56" s="31" t="n">
         <v>25452000</v>
       </c>
-      <c r="J56" s="17" t="n">
-        <v>909000</v>
-      </c>
-      <c r="K56" s="17" t="n">
-        <v>25452000</v>
-      </c>
-      <c r="L56" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N56" s="16" t="inlineStr">
-        <is>
-          <t>2.08.37.001.KOR.97.000 | Sửa chữa tời điện Tời điện 15 tấn quạt gió 2B theo BBKT 435/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J56" s="31" t="n">
+        <v>890000</v>
+      </c>
+      <c r="K56" s="31" t="n">
+        <v>24920000</v>
+      </c>
+      <c r="L56" s="23" t="n">
+        <v>532000</v>
+      </c>
+      <c r="M56" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N56" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -5303,21 +6891,21 @@
       </c>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="14" t="n">
+      <c r="A59" s="28" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B59" s="29" t="inlineStr">
         <is>
           <t>3.34.20.133.CHN.99.000</t>
         </is>
       </c>
-      <c r="C59" s="16" t="inlineStr">
+      <c r="C59" s="30" t="inlineStr">
         <is>
           <t>Pendant control station:
 Type: XAC-A6913</t>
         </is>
       </c>
-      <c r="D59" s="16" t="inlineStr">
+      <c r="D59" s="30" t="inlineStr">
         <is>
           <t>Pendant control station:
 Type: XAC-A6913
@@ -5327,101 +6915,101 @@
 Color: Yellow</t>
         </is>
       </c>
-      <c r="E59" s="15" t="inlineStr">
+      <c r="E59" s="29" t="inlineStr">
         <is>
           <t>Schnerder/ Czech Republic</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="F59" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G59" s="17" t="n">
+      <c r="G59" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H59" s="17" t="n">
+      <c r="H59" s="31" t="n">
         <v>13319000</v>
       </c>
-      <c r="I59" s="17" t="n">
+      <c r="I59" s="31" t="n">
         <v>13319000</v>
       </c>
-      <c r="J59" s="17" t="n">
-        <v>13319000</v>
-      </c>
-      <c r="K59" s="17" t="n">
-        <v>13319000</v>
-      </c>
-      <c r="L59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N59" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 10 tấn quạt khói theo BBKT 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J59" s="31" t="n">
+        <v>3290400</v>
+      </c>
+      <c r="K59" s="31" t="n">
+        <v>3290400</v>
+      </c>
+      <c r="L59" s="23" t="n">
+        <v>10028600</v>
+      </c>
+      <c r="M59" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N59" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="14" t="n">
+      <c r="A60" s="28" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B60" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C60" s="16" t="inlineStr">
+      <c r="C60" s="30" t="inlineStr">
         <is>
           <t>Lưỡi gà móc cẩu 3 tấn</t>
         </is>
       </c>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="D60" s="30" t="inlineStr">
         <is>
           <t>Lưỡi gà móc cẩu 3 tấn
 Kích thước: rộng 25mm x dài 60mm</t>
         </is>
       </c>
-      <c r="E60" s="15" t="inlineStr">
+      <c r="E60" s="29" t="inlineStr">
         <is>
           <t>MT/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F60" s="14" t="inlineStr">
+      <c r="F60" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G60" s="17" t="n">
+      <c r="G60" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H60" s="17" t="n">
+      <c r="H60" s="31" t="n">
         <v>610000</v>
       </c>
-      <c r="I60" s="17" t="n">
+      <c r="I60" s="31" t="n">
         <v>610000</v>
       </c>
-      <c r="J60" s="17" t="n">
-        <v>610000</v>
-      </c>
-      <c r="K60" s="17" t="n">
-        <v>610000</v>
-      </c>
-      <c r="L60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N60" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J60" s="31" t="n">
+        <v>314600</v>
+      </c>
+      <c r="K60" s="31" t="n">
+        <v>314600</v>
+      </c>
+      <c r="L60" s="23" t="n">
+        <v>295400</v>
+      </c>
+      <c r="M60" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N60" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -5543,121 +7131,121 @@
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="14" t="n">
+      <c r="A63" s="28" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="B63" s="29" t="inlineStr">
         <is>
           <t>2.50.05.003.CHN.00.000</t>
         </is>
       </c>
-      <c r="C63" s="16" t="inlineStr">
+      <c r="C63" s="30" t="inlineStr">
         <is>
           <t>Cáp inox 304 
 Kích thước: Ø 3 mm</t>
         </is>
       </c>
-      <c r="D63" s="16" t="inlineStr">
+      <c r="D63" s="30" t="inlineStr">
         <is>
           <t>Cáp inox 304 
 Kích thước: Ø 3 mm</t>
         </is>
       </c>
-      <c r="E63" s="15" t="inlineStr">
+      <c r="E63" s="29" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F63" s="14" t="inlineStr">
+      <c r="F63" s="28" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G63" s="17" t="n">
+      <c r="G63" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="H63" s="17" t="n">
+      <c r="H63" s="31" t="n">
         <v>37000</v>
       </c>
-      <c r="I63" s="17" t="n">
+      <c r="I63" s="31" t="n">
         <v>2220000</v>
       </c>
-      <c r="J63" s="17" t="n">
-        <v>37000</v>
-      </c>
-      <c r="K63" s="17" t="n">
-        <v>2220000</v>
-      </c>
-      <c r="L63" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N63" s="16" t="inlineStr">
-        <is>
-          <t>2.50.05.003.CHN.00.000 | Sửa chữa Tời điện 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J63" s="31" t="n">
+        <v>24000</v>
+      </c>
+      <c r="K63" s="31" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="L63" s="23" t="n">
+        <v>780000</v>
+      </c>
+      <c r="M63" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N63" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="14" t="n">
+      <c r="A64" s="28" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="15" t="inlineStr">
+      <c r="B64" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>Phe cài trục ngoài cho đường kính 28mm</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>Phe cài trục ngoài cho đường kính 28mm.
 Vật liệu: Inox 304</t>
         </is>
       </c>
-      <c r="E64" s="15" t="inlineStr">
+      <c r="E64" s="29" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F64" s="14" t="inlineStr">
+      <c r="F64" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G64" s="17" t="n">
+      <c r="G64" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H64" s="17" t="n">
+      <c r="H64" s="31" t="n">
         <v>56000</v>
       </c>
-      <c r="I64" s="17" t="n">
+      <c r="I64" s="31" t="n">
         <v>56000</v>
       </c>
-      <c r="J64" s="17" t="n">
-        <v>56000</v>
-      </c>
-      <c r="K64" s="17" t="n">
-        <v>56000</v>
-      </c>
-      <c r="L64" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N64" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J64" s="31" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K64" s="31" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L64" s="23" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M64" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N64" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -5978,22 +7566,22 @@
       </c>
     </row>
     <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="14" t="n">
+      <c r="A70" s="28" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>2.06.60.080.TPE.00.000</t>
         </is>
       </c>
-      <c r="C70" s="16" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>Kẹp cố định đầu ray
 Loại: CH2260
 Size: 80x51x3mm</t>
         </is>
       </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>Kẹp cố định đầu ray
 Loại: CH2260
@@ -6002,42 +7590,42 @@
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="E70" s="15" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>ITS/ Đài Loan</t>
         </is>
       </c>
-      <c r="F70" s="14" t="inlineStr">
+      <c r="F70" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G70" s="17" t="n">
+      <c r="G70" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H70" s="17" t="n">
+      <c r="H70" s="31" t="n">
         <v>2254000</v>
       </c>
-      <c r="I70" s="17" t="n">
+      <c r="I70" s="31" t="n">
         <v>4508000</v>
       </c>
-      <c r="J70" s="17" t="n">
-        <v>2254000</v>
-      </c>
-      <c r="K70" s="17" t="n">
-        <v>4508000</v>
-      </c>
-      <c r="L70" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N70" s="16" t="inlineStr">
-        <is>
-          <t>2.06.60.080.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J70" s="31" t="n">
+        <v>578078</v>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>1156156</v>
+      </c>
+      <c r="L70" s="23" t="n">
+        <v>3351844</v>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N70" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -6104,22 +7692,22 @@
       </c>
     </row>
     <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="14" t="n">
+      <c r="A72" s="28" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="15" t="inlineStr">
+      <c r="B72" s="29" t="inlineStr">
         <is>
           <t>3.15.44.076.CHN.00.000</t>
         </is>
       </c>
-      <c r="C72" s="16" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>Cáp điện dẹt cho cầu trục
 Quy cách: 16mm2 x 4C
 Ruột mềm</t>
         </is>
       </c>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>Cáp điện dẹt cho cầu trục
 Quy cách: 16mm2 x 4C
@@ -6129,299 +7717,299 @@
 NSX: Imatek</t>
         </is>
       </c>
-      <c r="E72" s="15" t="inlineStr">
+      <c r="E72" s="29" t="inlineStr">
         <is>
           <t>Imatek/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F72" s="14" t="inlineStr">
+      <c r="F72" s="28" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G72" s="17" t="n">
+      <c r="G72" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="H72" s="17" t="n">
+      <c r="H72" s="31" t="n">
         <v>711000</v>
       </c>
-      <c r="I72" s="17" t="n">
+      <c r="I72" s="31" t="n">
         <v>35550000</v>
       </c>
-      <c r="J72" s="17" t="n">
-        <v>711000</v>
-      </c>
-      <c r="K72" s="17" t="n">
-        <v>35550000</v>
-      </c>
-      <c r="L72" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N72" s="16" t="inlineStr">
-        <is>
-          <t>3.15.44.076.CHN.00.000 | Sửa chữa Tời điện 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J72" s="31" t="n">
+        <v>76000</v>
+      </c>
+      <c r="K72" s="31" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="L72" s="23" t="n">
+        <v>31750000</v>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N72" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="14" t="n">
+      <c r="A73" s="28" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="15" t="inlineStr">
+      <c r="B73" s="29" t="inlineStr">
         <is>
           <t>3.20.22.003.TPE.00.000</t>
         </is>
       </c>
-      <c r="C73" s="16" t="inlineStr">
+      <c r="C73" s="30" t="inlineStr">
         <is>
           <t>Khóa cáp 
 Dùng cho cáp: 3mm</t>
         </is>
       </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="D73" s="30" t="inlineStr">
         <is>
           <t>Khóa cáp 
 Dùng cho cáp: 3mm</t>
         </is>
       </c>
-      <c r="E73" s="15" t="inlineStr">
+      <c r="E73" s="29" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F73" s="14" t="inlineStr">
+      <c r="F73" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G73" s="17" t="n">
+      <c r="G73" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="H73" s="17" t="n">
+      <c r="H73" s="31" t="n">
         <v>20000</v>
       </c>
-      <c r="I73" s="17" t="n">
+      <c r="I73" s="31" t="n">
         <v>1100000</v>
       </c>
-      <c r="J73" s="17" t="n">
-        <v>20000</v>
-      </c>
-      <c r="K73" s="17" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="L73" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N73" s="16" t="inlineStr">
-        <is>
-          <t>3.20.22.003.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J73" s="31" t="n">
+        <v>14000</v>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>770000</v>
+      </c>
+      <c r="L73" s="23" t="n">
+        <v>330000</v>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N73" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="14" t="n">
+      <c r="A74" s="28" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="15" t="inlineStr">
+      <c r="B74" s="29" t="inlineStr">
         <is>
           <t>3.34.20.130.CHN.99.000</t>
         </is>
       </c>
-      <c r="C74" s="16" t="inlineStr">
+      <c r="C74" s="30" t="inlineStr">
         <is>
           <t>Pendant control station (Tay bấm điều khiển tời điện): 
 - Type: XAC-A6713</t>
         </is>
       </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="D74" s="30" t="inlineStr">
         <is>
           <t>Pendant control station (Tay bấm điều khiển tời điện): 
 - Type: XAC-A6713
 Control station composition: 06, push buttons + 01 emergency stop</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr">
+      <c r="E74" s="29" t="inlineStr">
         <is>
           <t>Schnerder/ Czech Republic</t>
         </is>
       </c>
-      <c r="F74" s="14" t="inlineStr">
+      <c r="F74" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G74" s="17" t="n">
+      <c r="G74" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="17" t="n">
+      <c r="H74" s="31" t="n">
         <v>7406000</v>
       </c>
-      <c r="I74" s="17" t="n">
+      <c r="I74" s="31" t="n">
         <v>7406000</v>
       </c>
-      <c r="J74" s="17" t="n">
-        <v>7406000</v>
-      </c>
-      <c r="K74" s="17" t="n">
-        <v>7406000</v>
-      </c>
-      <c r="L74" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N74" s="16" t="inlineStr">
-        <is>
-          <t>3.34.20.130.CHN.99.000 | Sửa chữa Tời điện Tời điện 3 tấn máy nén khí turbine theo BBKT 624/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="J74" s="31" t="n">
+        <v>3310185</v>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>3310185</v>
+      </c>
+      <c r="L74" s="23" t="n">
+        <v>4095815</v>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N74" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="14" t="n">
+      <c r="A75" s="28" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="15" t="inlineStr">
+      <c r="B75" s="29" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C75" s="16" t="inlineStr">
+      <c r="C75" s="30" t="inlineStr">
         <is>
           <t>Lưỡi gà móc cẩu 7 tấn</t>
         </is>
       </c>
-      <c r="D75" s="16" t="inlineStr">
+      <c r="D75" s="30" t="inlineStr">
         <is>
           <t>Lưỡi gà móc cẩu 7 tấn:
  + Kích thước: 60 x 175x 3mm
  + Vật liệu: thép</t>
         </is>
       </c>
-      <c r="E75" s="15" t="inlineStr">
+      <c r="E75" s="29" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F75" s="14" t="inlineStr">
+      <c r="F75" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G75" s="17" t="n">
+      <c r="G75" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="17" t="n">
+      <c r="H75" s="31" t="n">
         <v>656000</v>
       </c>
-      <c r="I75" s="17" t="n">
+      <c r="I75" s="31" t="n">
         <v>656000</v>
       </c>
-      <c r="J75" s="17" t="n">
-        <v>656000</v>
-      </c>
-      <c r="K75" s="17" t="n">
-        <v>656000</v>
-      </c>
-      <c r="L75" s="17" t="n">
+      <c r="J75" s="31" t="n">
+        <v>585000</v>
+      </c>
+      <c r="K75" s="31" t="n">
+        <v>585000</v>
+      </c>
+      <c r="L75" s="23" t="n">
+        <v>71000</v>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N75" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="28" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>Sơn dầu Jotun chống sét Green 437</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>Sơn dầu Jotun chống sét Green 437</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F76" s="28" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="G76" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="H76" s="31" t="n">
+        <v>625000</v>
+      </c>
+      <c r="I76" s="31" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="J76" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="M75" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N75" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa tời điên Cầu trục 7 tấn lưới quay rác trạm bơm tuần hoàn theo BBKT 432/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="14" t="n">
-        <v>72</v>
-      </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C76" s="16" t="inlineStr">
-        <is>
-          <t>Sơn dầu Jotun chống sét Green 437</t>
-        </is>
-      </c>
-      <c r="D76" s="16" t="inlineStr">
-        <is>
-          <t>Sơn dầu Jotun chống sét Green 437</t>
-        </is>
-      </c>
-      <c r="E76" s="15" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F76" s="14" t="inlineStr">
-        <is>
-          <t>Lít</t>
-        </is>
-      </c>
-      <c r="G76" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="H76" s="17" t="n">
-        <v>625000</v>
-      </c>
-      <c r="I76" s="17" t="n">
+      <c r="K76" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="23" t="n">
         <v>12500000</v>
       </c>
-      <c r="J76" s="17" t="n">
-        <v>625000</v>
-      </c>
-      <c r="K76" s="17" t="n">
-        <v>12500000</v>
-      </c>
-      <c r="L76" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N76" s="16" t="inlineStr">
-        <is>
-          <t>Chưa có mã | Sửa chữa tời điên Cầu trục 7 tấn lưới quay rác trạm bơm tuần hoàn theo BBKT 432/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N76" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="14" t="n">
+      <c r="A77" s="28" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="15" t="inlineStr">
+      <c r="B77" s="29" t="inlineStr">
         <is>
           <t>3.82.63.103.LTU.00.000</t>
         </is>
       </c>
-      <c r="C77" s="16" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>Đế gắn module IO HBS 01 - FPN</t>
         </is>
       </c>
-      <c r="D77" s="16" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>Đế gắn module IO:
 - Hãng: ABB
@@ -6429,60 +8017,60 @@
 - PR (Product Revision): M</t>
         </is>
       </c>
-      <c r="E77" s="15" t="inlineStr">
+      <c r="E77" s="29" t="inlineStr">
         <is>
           <t>ABB/ Lithuania</t>
         </is>
       </c>
-      <c r="F77" s="14" t="inlineStr">
+      <c r="F77" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G77" s="17" t="n">
+      <c r="G77" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="H77" s="17" t="n">
+      <c r="H77" s="31" t="n">
         <v>21120000</v>
       </c>
-      <c r="I77" s="17" t="n">
+      <c r="I77" s="31" t="n">
         <v>633600000</v>
       </c>
-      <c r="J77" s="17" t="n">
-        <v>21120000</v>
-      </c>
-      <c r="K77" s="17" t="n">
-        <v>633600000</v>
-      </c>
-      <c r="L77" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N77" s="16" t="inlineStr">
-        <is>
-          <t>3.82.63.103.LTU.00.000 | Dự phòng thay thế cho các đế module IO hệ thống DCS ABB tổ máy S1, S2, S3 và COM suy giảm điện dung  | Vật tư không có trong KHSXKD 2026</t>
+      <c r="J77" s="31" t="n">
+        <v>19360000</v>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>580800000</v>
+      </c>
+      <c r="L77" s="23" t="n">
+        <v>52800000</v>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N77" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="14" t="n">
+      <c r="A78" s="28" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="15" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>3.94.00.808.MLT.00.000</t>
         </is>
       </c>
-      <c r="C78" s="16" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>Đế gắn module IO HBS01-FPH</t>
         </is>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>Đế gắn module IO:
 - Hãng: ABB
@@ -6490,42 +8078,42 @@
 - PR (Product Revision): M</t>
         </is>
       </c>
-      <c r="E78" s="15" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>ABB/ Lithuania</t>
         </is>
       </c>
-      <c r="F78" s="14" t="inlineStr">
+      <c r="F78" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G78" s="17" t="n">
+      <c r="G78" s="31" t="n">
         <v>26</v>
       </c>
-      <c r="H78" s="17" t="n">
+      <c r="H78" s="31" t="n">
         <v>21120000</v>
       </c>
-      <c r="I78" s="17" t="n">
+      <c r="I78" s="31" t="n">
         <v>549120000</v>
       </c>
-      <c r="J78" s="17" t="n">
-        <v>21120000</v>
-      </c>
-      <c r="K78" s="17" t="n">
+      <c r="J78" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="23" t="n">
         <v>549120000</v>
       </c>
-      <c r="L78" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N78" s="16" t="inlineStr">
-        <is>
-          <t>3.94.00.808.MLT.00.000 | Dự phòng thay thế cho các đế module IO hệ thống DCS ABB tổ máy S1, S2, S3 và COM suy giảm điện dung | Vật tư không có trong KHSXKD 2026</t>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N78" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
@@ -6571,10 +8159,10 @@
         <v>183500000</v>
       </c>
       <c r="J79" s="17" t="n">
-        <v>21120000</v>
+        <v>18350000</v>
       </c>
       <c r="K79" s="17" t="n">
-        <v>211200000</v>
+        <v>183500000</v>
       </c>
       <c r="L79" s="17" t="n">
         <v>0</v>
@@ -7005,13 +8593,13 @@
         <v>5236608000</v>
       </c>
       <c r="J86" s="31" t="n">
-        <v>1300000</v>
+        <v>1845000000</v>
       </c>
       <c r="K86" s="31" t="n">
-        <v>2600000</v>
+        <v>3690000000</v>
       </c>
       <c r="L86" s="23" t="n">
-        <v>5234008000</v>
+        <v>1546608000</v>
       </c>
       <c r="M86" s="32" t="inlineStr">
         <is>
@@ -8821,10 +10409,10 @@
       </c>
       <c r="J117" s="35" t="n"/>
       <c r="K117" s="36" t="n">
-        <v>32385281416.5</v>
+        <v>34779577092.5</v>
       </c>
       <c r="L117" s="37" t="n">
-        <v>5937874583.5</v>
+        <v>3425998907.5</v>
       </c>
       <c r="M117" s="35" t="n"/>
       <c r="N117" s="35" t="n"/>
@@ -8845,10 +10433,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N102" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N102" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8860,7 +10474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8976,12 +10590,12 @@
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (13,559,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 1). Ngoài ra còn có: CÔNG TY CỔ PHẦN CÔNG NGHỆ CƠ ĐIỆN EME báo giá 15,592,850 đ (+15.0%)</t>
+          <t xml:space="preserve">Đơn giá trình (13,559,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 1). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 16,000,000 </t>
         </is>
       </c>
       <c r="G5" s="40" t="inlineStr">
         <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 6.015.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 115/2023. Ttr 2562/KHVT) theo hóa đơn số 00000041. 42. 43. 44. 45. 46 ngày 30.08.2024 ngày 2024-10-31. SL: 117 Cái); Các đợt nhập khác: 17.670.00</t>
+          <t>Vật tư có 2 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 11.842.500 đ/Cái (dao động từ 6.015.000 đ đến 17.670.000 đ). Đơn giá trình đợt này là 13.559.000 đ/Cái (+14.5% s</t>
         </is>
       </c>
       <c r="H5" s="40" t="inlineStr">
@@ -8997,8 +10611,9 @@
       <c r="J5" s="40" t="inlineStr"/>
       <c r="K5" s="41" t="inlineStr">
         <is>
-          <t>Đơn giá chốt: 6.015.000 đ
-(Tiết kiệm: 30.176.000 đ)</t>
+          <t>Đơn giá chốt: 11.842.500 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 6.866.000 đ)</t>
         </is>
       </c>
     </row>
@@ -9047,6 +10662,7 @@
       <c r="K6" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 7.000.000 đ
+(Cơ sở 2: Lịch sử mua sắm ERP Vĩnh Tân 4 (QĐ 161))
 (Tiết kiệm: 7.208.000 đ)</t>
         </is>
       </c>
@@ -9107,6 +10723,7 @@
       <c r="K7" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 16.491.600 đ
+(Cơ sở 5: Tham khảo TMĐT / Giá Web (Landed Cost DDP VT4))
 (Tiết kiệm: 197.542.000 đ)</t>
         </is>
       </c>
@@ -9168,6 +10785,7 @@
       <c r="K8" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 9.009.300 đ
+(Cơ sở 5: Tham khảo TMĐT / Giá Web)
 (Tiết kiệm: 274.953.500 đ)</t>
         </is>
       </c>
@@ -9225,6 +10843,7 @@
       <c r="K9" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 1.500.000 đ
+(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 0 đ)</t>
         </is>
       </c>
@@ -9282,6 +10901,7 @@
       <c r="K10" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 8.910.000 đ
+(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 52.340.000 đ)</t>
         </is>
       </c>
@@ -9333,7 +10953,7 @@
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
-          <t>Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [KMX], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CS</t>
+          <t>Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khó</t>
         </is>
       </c>
       <c r="J11" s="40" t="inlineStr">
@@ -9344,6 +10964,7 @@
       <c r="K11" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 452.147.000 đ
+(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 0 đ)</t>
         </is>
       </c>
@@ -9409,6 +11030,7 @@
       <c r="K12" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 620.000 đ
+(Cơ sở 2: Lịch sử mua sắm ERP Vĩnh Tân 4 (HĐ 03/2022))
 (Tiết kiệm: 3.840.000 đ)</t>
         </is>
       </c>
@@ -9470,6 +11092,7 @@
       <c r="K13" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 1.315.000 đ
+(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 0 đ)</t>
         </is>
       </c>
@@ -9531,6 +11154,7 @@
       <c r="K14" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 1.508.000 đ
+(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 0 đ)</t>
         </is>
       </c>
@@ -9600,6 +11224,7 @@
       <c r="K15" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 113.232.916 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
 (Tiết kiệm: 4.367.084 đ)</t>
         </is>
       </c>
@@ -9610,13 +11235,15 @@
       </c>
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t>2.46.35.037.CHN.00.000</t>
+          <t>Chưa có mã vật tư</t>
         </is>
       </c>
       <c r="C16" s="40" t="inlineStr">
         <is>
-          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m
-(Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m)</t>
+          <t>Thanh cái đồng V phân phối mạ bạc
+(Thanh cái đồng V phân phối mạ bạc
+Kích thước: 28x40x6mm
+Chiều dài: 920mm)</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -9631,33 +11258,34 @@
       </c>
       <c r="F16" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (19,300,000 đ) không trùng với báo giá nào. Trong đó đơn giá thấp nhất thu thập được là 18,522,000 đ của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf).</t>
+          <t>Đơn giá trình (48,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 3). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 50,200,000 đ (+4.6%)</t>
         </is>
       </c>
       <c r="G16" s="40" t="inlineStr">
         <is>
-          <t>Vật tư có 2 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 21.200.000 đ/Cái (dao động từ 17.500.000 đ đến 24.900.000 đ). Đơn giá trình đợt này là 19.300.000 đ/Cái (-9.0% s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [28x40x6], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện tron</t>
         </is>
       </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
-          <t>Đã tra cứu từ khóa [SS-T6-S-065-20] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 17:27 ngày 08/09/2026; ghi nhận mức giá trúng thầu tham chiếu là 27.390.000 đ (Mã TBMT: IB2400452305, Bên mời thầu: NHÀ MÁY NHIỆ</t>
+          <t>Đã tra cứu từ khóa [Thanh cái đồng V phân phối mạ bạc] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:20 ngày 09/09/2026 nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
         </is>
       </c>
       <c r="J16" s="40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Đã tra cứu từ khóa [Thanh cái đồng V phân phối mạ bạc] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không n</t>
         </is>
       </c>
       <c r="K16" s="41" t="inlineStr">
         <is>
-          <t>Đơn giá chốt: 18.522.000 đ
-(Tiết kiệm: 27.230.000 đ)</t>
+          <t>Đơn giá chốt: 1.390.909 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 186.436.364 đ)</t>
         </is>
       </c>
     </row>
@@ -9667,14 +11295,13 @@
       </c>
       <c r="B17" s="39" t="inlineStr">
         <is>
-          <t>3.96.13.320.USA.00.000</t>
+          <t>2.46.35.037.CHN.00.000</t>
         </is>
       </c>
       <c r="C17" s="40" t="inlineStr">
         <is>
-          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
-(Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
-NSX: MERRICK)</t>
+          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m
+(Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m)</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -9689,33 +11316,34 @@
       </c>
       <c r="F17" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (56,105,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 4). Ngoài ra còn có: CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN H</t>
+          <t>Đơn giá trình (19,300,000 đ) không trùng với báo giá nào. Trong đó đơn giá thấp nhất thu thập được là 18,522,000 đ của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf).</t>
         </is>
       </c>
       <c r="G17" s="40" t="inlineStr">
         <is>
+          <t>Vật tư có 2 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 21.200.000 đ/Cái (dao động từ 17.500.000 đ đến 24.900.000 đ). Đơn giá trình đợt này là 19.300.000 đ/Cái (-9.0% s</t>
+        </is>
+      </c>
+      <c r="H17" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [SS-T6-S-065-20], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát đi</t>
+        </is>
+      </c>
+      <c r="I17" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [SS-T6-S-065-20] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 17:27 ngày 08/09/2026; ghi nhận mức giá trúng thầu tham chiếu là 27.390.000 đ (Mã TBMT: IB2400452305, Bên mời thầu: NHÀ MÁY NHIỆ</t>
+        </is>
+      </c>
+      <c r="J17" s="40" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K17" s="41" t="inlineStr">
         <is>
-          <t>Đơn giá chốt: 23.000.000 đ
-(Tiết kiệm: 66.210.000 đ)</t>
+          <t>Đơn giá chốt: 18.522.000 đ
+(Cơ sở 1: Báo giá nộp kèm)
+(Tiết kiệm: 27.230.000 đ)</t>
         </is>
       </c>
     </row>
@@ -9725,10 +11353,1448 @@
       </c>
       <c r="B18" s="39" t="inlineStr">
         <is>
+          <t>2.46.35.019.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="inlineStr">
+        <is>
+          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m
+(Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m)</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (19,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có 2 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 12.350.000 đ/Cái (dao động từ 5.400.000 đ đến 19.300.000 đ). Đơn giá trình đợt này là 19.000.000 đ/Cái (+53.8% s</t>
+        </is>
+      </c>
+      <c r="H18" s="40" t="inlineStr"/>
+      <c r="I18" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [SS-T8-S-065-20] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:43 ngày 09/09/2026; ghi nhận mức giá trúng thầu tham chiếu là 21.230.000 đ (Mã TBMT: IB2400452305, Bên mời thầu: NHÀ MÁY NHIỆ</t>
+        </is>
+      </c>
+      <c r="J18" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [SS-T8-S-065-20] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thư</t>
+        </is>
+      </c>
+      <c r="K18" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 12.350.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 13.300.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>4.82.22.013.USA.00.000</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6
+(Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6)</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E19" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (1,700,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 2,150,000 đ (+26.</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:03/2022) theo hóa đơn số 00000017 ngày 04.03.2022 (ngày ký 2022-03-07 00:00:00, do Nhập kho vật tư (HĐ:03/2022) theo hóa đơn số 00000017 ngày 04.</t>
+        </is>
+      </c>
+      <c r="H19" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [SS-810-6], vật tư có lịch sử mua sắm tương đương tại Công ty Dịch vụ sửa chữa các nhà máy điện EVNGENCO3 (t</t>
+        </is>
+      </c>
+      <c r="I19" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [SS-810-6] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:46 ngày 09/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 1.319.000 đ (Mã TBMT: IB2600209753, Bên mời thầu: CÔNG TY N</t>
+        </is>
+      </c>
+      <c r="J19" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các t</t>
+        </is>
+      </c>
+      <c r="K19" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 1.319.000 đ
+(Cơ sở 4: Mua Sắm Công e-GP)
+(Tiết kiệm: 762.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="110" customHeight="1">
+      <c r="A20" s="38" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>4.82.22.025.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="inlineStr">
+        <is>
+          <t>Đầu nối - Union Swagelok Model: SS-600-6
+(Đầu nối - Union Swagelok Model: SS-600-6)</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr"/>
+      <c r="E20" s="42" t="inlineStr">
+        <is>
+          <t>Mở liên kết trực tuyến ↗</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (2,600,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LO</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có lịch sử nhập kho theo Nhập kho vật tư (HĐ: 25/2025) theo hóa đơn số 00000091 ngày 24.06.2025 (ngày ký 2025-07-24 00:00:00) với đơn giá 2.600.000 đ/Cái (Tổng số 6 đợt mua sắm lịch sử có đơn giá dao động từ 630.0</t>
+        </is>
+      </c>
+      <c r="H20" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [SS-600-6], vật tư có lịch sử mua sắm tương đương tại GENCO1 - Công ty Nhiệt Điện Nghi Sơn (thời gian N/A) v</t>
+        </is>
+      </c>
+      <c r="I20" s="40" t="inlineStr"/>
+      <c r="J20" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Đầu nối - Union Swagelok Model: SS-600-6 - Đầu nối - Union Swagelok Model: SS-600-6] trên thị trường Thương mại điện tử / Website nhà cung cấp (Ảnh chụp màn hình web) tại đường link [https://www.ebay.</t>
+        </is>
+      </c>
+      <c r="K20" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 644.760 đ
+(Cơ sở 3: EVN IMIS)
+(Tiết kiệm: 195.524.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="38" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>5.33.70.184.GER.99.000</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001
+(Bộ điều khiển định vị Positioner:
+- Model: TZIDC-V18345- 2020521001
+-Type: Double acting 
+-Sofw.Rev: 3 
+-Supply press: 1,4 ~ 6 bar 
+-Input: Analog 4 ~ 20 mA
+ -Loss of electric: Fail freeze
+- Option: Analog feedback, FSK, Position indicator 
+-NSX: ABB)</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E21" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (85,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có lịch sử nhập kho gần nhất tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:37/2026) hóa đơn số 00000035 ngày 28.05.2026 (ngày ký 2026-06-03 00:00:00, do Nhập kho vật tư (HĐ:37/2026) hóa đơn số 00000035 ngày 28.05.2</t>
+        </is>
+      </c>
+      <c r="H21" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [TZIDC], vật tư có lịch sử mua sắm tương đương tại Công ty Nhiệt điện Cần Thơ (thời gian N/A) với đơn giá 83</t>
+        </is>
+      </c>
+      <c r="I21" s="40" t="inlineStr"/>
+      <c r="J21" s="40" t="inlineStr"/>
+      <c r="K21" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 83.484.000 đ
+(Cơ sở 3: EVN IMIS)
+(Tiết kiệm: 7.580.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>3.96.13.144.USA.00.000</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="inlineStr">
+        <is>
+          <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire
+(Cảm biến nhiệt độ - Model: S14405PD3S350B0
+- NSX: MINCO 
+- Element: Platinum 
+- Element length: 6.4 mm 
+- Cable dimension "C": 1778 mm 
+- Cable dimension "L": 8890 mm 
+- Single duplex: Duplex 
+- Sheath: 2.9 mm OD 
+- Type: RTD PT100, 3 Wire 
+- Range: 0 - 260 °C)</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E22" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (30,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 5). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có lịch sử nhập kho gần nhất tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:36/2026) theo hóa đơn số 00000842 ngày 15.06.2026 (ngày ký 2026-07-22 00:00:00, do Nhập kho vật tư (HĐ:36/2026) theo hóa đơn số 00000842 ng</t>
+        </is>
+      </c>
+      <c r="H22" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [RTD PT100], vật tư có lịch sử mua sắm tương đương tại Công ty Cổ phần Thủy điện Thác Mơ (thời gian N/A) </t>
+        </is>
+      </c>
+      <c r="I22" s="40" t="inlineStr"/>
+      <c r="J22" s="40" t="inlineStr"/>
+      <c r="K22" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 27.923.445 đ
+(Cơ sở 4: Mua Sắm Công e-GP)
+(Tiết kiệm: 2.076.555 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="110" customHeight="1">
+      <c r="A23" s="38" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C18" s="40" t="inlineStr">
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm)
+(LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
+Model: LST400 Y0/S15/N1/P6/A1/H1/SC6/B2/CR/M5
+Range: 0.5m to 15m Signal: 4 - 20 mA 
+Supply power: 115 to 230 V AC or 24 V DC.
+NSX: ABB)</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr"/>
+      <c r="E23" s="42" t="inlineStr">
+        <is>
+          <t>Mở liên kết trực tuyến ↗</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (189,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 5). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG </t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:233) theo hóa đơn số 0000216 ngày 30.03.2021 (ngày ký 2021-04-28 00:00:00, do Nhập kho vật tư (HĐ:233) theo hóa đơn số 0000216 ngày 30.03.2021 cu</t>
+        </is>
+      </c>
+      <c r="H23" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [LST400], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong</t>
+        </is>
+      </c>
+      <c r="I23" s="40" t="inlineStr"/>
+      <c r="J23" s="40" t="inlineStr"/>
+      <c r="K23" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 58.423.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 130.577.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="110" customHeight="1">
+      <c r="A24" s="38" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="inlineStr">
+        <is>
+          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
+(Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
+Model: MA3145-230-2-R
+- Điện áp hoạt động tối đa (Max working voltage): ≥ 270 VAC.
+- Điện áp định mức (Voltage rating): 230 VAC.
+- Dòng cắt sét / Khả năng chịu dòng ngắn mạch (Circuit breaker / Surge capacity): ≥ 40 kA.
+NSX: Cooper Crouse-Hinds MTL / Eaton)</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr"/>
+      <c r="E24" s="42" t="inlineStr">
+        <is>
+          <t>Mở liên kết trực tuyến ↗</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (35,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 7). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4, các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn g</t>
+        </is>
+      </c>
+      <c r="H24" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [MA3145], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong</t>
+        </is>
+      </c>
+      <c r="I24" s="40" t="inlineStr">
+        <is>
+          <t>Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [MTL], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CS</t>
+        </is>
+      </c>
+      <c r="J24" s="40" t="inlineStr"/>
+      <c r="K24" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 21.609.600 đ
+(Cơ sở 5: Tham khảo TMĐT / Giá Web)
+(Tiết kiệm: 40.171.200 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="38" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t>3.34.40.009.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>Công tắc lưu lượng (Flow Switch)
+(Công tắc lưu lượng (Flow Switch)
+Model: WP/FS-25VFL
+Switch : SPDT Snap Acting Micro
+Rating : 5A 250VAC 
+NSX: Dag Process Instruments Pvt. Ltd)</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E25" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (38,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 8). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 32.500.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 12/2025) theo hóa đơn số 00000036 ngày 24.03.2025 ngày 2025-03-27. SL: 1 Cái)</t>
+        </is>
+      </c>
+      <c r="H25" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu CSDL EVN IMIS theo từ khóa [Công tắc lưu lượng], các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán nên thẩm định viên không áp dụng làm căn cứ thẩm định.</t>
+        </is>
+      </c>
+      <c r="I25" s="40" t="inlineStr"/>
+      <c r="J25" s="40" t="inlineStr"/>
+      <c r="K25" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 32.500.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 5.500.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="110" customHeight="1">
+      <c r="A26" s="38" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>3.96.13.165.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor
+(Cảm biến tiệm cận/proximity sensor
+- Model: PR30-10AC
+Đường kính cạnh phát hiện: 30mm
+- Điện áp hoạt động: 100-240 Vac
+- Ngõ ra điều khiển: NC
+- Protection: IP67)</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr"/>
+      <c r="E26" s="42" t="inlineStr">
+        <is>
+          <t>Mở liên kết trực tuyến ↗</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (1,219,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 6). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 2,000,000 đ (+64.1%).</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 598.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:123/2022) theo hóa đơn số 993. 994 ngày 26.12.2022 ngày 2022-12-27. SL: 1 Cái)</t>
+        </is>
+      </c>
+      <c r="H26" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 10/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [PR30], vật tư có lịch sử mua sắm tương đương tại Công ty Nhiệt điện Mông Dương (thời gian N/A) với đơn giá </t>
+        </is>
+      </c>
+      <c r="I26" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Autonics] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 08:23 ngày 10/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 382.320 đ (Mã TBMT: IB2600205775, Bên mời thầu: CÔNG TY THỦ</t>
+        </is>
+      </c>
+      <c r="J26" s="40" t="inlineStr"/>
+      <c r="K26" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 911.127 đ
+(Cơ sở 3: EVN IMIS)
+(Tiết kiệm: 615.746 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="110" customHeight="1">
+      <c r="A27" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="39" t="inlineStr">
+        <is>
+          <t>3.96.13.114.KOR.99.000</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor
+(Cảm biến tiệm cận/proximity sensor
+- Model: PR18-8AO
+- Đường kính đầu dò: 18mm
+- Điện áp hoạt động: 100-240 Vac
+- Ngõ ra điều khiển: NO
+- Protection: IP67)</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr"/>
+      <c r="E27" s="42" t="inlineStr">
+        <is>
+          <t>Mở liên kết trực tuyến ↗</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (1,150,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 1,600,000 đ (+39.1%).</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có 3 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 598.667 đ/Cái (dao động từ 528.000 đ đến 740.000 đ). Đơn giá trình đợt này là 1.150.000 đ/Cái (+92.1% so với đơn</t>
+        </is>
+      </c>
+      <c r="H27" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 10/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [PR18], vật tư có lịch sử mua sắm tương đương tại Công ty TNHH MTV Thủy điện Trung Sơn (thời gian N/A) với đ</t>
+        </is>
+      </c>
+      <c r="I27" s="40" t="inlineStr"/>
+      <c r="J27" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Cảm biến tiệm cận/proximity sensor - Cảm biến tiệm cận/proximity sensor - Model: PR18-8AO - Đường kính đầu dò: 18mm - Điện áp hoạt động: 100-240 Vac - Ngõ ra điều khiển: NO - Protection: IP67] trên th</t>
+        </is>
+      </c>
+      <c r="K27" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 577.200 đ
+(Cơ sở 5: Tham khảo TMĐT / Giá Web)
+(Tiết kiệm: 572.800 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="110" customHeight="1">
+      <c r="A28" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>3.34.20.134.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A12713
+(Pendant control station:
+Type: XAC-A12713)</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr"/>
+      <c r="E28" s="42" t="inlineStr">
+        <is>
+          <t>Mở liên kết trực tuyến ↗</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (5,784,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 6,000,000 đ (+3.7%). </t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 2.369.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:132/2023) theo hóa đơn số 00000011 ngày 22.01.2024 ngày 2024-02-27. SL: 6 Cái)</t>
+        </is>
+      </c>
+      <c r="H28" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu CSDL EVN IMIS theo từ khóa [XAC-A12713], các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán nên thẩm định viên không áp dụng làm căn cứ thẩm định.</t>
+        </is>
+      </c>
+      <c r="I28" s="40" t="inlineStr"/>
+      <c r="J28" s="40" t="inlineStr"/>
+      <c r="K28" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 420.000 đ
+(Cơ sở 5: Tham khảo TMĐT / Giá Web)
+(Tiết kiệm: 5.364.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="38" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="39" t="inlineStr">
+        <is>
+          <t>4.90.80.030.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)
+(Joint cover (bao che giữa các khớp nối đường ray cáp điện):
+- Material: PVC
+- Maker: Eunchang T&amp;C)</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E29" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (66,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 82,000 đ (+24.2%). Đơn g</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 26.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:116/2022) theo hóa đơn số 00000008 ngày 27.02.2023 ngày 2023-02-27. SL: 300 Cái); Các đợt nhập khác: 24.800 đ, 80.000 đ</t>
+        </is>
+      </c>
+      <c r="H29" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Bao che giữa các], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I29" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Bao che giữa các khớp nối đường ray cáp điện (Joint cover)] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+        </is>
+      </c>
+      <c r="J29" s="40" t="inlineStr"/>
+      <c r="K29" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 26.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 9.400.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="38" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>4.90.80.027.KOR.00.000</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>Nắp che phía cuối đường ray cáp điện (End cap)
+(Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
+- Maker: Eunchang T&amp;C)</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (68,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 76,000 đ (+11.8%). Đơn g</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 21.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:116/2022) theo hóa đơn số 00000008 ngày 27.02.2023 ngày 2023-02-27. SL: 32 Cái); Các đợt nhập khác: 18.000 đ, 710.000 đ</t>
+        </is>
+      </c>
+      <c r="H30" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Nắp che phía cuối], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I30" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Nắp che phía cuối đường ray cáp điện (End cap)] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+        </is>
+      </c>
+      <c r="J30" s="40" t="inlineStr"/>
+      <c r="K30" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 21.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 1.504.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="38" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="39" t="inlineStr">
+        <is>
+          <t>2.08.37.001.KOR.97.000</t>
+        </is>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>Trolley-bar (thanh ray cấp nguồn)
+(Trolley-bar (thanh ray cấp nguồn):
+- Iđm: 60A;
+- Uđm: 400VAC;
+- Length: 3m / cây
+- Material: Copper
+- Maker: EunchangT&amp;C)</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E31" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (909,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 1,020,000 đ (+12.2%). Đ</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:62/2023) theo hóa đơn số 00001202 ngày 12.09.2023 (ngày ký 2023-09-25 00:00:00, do Nhập kho vật tư (HĐ:62/2023) theo hóa đơn số 00001202 ngày 12.</t>
+        </is>
+      </c>
+      <c r="H31" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Trolley bar (thanh ray], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I31" s="40" t="inlineStr">
+        <is>
+          <t>Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [Trolley-bar], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp</t>
+        </is>
+      </c>
+      <c r="J31" s="40" t="inlineStr"/>
+      <c r="K31" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 890.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 532.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="38" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="39" t="inlineStr">
+        <is>
+          <t>3.34.20.133.CHN.99.000</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A6913
+(Pendant control station:
+Type: XAC-A6913
+Control station composition: 06 push buttons + 01 emergency stop
+Product compatibility: 
+ZB2BE102 for emergency stop, XEN-G1191 for each direction
+Color: Yellow)</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E32" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (13,319,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 14,670,000 đ (+10.1%</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="inlineStr"/>
+      <c r="H32" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 10/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [A6913], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong </t>
+        </is>
+      </c>
+      <c r="I32" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [XAC] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:08 ngày 10/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 3.290.400 đ (Mã TBMT: IB2600015122, Bên mời thầu: CHI NHÁNH TỔNG</t>
+        </is>
+      </c>
+      <c r="J32" s="40" t="inlineStr"/>
+      <c r="K32" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 3.290.400 đ
+(Cơ sở 4: Mua Sắm Công e-GP)
+(Tiết kiệm: 10.028.600 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="38" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 3 tấn
+(Lưỡi gà móc cẩu 3 tấn
+Kích thước: rộng 25mm x dài 60mm)</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E33" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (610,000 đ) không trùng với báo giá nào. Trong đó đơn giá thấp nhất thu thập được là 716,000 đ của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf).</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ: 57/2024) theo hóa đơn số 615 ngày 27.08.2024 (ngày ký 2024-09-06 00:00:00, do Nhập kho vật tư (HĐ: 57/2024) theo hóa đơn số 615 ngày 27.08.2024 </t>
+        </is>
+      </c>
+      <c r="H33" s="40" t="inlineStr"/>
+      <c r="I33" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Lưỡi gà móc cẩu] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:18 ngày 10/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 314.600 đ (Mã TBMT: IB2300214547, Bên mời thầu: CÔNG</t>
+        </is>
+      </c>
+      <c r="J33" s="40" t="inlineStr"/>
+      <c r="K33" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 314.600 đ
+(Cơ sở 4: Mua Sắm Công e-GP)
+(Tiết kiệm: 295.400 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="39" t="inlineStr">
+        <is>
+          <t>2.50.05.003.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="inlineStr">
+        <is>
+          <t>Cáp inox 304 
+Kích thước: Ø 3 mm
+(Cáp inox 304 
+Kích thước: Ø 3 mm)</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E34" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (37,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 41,000 đ (+10.8%). Đơn g</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 86.000 đ/Mét (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 90 Mét); Các đợt nhập khác: 67.000 đ, 12.000 đ</t>
+        </is>
+      </c>
+      <c r="H34" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Cáp inox 304 Kích], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I34" s="40" t="inlineStr">
+        <is>
+          <t>e-GP MSC: 10.000 đ/Cái (Kết quả trúng thầu)</t>
+        </is>
+      </c>
+      <c r="J34" s="40" t="inlineStr"/>
+      <c r="K34" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 24.000 đ
+(Cơ sở 4: Mua Sắm Công e-GP)
+(Tiết kiệm: 780.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="38" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>Phe cài trục ngoài cho đường kính 28mm
+(Phe cài trục ngoài cho đường kính 28mm.
+Vật liệu: Inox 304)</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E35" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (56,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 67,000 đ (+19.6%). Đơn g</t>
+        </is>
+      </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 50.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:43) theo hóa đơn số 0000015 ngày 21.06.2021 ngày 2021-06-26. SL: 201 Cái); Các đợt nhập khác: 48.400 đ, 371.800 đ</t>
+        </is>
+      </c>
+      <c r="H35" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu CSDL EVN IMIS theo từ khóa [Phe cài trục ngoài], các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán nên thẩm định viên không áp dụng làm căn cứ thẩm định.</t>
+        </is>
+      </c>
+      <c r="I35" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Phe cài trục ngoài cho đường kính 28mm] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+        </is>
+      </c>
+      <c r="J35" s="40" t="inlineStr"/>
+      <c r="K35" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 50.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 6.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>2.06.60.080.TPE.00.000</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="inlineStr">
+        <is>
+          <t>Kẹp cố định đầu ray
+Loại: CH2260
+Size: 80x51x3mm
+(Kẹp cố định đầu ray
+Loại: CH2260
+Size: 80x51x3mm
+Vật liệu: Inox 304
+Hãng: ITS Đài loan)</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E36" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (2,254,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 3,670,000 đ (+62.8%).</t>
+        </is>
+      </c>
+      <c r="G36" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lịch sử nhập kho ERP Vĩnh Tân 4 [Kẹp cố định đầu ray. Loại: CH2260. Size: 80x51x3mm. Vật liệu: Inox 304]: 3.574.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: </t>
+        </is>
+      </c>
+      <c r="H36" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [2.06.60.080.TPE.00.000], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I36" s="40" t="inlineStr">
+        <is>
+          <t>e-GP MSC: 578.078 đ/Cái (Kết quả trúng thầu)</t>
+        </is>
+      </c>
+      <c r="J36" s="40" t="inlineStr"/>
+      <c r="K36" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 578.078 đ
+(Cơ sở: Tự động/Rà soát nhanh)
+(Tiết kiệm: 3.351.844 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="39" t="inlineStr">
+        <is>
+          <t>3.15.44.076.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>Cáp điện dẹt cho cầu trục
+Quy cách: 16mm2 x 4C
+Ruột mềm
+(Cáp điện dẹt cho cầu trục
+Quy cách: 16mm2 x 4C
+Ruột mềm
+Điện áp: 450/750V
+Cách điện: PVC, dẻo
+NSX: Imatek)</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E37" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (711,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 780,000 đ (+9.7%). Đơn </t>
+        </is>
+      </c>
+      <c r="G37" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Cáp điện dẹt cho cầu trục. 16mm2 x 4C]: 1.091.000 đ/Mét (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 99 Mét); Các đợt nhập khác: 730.0</t>
+        </is>
+      </c>
+      <c r="H37" s="40" t="inlineStr">
+        <is>
+          <t>IMIS EVN: 76.000 đ/Cái (Trung tâm Dịch vụ sửa chữa EVN - Chi nhánh Tập đoàn Điện lực Việt Nam)</t>
+        </is>
+      </c>
+      <c r="I37" s="40" t="inlineStr">
+        <is>
+          <t>e-GP MSC: 125.000 đ/Cái (Kết quả trúng thầu)</t>
+        </is>
+      </c>
+      <c r="J37" s="40" t="inlineStr"/>
+      <c r="K37" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 76.000 đ
+(Cơ sở: Tự động/Rà soát nhanh)
+(Tiết kiệm: 31.750.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="38" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="39" t="inlineStr">
+        <is>
+          <t>3.20.22.003.TPE.00.000</t>
+        </is>
+      </c>
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>Khóa cáp 
+Dùng cho cáp: 3mm
+(Khóa cáp 
+Dùng cho cáp: 3mm)</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E38" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (20,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 31,000 đ (+55.0%). Đơn g</t>
+        </is>
+      </c>
+      <c r="G38" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Khóa cáp dùng cho cáp 3mm]: 14.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 108 Cái); Các đợt nhập khác: 38.000 đ, 14.000 đ</t>
+        </is>
+      </c>
+      <c r="H38" s="40" t="inlineStr">
+        <is>
+          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Khóa cáp Dùng cho], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
+        </is>
+      </c>
+      <c r="I38" s="40" t="inlineStr">
+        <is>
+          <t>e-GP MSC: 5.000 đ/Cái (Kết quả trúng thầu)</t>
+        </is>
+      </c>
+      <c r="J38" s="40" t="inlineStr"/>
+      <c r="K38" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 14.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 330.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="39" t="inlineStr">
+        <is>
+          <t>3.34.20.130.CHN.99.000</t>
+        </is>
+      </c>
+      <c r="C39" s="40" t="inlineStr">
+        <is>
+          <t>Pendant control station (Tay bấm điều khiển tời điện): 
+- Type: XAC-A6713
+(Pendant control station (Tay bấm điều khiển tời điện): 
+- Type: XAC-A6713
+Control station composition: 06, push buttons + 01 emergency stop)</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E39" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (7,406,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 9). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 8,000,000 đ (+8.0%). </t>
+        </is>
+      </c>
+      <c r="G39" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Pendant control station. Type: XACA6713]: 6.600.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 65/2024) theo hóa đơn số 00000031 ngày 18.09.2024 ngày 2024-10-09. SL: 10 Cái); Các đợt nhập khác: 1.71</t>
+        </is>
+      </c>
+      <c r="H39" s="40" t="inlineStr">
+        <is>
+          <t>IMIS EVN: 3.310.185 đ/Cái (Công ty Nhiệt điện Vĩnh Tân)</t>
+        </is>
+      </c>
+      <c r="I39" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu từ khóa [Pendant control station (Tay bấm điều khiển tời điện):] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+        </is>
+      </c>
+      <c r="J39" s="40" t="inlineStr"/>
+      <c r="K39" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 3.310.185 đ
+(Cơ sở 3: EVN IMIS)
+(Tiết kiệm: 4.095.815 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C40" s="40" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 7 tấn
+(Lưỡi gà móc cẩu 7 tấn:
+ + Kích thước: 60 x 175x 3mm
+ + Vật liệu: thép)</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E40" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (656,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 9). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 712,000 đ (+8.5%). Đơn </t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Lưỡi gà móc cẩu BCD10t. Kích thước (DxR): 120mmx41mm]: 585.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 57/2024) theo hóa đơn số 615 ngày 27.08.2024 ngày 2024-09-06. SL: 1 Cái); Các đợt nhập khác:</t>
+        </is>
+      </c>
+      <c r="H40" s="40" t="inlineStr">
+        <is>
+          <t>Đã tra cứu CSDL EVN IMIS theo từ khóa [Lưỡi gà móc cẩu], các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán nên thẩm định viên không áp dụng làm căn cứ thẩm định.</t>
+        </is>
+      </c>
+      <c r="I40" s="40" t="inlineStr"/>
+      <c r="J40" s="40" t="inlineStr"/>
+      <c r="K40" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 585.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 71.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C41" s="40" t="inlineStr">
+        <is>
+          <t>Sơn dầu Jotun chống sét Green 437
+(Sơn dầu Jotun chống sét Green 437)</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E41" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (625,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 9). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 710,000 đ (+13.6%). Đơn</t>
+        </is>
+      </c>
+      <c r="G41" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có lịch sử nhập kho theo Nhập kho vật tư tổng hợp theo (HĐ:78) theo hóa đơn số 0000043 ngày 11.09.2019 (ngày ký 2019-09-13 00:00:00) với đơn giá 675.000 đ/Cái (Tổng số 20 đợt mua sắm lịch sử có đơn giá dao động từ</t>
+        </is>
+      </c>
+      <c r="H41" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 0 đ
+(Cơ sở: Tự động/Rà soát nhanh)
+(Tiết kiệm: 12.500.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="38" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="39" t="inlineStr">
+        <is>
+          <t>3.82.63.103.LTU.00.000</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO HBS 01 - FPN
+(Đế gắn module IO:
+- Hãng: ABB
+- Mã: HBS 01 - FPN
+- PR (Product Revision): M)</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E42" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (21,120,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 7). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 25,200,000 </t>
+        </is>
+      </c>
+      <c r="G42" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:118/2021) theo hóa đơn số 00000001 ngày 05.01.2022 (ngày ký 2022-01-05 00:00:00, do Nhập kho vật tư (HĐ:118/2021) theo hóa đơn số 00000001 ngày 0</t>
+        </is>
+      </c>
+      <c r="H42" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 19.360.000 đ
+(Cơ sở 2: ERP Vĩnh Tân 4)
+(Tiết kiệm: 52.800.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="38" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="39" t="inlineStr">
+        <is>
+          <t>3.94.00.808.MLT.00.000</t>
+        </is>
+      </c>
+      <c r="C43" s="40" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO HBS01-FPH
+(Đế gắn module IO:
+- Hãng: ABB
+- Mã: HBS 01 - FPH
+- PR (Product Revision): M)</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E43" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá trình (21,120,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 7). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 22,000,000 </t>
+        </is>
+      </c>
+      <c r="G43" s="40" t="inlineStr">
+        <is>
+          <t>Vật tư có lịch sử nhập kho gần nhất theo Nhập kho vật tư (HĐ:88/2025) theo hóa đơn số 00000376 ngày 16.03.2026 (ngày 2026-04-22 00:00:00) với đơn giá 25.000.000 đ/Cái (Tổng số 4 đợt mua sắm lịch sử có đơn giá dao động từ</t>
+        </is>
+      </c>
+      <c r="H43" s="40" t="inlineStr"/>
+      <c r="I43" s="40" t="inlineStr"/>
+      <c r="J43" s="40" t="inlineStr"/>
+      <c r="K43" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 0 đ
+(Cơ sở: Tự động/Rà soát nhanh)
+(Tiết kiệm: 549.120.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="110" customHeight="1">
+      <c r="A44" s="38" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="39" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C44" s="40" t="inlineStr">
         <is>
           <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than
 (Lining Plate (Compound Armour Plate)
@@ -9744,54 +12810,51 @@
 - Chống mài mòn theo ASTM G65: 0,0060 mm3/m)</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E18" s="40" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr"/>
+      <c r="E44" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="40" t="inlineStr">
-        <is>
-          <t>CẢNH BÁO: Đơn giá trình (2,618,304,000 đ) lấy từ Báo giá của DTL 19.8.2026. xlsx nhưng KHÔNG PHẢI là đơn giá thấp nhất! Đơn giá thấp nhất là 1,300,000 đ của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO G</t>
-        </is>
-      </c>
-      <c r="G18" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 1.845.000.000 đ/Bộ (HĐ: Nhập kho vật tư (HĐ: 32/2025) theo hóa đơn số 00000181 ngày 26.11.2025 ngày 2025-12-04. SL: 3 Bộ); Các đợt nhập khác: 1.293.213.000 đ</t>
-        </is>
-      </c>
-      <c r="H18" s="40" t="inlineStr">
+      <c r="F44" s="40" t="inlineStr">
+        <is>
+          <t>Đơn giá trình (2,618,304,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 8). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 2,716,00</t>
+        </is>
+      </c>
+      <c r="G44" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Tấm lót bàn nghiền máy nghiền LM 28.3 D/ Grinding Plate. KT: 125txOD2800xID1510. vật liệu: sintercast]: 1.845.000.000 đ/Bộ (HĐ: Nhập kho vật tư (HĐ: 32/2025) theo hóa đơn số 00000181 ngày</t>
+        </is>
+      </c>
+      <c r="H44" s="40" t="inlineStr">
         <is>
           <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Lining Plate (Compound Armour], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
         </is>
       </c>
-      <c r="I18" s="40" t="inlineStr">
+      <c r="I44" s="40" t="inlineStr">
         <is>
           <t>Đã tra cứu từ khóa [Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
         </is>
       </c>
-      <c r="J18" s="40" t="inlineStr"/>
-      <c r="K18" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 1.300.000 đ
-(Tiết kiệm: 5.234.008.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="J44" s="40" t="inlineStr"/>
+      <c r="K44" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 1.845.000.000 đ
+(Cơ sở 5: Tham khảo TMĐT / Giá Web)
+(Tiết kiệm: 1.546.608.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="38" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="39" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C45" s="40" t="inlineStr">
         <is>
           <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW
 (Bơm (SP-Circulation pump):
@@ -9809,40 +12872,41 @@
 IEC60034-1)</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>[Lưu trong hồ sơ PDF]</t>
         </is>
       </c>
-      <c r="E19" s="40" t="inlineStr">
+      <c r="E45" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="40" t="inlineStr">
+      <c r="F45" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">CẢNH BÁO: Đơn giá trình (770,000,000 đ) lấy từ Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG nhưng KHÔNG PHẢI là đơn giá thấp nhất! Đơn giá thấp nhất là 750,000,000 đ của 08-27-26. BV-VT 4. . 1,620,000,000 </t>
         </is>
       </c>
-      <c r="G19" s="40" t="inlineStr">
+      <c r="G45" s="40" t="inlineStr">
         <is>
           <t>Vật tư chưa có lịch sử mua sắm/nhập kho trong CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4.</t>
         </is>
       </c>
-      <c r="H19" s="40" t="inlineStr">
+      <c r="H45" s="40" t="inlineStr">
         <is>
           <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [TP400 PP], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
         </is>
       </c>
-      <c r="I19" s="40" t="inlineStr">
+      <c r="I45" s="40" t="inlineStr">
         <is>
           <t>Đã tra cứu từ khóa [Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
         </is>
       </c>
-      <c r="J19" s="40" t="inlineStr"/>
-      <c r="K19" s="41" t="inlineStr">
+      <c r="J45" s="40" t="inlineStr"/>
+      <c r="K45" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 750.000.000 đ
+(Cơ sở 1: Đàm phán giảm giá / Báo giá chào)
 (Tiết kiệm: 40.000.000 đ)</t>
         </is>
       </c>
@@ -9851,8 +12915,14 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
 </worksheet>
 </file>
--- a/data/Bao_Cao_Tham_Dinh_Trinh_Lanh_Dao.xlsx
+++ b/data/Bao_Cao_Tham_Dinh_Trinh_Lanh_Dao.xlsx
@@ -438,181 +438,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2438400" cy="1285875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2476500" cy="1276350"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2476500" cy="1200150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1895475" cy="1285875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1847850" cy="1285875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2247900" cy="1285875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>43</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1295400" cy="1285875"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -905,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -954,7 +779,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Lâm Đồng, ngày 10 tháng 09 năm 2026</t>
+          <t>Lâm Đồng, ngày 09 tháng 09 năm 2026</t>
         </is>
       </c>
     </row>
@@ -1001,14 +826,14 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Tổng số: 112 mục (Đã chốt: 41 mục)</t>
+          <t>Tổng số: 112 mục (Đã chốt: 15 mục)</t>
         </is>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Trình: 38.145.576.000 đ  --&gt;  Thẩm định: 34.779.577.092 đ</t>
+          <t>Trình: 38.145.576.000 đ  --&gt;  Thẩm định: 32.385.281.416 đ</t>
         </is>
       </c>
       <c r="E9" s="9" t="n"/>
@@ -1016,7 +841,7 @@
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>TIẾT KIỆM CHO NHÀ MÁY: -3.425.998.908 đ  (8.98%)</t>
+          <t>TIẾT KIỆM CHO NHÀ MÁY: -5.937.874.584 đ  (15.57%)</t>
         </is>
       </c>
       <c r="I9" s="9" t="n"/>
@@ -1131,13 +956,13 @@
         <v>13559000</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>11842500</v>
+        <v>6015000</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>47370000</v>
+        <v>24060000</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>6866000</v>
+        <v>30176000</v>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
@@ -1711,45 +1536,43 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Chưa có mã vật tư</t>
+          <t>2.46.35.037.CHN.00.000</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>Thanh cái đồng V phân phối mạ bạc</t>
+          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>Thanh cái đồng V phân phối mạ bạc
-Kích thước: 28x40x6mm
-Chiều dài: 920mm</t>
+          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Kungho/ Trung Quốc</t>
+          <t>Swagelok/ Đức</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Thanh</t>
+          <t>Cái</t>
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>48000000</v>
+        <v>19300000</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>1390909</v>
+        <v>18522000</v>
       </c>
       <c r="J24" s="17" t="n">
-        <v>5563636</v>
+        <v>648270000</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>186436364</v>
+        <v>27230000</v>
       </c>
       <c r="L24" s="19" t="inlineStr">
         <is>
@@ -1763,22 +1586,23 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>2.46.35.037.CHN.00.000</t>
+          <t>3.96.13.320.USA.00.000</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
+          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
+          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
+NSX: MERRICK</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>Swagelok/ Đức</t>
+          <t>Merrick/ Mỹ</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -1787,19 +1611,19 @@
         </is>
       </c>
       <c r="G25" s="17" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>19300000</v>
+        <v>56105000</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>18522000</v>
+        <v>23000000</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>648270000</v>
+        <v>46000000</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>27230000</v>
+        <v>66210000</v>
       </c>
       <c r="L25" s="19" t="inlineStr">
         <is>
@@ -1813,1401 +1637,15 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>2.46.35.019.CHN.00.000</t>
+          <t>Chưa có mã vật tư</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
+          <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>Swagelok/ Đức</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="17" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="I26" s="17" t="n">
-        <v>12350000</v>
-      </c>
-      <c r="J26" s="17" t="n">
-        <v>24700000</v>
-      </c>
-      <c r="K26" s="18" t="n">
-        <v>13300000</v>
-      </c>
-      <c r="L26" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>4.82.22.013.USA.00.000</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>Swagelok/ Đức</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>Bộ</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="17" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="I27" s="17" t="n">
-        <v>1319000</v>
-      </c>
-      <c r="J27" s="17" t="n">
-        <v>2638000</v>
-      </c>
-      <c r="K27" s="18" t="n">
-        <v>762000</v>
-      </c>
-      <c r="L27" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>4.82.22.025.CHN.00.000</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>Swagelok/ Đức</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="H28" s="17" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="I28" s="17" t="n">
-        <v>644760</v>
-      </c>
-      <c r="J28" s="17" t="n">
-        <v>64476000</v>
-      </c>
-      <c r="K28" s="18" t="n">
-        <v>195524000</v>
-      </c>
-      <c r="L28" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>5.33.70.184.GER.99.000</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>Bộ điều khiển định vị Positioner:
-- Model: TZIDC-V18345- 2020521001
--Type: Double acting 
--Sofw.Rev: 3 
--Supply press: 1,4 ~ 6 bar 
--Input: Analog 4 ~ 20 mA
- -Loss of electric: Fail freeze
-- Option: Analog feedback, FSK, Position indicator 
--NSX: ABB</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>ABB/ Đức</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>Bộ</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H29" s="17" t="n">
-        <v>85000000</v>
-      </c>
-      <c r="I29" s="17" t="n">
-        <v>83484000</v>
-      </c>
-      <c r="J29" s="17" t="n">
-        <v>417420000</v>
-      </c>
-      <c r="K29" s="18" t="n">
-        <v>7580000</v>
-      </c>
-      <c r="L29" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>3.96.13.144.USA.00.000</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>Cảm biến nhiệt độ - Model: S14405PD3S350B0
-- NSX: MINCO 
-- Element: Platinum 
-- Element length: 6.4 mm 
-- Cable dimension "C": 1778 mm 
-- Cable dimension "L": 8890 mm 
-- Single duplex: Duplex 
-- Sheath: 2.9 mm OD 
-- Type: RTD PT100, 3 Wire 
-- Range: 0 - 260 °C</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>Minco/ Mỹ</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>Bộ</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="17" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="I30" s="17" t="n">
-        <v>27923445</v>
-      </c>
-      <c r="J30" s="17" t="n">
-        <v>27923445</v>
-      </c>
-      <c r="K30" s="18" t="n">
-        <v>2076555</v>
-      </c>
-      <c r="L30" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
-Model: LST400 Y0/S15/N1/P6/A1/H1/SC6/B2/CR/M5
-Range: 0.5m to 15m Signal: 4 - 20 mA 
-Supply power: 115 to 230 V AC or 24 V DC.
-NSX: ABB</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
-          <t>ABB/ Đức</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="17" t="n">
-        <v>189000000</v>
-      </c>
-      <c r="I31" s="17" t="n">
-        <v>58423000</v>
-      </c>
-      <c r="J31" s="17" t="n">
-        <v>58423000</v>
-      </c>
-      <c r="K31" s="18" t="n">
-        <v>130577000</v>
-      </c>
-      <c r="L31" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
-Model: MA3145-230-2-R
-- Điện áp hoạt động tối đa (Max working voltage): ≥ 270 VAC.
-- Điện áp định mức (Voltage rating): 230 VAC.
-- Dòng cắt sét / Khả năng chịu dòng ngắn mạch (Circuit breaker / Surge capacity): ≥ 40 kA.
-NSX: Cooper Crouse-Hinds MTL / Eaton</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>Eaton/ Slovenia</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="17" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="I32" s="17" t="n">
-        <v>21609600</v>
-      </c>
-      <c r="J32" s="17" t="n">
-        <v>64828800</v>
-      </c>
-      <c r="K32" s="18" t="n">
-        <v>40171200</v>
-      </c>
-      <c r="L32" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="14" t="n">
-        <v>21</v>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>3.34.40.009.IND.00.000</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>Công tắc lưu lượng (Flow Switch)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>Công tắc lưu lượng (Flow Switch)
-Model: WP/FS-25VFL
-Switch : SPDT Snap Acting Micro
-Rating : 5A 250VAC 
-NSX: Dag Process Instruments Pvt. Ltd</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>Dag Process Instruments Pvt. Ltd/ Ấn Độ</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="17" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="I33" s="17" t="n">
-        <v>32500000</v>
-      </c>
-      <c r="J33" s="17" t="n">
-        <v>32500000</v>
-      </c>
-      <c r="K33" s="18" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="L33" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>3.96.13.165.KOR.00.000</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>Cảm biến tiệm cận/proximity sensor</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>Cảm biến tiệm cận/proximity sensor
-- Model: PR30-10AC
-Đường kính cạnh phát hiện: 30mm
-- Điện áp hoạt động: 100-240 Vac
-- Ngõ ra điều khiển: NC
-- Protection: IP67</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>Autonics/ China</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="17" t="n">
-        <v>1219000</v>
-      </c>
-      <c r="I34" s="17" t="n">
-        <v>911127</v>
-      </c>
-      <c r="J34" s="17" t="n">
-        <v>1822254</v>
-      </c>
-      <c r="K34" s="18" t="n">
-        <v>615746</v>
-      </c>
-      <c r="L34" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>3.96.13.114.KOR.99.000</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>Cảm biến tiệm cận/proximity sensor</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>Cảm biến tiệm cận/proximity sensor
-- Model: PR18-8AO
-- Đường kính đầu dò: 18mm
-- Điện áp hoạt động: 100-240 Vac
-- Ngõ ra điều khiển: NO
-- Protection: IP67</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>Autonics/ China</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>Bộ</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="17" t="n">
-        <v>1150000</v>
-      </c>
-      <c r="I35" s="17" t="n">
-        <v>577200</v>
-      </c>
-      <c r="J35" s="17" t="n">
-        <v>577200</v>
-      </c>
-      <c r="K35" s="18" t="n">
-        <v>572800</v>
-      </c>
-      <c r="L35" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>3.34.20.134.CHN.00.000</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>Pendant control station:
-Type: XAC-A12713</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>Pendant control station:
-Type: XAC-A12713</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>Schnerder/ Czech Republic</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="17" t="n">
-        <v>5784000</v>
-      </c>
-      <c r="I36" s="17" t="n">
-        <v>420000</v>
-      </c>
-      <c r="J36" s="17" t="n">
-        <v>420000</v>
-      </c>
-      <c r="K36" s="18" t="n">
-        <v>5364000</v>
-      </c>
-      <c r="L36" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>4.90.80.030.KOR.00.000</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>Joint cover (bao che giữa các khớp nối đường ray cáp điện):
-- Material: PVC
-- Maker: Eunchang T&amp;C</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>Eunchang/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="n">
-        <v>235</v>
-      </c>
-      <c r="H37" s="17" t="n">
-        <v>66000</v>
-      </c>
-      <c r="I37" s="17" t="n">
-        <v>26000</v>
-      </c>
-      <c r="J37" s="17" t="n">
-        <v>6110000</v>
-      </c>
-      <c r="K37" s="18" t="n">
-        <v>9400000</v>
-      </c>
-      <c r="L37" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="14" t="n">
-        <v>26</v>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>4.90.80.027.KOR.00.000</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>Nắp che phía cuối đường ray cáp điện (End cap)</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
-- Maker: Eunchang T&amp;C</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>Eunchang/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="H38" s="17" t="n">
-        <v>68000</v>
-      </c>
-      <c r="I38" s="17" t="n">
-        <v>21000</v>
-      </c>
-      <c r="J38" s="17" t="n">
-        <v>672000</v>
-      </c>
-      <c r="K38" s="18" t="n">
-        <v>1504000</v>
-      </c>
-      <c r="L38" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="14" t="n">
-        <v>27</v>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>2.08.37.001.KOR.97.000</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>Trolley-bar (thanh ray cấp nguồn)</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>Trolley-bar (thanh ray cấp nguồn):
-- Iđm: 60A;
-- Uđm: 400VAC;
-- Length: 3m / cây
-- Material: Copper
-- Maker: EunchangT&amp;C</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
-          <t>Eunchang/ Hàn Quốc</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>Cây</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="n">
-        <v>28</v>
-      </c>
-      <c r="H39" s="17" t="n">
-        <v>909000</v>
-      </c>
-      <c r="I39" s="17" t="n">
-        <v>890000</v>
-      </c>
-      <c r="J39" s="17" t="n">
-        <v>24920000</v>
-      </c>
-      <c r="K39" s="18" t="n">
-        <v>532000</v>
-      </c>
-      <c r="L39" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="14" t="n">
-        <v>28</v>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>3.34.20.133.CHN.99.000</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>Pendant control station:
-Type: XAC-A6913</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>Pendant control station:
-Type: XAC-A6913
-Control station composition: 06 push buttons + 01 emergency stop
-Product compatibility: 
-ZB2BE102 for emergency stop, XEN-G1191 for each direction
-Color: Yellow</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>Schnerder/ Czech Republic</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="17" t="n">
-        <v>13319000</v>
-      </c>
-      <c r="I40" s="17" t="n">
-        <v>3290400</v>
-      </c>
-      <c r="J40" s="17" t="n">
-        <v>3290400</v>
-      </c>
-      <c r="K40" s="18" t="n">
-        <v>10028600</v>
-      </c>
-      <c r="L40" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="14" t="n">
-        <v>29</v>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>Lưỡi gà móc cẩu 3 tấn</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>Lưỡi gà móc cẩu 3 tấn
-Kích thước: rộng 25mm x dài 60mm</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>MT/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="17" t="n">
-        <v>610000</v>
-      </c>
-      <c r="I41" s="17" t="n">
-        <v>314600</v>
-      </c>
-      <c r="J41" s="17" t="n">
-        <v>314600</v>
-      </c>
-      <c r="K41" s="18" t="n">
-        <v>295400</v>
-      </c>
-      <c r="L41" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>2.50.05.003.CHN.00.000</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>Cáp inox 304 
-Kích thước: Ø 3 mm</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>Cáp inox 304 
-Kích thước: Ø 3 mm</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>Mét</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="H42" s="17" t="n">
-        <v>37000</v>
-      </c>
-      <c r="I42" s="17" t="n">
-        <v>24000</v>
-      </c>
-      <c r="J42" s="17" t="n">
-        <v>1440000</v>
-      </c>
-      <c r="K42" s="18" t="n">
-        <v>780000</v>
-      </c>
-      <c r="L42" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="14" t="n">
-        <v>31</v>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>Phe cài trục ngoài cho đường kính 28mm</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>Phe cài trục ngoài cho đường kính 28mm.
-Vật liệu: Inox 304</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G43" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="17" t="n">
-        <v>56000</v>
-      </c>
-      <c r="I43" s="17" t="n">
-        <v>50000</v>
-      </c>
-      <c r="J43" s="17" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K43" s="18" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L43" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="14" t="n">
-        <v>32</v>
-      </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>2.06.60.080.TPE.00.000</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>Kẹp cố định đầu ray
-Loại: CH2260
-Size: 80x51x3mm</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>Kẹp cố định đầu ray
-Loại: CH2260
-Size: 80x51x3mm
-Vật liệu: Inox 304
-Hãng: ITS Đài loan</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>ITS/ Đài Loan</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="17" t="n">
-        <v>2254000</v>
-      </c>
-      <c r="I44" s="17" t="n">
-        <v>578078</v>
-      </c>
-      <c r="J44" s="17" t="n">
-        <v>1156156</v>
-      </c>
-      <c r="K44" s="18" t="n">
-        <v>3351844</v>
-      </c>
-      <c r="L44" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="14" t="n">
-        <v>33</v>
-      </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>3.15.44.076.CHN.00.000</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>Cáp điện dẹt cho cầu trục
-Quy cách: 16mm2 x 4C
-Ruột mềm</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="inlineStr">
-        <is>
-          <t>Cáp điện dẹt cho cầu trục
-Quy cách: 16mm2 x 4C
-Ruột mềm
-Điện áp: 450/750V
-Cách điện: PVC, dẻo
-NSX: Imatek</t>
-        </is>
-      </c>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
-          <t>Imatek/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="inlineStr">
-        <is>
-          <t>Mét</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="H45" s="17" t="n">
-        <v>711000</v>
-      </c>
-      <c r="I45" s="17" t="n">
-        <v>76000</v>
-      </c>
-      <c r="J45" s="17" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="K45" s="18" t="n">
-        <v>31750000</v>
-      </c>
-      <c r="L45" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="14" t="n">
-        <v>34</v>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>3.20.22.003.TPE.00.000</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>Khóa cáp 
-Dùng cho cáp: 3mm</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>Khóa cáp 
-Dùng cho cáp: 3mm</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G46" s="17" t="n">
-        <v>55</v>
-      </c>
-      <c r="H46" s="17" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I46" s="17" t="n">
-        <v>14000</v>
-      </c>
-      <c r="J46" s="17" t="n">
-        <v>770000</v>
-      </c>
-      <c r="K46" s="18" t="n">
-        <v>330000</v>
-      </c>
-      <c r="L46" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="14" t="n">
-        <v>35</v>
-      </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>3.34.20.130.CHN.99.000</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>Pendant control station (Tay bấm điều khiển tời điện): 
-- Type: XAC-A6713</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="inlineStr">
-        <is>
-          <t>Pendant control station (Tay bấm điều khiển tời điện): 
-- Type: XAC-A6713
-Control station composition: 06, push buttons + 01 emergency stop</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>Schnerder/ Czech Republic</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G47" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="17" t="n">
-        <v>7406000</v>
-      </c>
-      <c r="I47" s="17" t="n">
-        <v>3310185</v>
-      </c>
-      <c r="J47" s="17" t="n">
-        <v>3310185</v>
-      </c>
-      <c r="K47" s="18" t="n">
-        <v>4095815</v>
-      </c>
-      <c r="L47" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="14" t="n">
-        <v>36</v>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>Lưỡi gà móc cẩu 7 tấn</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>Lưỡi gà móc cẩu 7 tấn:
- + Kích thước: 60 x 175x 3mm
- + Vật liệu: thép</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G48" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="17" t="n">
-        <v>656000</v>
-      </c>
-      <c r="I48" s="17" t="n">
-        <v>585000</v>
-      </c>
-      <c r="J48" s="17" t="n">
-        <v>585000</v>
-      </c>
-      <c r="K48" s="18" t="n">
-        <v>71000</v>
-      </c>
-      <c r="L48" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="14" t="n">
-        <v>37</v>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>Sơn dầu Jotun chống sét Green 437</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>Sơn dầu Jotun chống sét Green 437</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
-        <is>
-          <t>Kungho/ Trung Quốc</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>Lít</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="H49" s="17" t="n">
-        <v>625000</v>
-      </c>
-      <c r="I49" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="18" t="n">
-        <v>12500000</v>
-      </c>
-      <c r="L49" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="14" t="n">
-        <v>38</v>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>3.82.63.103.LTU.00.000</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO HBS 01 - FPN</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO:
-- Hãng: ABB
-- Mã: HBS 01 - FPN
-- PR (Product Revision): M</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
-          <t>ABB/ Lithuania</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="H50" s="17" t="n">
-        <v>21120000</v>
-      </c>
-      <c r="I50" s="17" t="n">
-        <v>19360000</v>
-      </c>
-      <c r="J50" s="17" t="n">
-        <v>580800000</v>
-      </c>
-      <c r="K50" s="18" t="n">
-        <v>52800000</v>
-      </c>
-      <c r="L50" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="14" t="n">
-        <v>39</v>
-      </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>3.94.00.808.MLT.00.000</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO HBS01-FPH</t>
-        </is>
-      </c>
-      <c r="D51" s="16" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO:
-- Hãng: ABB
-- Mã: HBS 01 - FPH
-- PR (Product Revision): M</t>
-        </is>
-      </c>
-      <c r="E51" s="15" t="inlineStr">
-        <is>
-          <t>ABB/ Lithuania</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>Cái</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="n">
-        <v>26</v>
-      </c>
-      <c r="H51" s="17" t="n">
-        <v>21120000</v>
-      </c>
-      <c r="I51" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="18" t="n">
-        <v>549120000</v>
-      </c>
-      <c r="L51" s="19" t="inlineStr">
-        <is>
-          <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Lining Plate (Compound Armour Plate)
 Tấm lót thân máy nghiền
@@ -3222,52 +1660,52 @@
 - Chống mài mòn theo ASTM G65: 0,0060 mm3/m</t>
         </is>
       </c>
-      <c r="E52" s="15" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>ML/ Ba Lan</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G52" s="17" t="n">
+      <c r="G26" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H52" s="17" t="n">
+      <c r="H26" s="17" t="n">
         <v>2618304000</v>
       </c>
-      <c r="I52" s="17" t="n">
-        <v>1845000000</v>
-      </c>
-      <c r="J52" s="17" t="n">
-        <v>3690000000</v>
-      </c>
-      <c r="K52" s="18" t="n">
-        <v>1546608000</v>
-      </c>
-      <c r="L52" s="19" t="inlineStr">
+      <c r="I26" s="17" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="J26" s="17" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>5234008000</v>
+      </c>
+      <c r="L26" s="19" t="inlineStr">
         <is>
           <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="14" t="n">
-        <v>41</v>
-      </c>
-      <c r="B53" s="15" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C53" s="16" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW</t>
         </is>
       </c>
-      <c r="D53" s="16" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Bơm (SP-Circulation pump):
 TP400 PP, P4-400V/50
@@ -3284,90 +1722,90 @@
 IEC60034-1</t>
         </is>
       </c>
-      <c r="E53" s="15" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>Grundfos/ Eu</t>
         </is>
       </c>
-      <c r="F53" s="14" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G53" s="17" t="n">
+      <c r="G27" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H53" s="17" t="n">
+      <c r="H27" s="17" t="n">
         <v>770000000</v>
       </c>
-      <c r="I53" s="17" t="n">
+      <c r="I27" s="17" t="n">
         <v>750000000</v>
       </c>
-      <c r="J53" s="17" t="n">
+      <c r="J27" s="17" t="n">
         <v>1500000000</v>
       </c>
-      <c r="K53" s="18" t="n">
+      <c r="K27" s="18" t="n">
         <v>40000000</v>
       </c>
-      <c r="L53" s="19" t="inlineStr">
+      <c r="L27" s="19" t="inlineStr">
         <is>
           <t>Chi tiết xin xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>TỔNG CỘNG CÁC MỤC ĐÃ CHỐT THẨM ĐỊNH:</t>
         </is>
       </c>
-      <c r="B54" s="21" t="n"/>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="21" t="n"/>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="n"/>
-      <c r="H54" s="21" t="n"/>
-      <c r="I54" s="21" t="n"/>
-      <c r="J54" s="22" t="n">
-        <v>7946260092.5</v>
-      </c>
-      <c r="K54" s="23" t="n">
-        <v>3425998907.5</v>
-      </c>
-      <c r="L54" s="21" t="n"/>
-    </row>
-    <row r="57">
-      <c r="B57" s="24" t="inlineStr">
+      <c r="B28" s="21" t="n"/>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="21" t="n"/>
+      <c r="F28" s="21" t="n"/>
+      <c r="G28" s="21" t="n"/>
+      <c r="H28" s="21" t="n"/>
+      <c r="I28" s="21" t="n"/>
+      <c r="J28" s="22" t="n">
+        <v>2953039416.5</v>
+      </c>
+      <c r="K28" s="23" t="n">
+        <v>5937874583.5</v>
+      </c>
+      <c r="L28" s="21" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>NGƯỜI LẬP BÁO CÁO / THƯ KÝ TỔ TTĐ</t>
         </is>
       </c>
-      <c r="J57" s="24" t="inlineStr">
+      <c r="J31" s="24" t="inlineStr">
         <is>
           <t>TỔ TRƯỞNG TỔ THẨM ĐỊNH DỰ TOÁN</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="25" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>(Ký và ghi rõ họ tên)</t>
         </is>
       </c>
-      <c r="J58" s="25" t="inlineStr">
+      <c r="J32" s="25" t="inlineStr">
         <is>
           <t>(Ký và ghi rõ họ tên)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="26" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>Nguyễn Anh Hiếu</t>
         </is>
       </c>
-      <c r="J63" s="26" t="inlineStr">
+      <c r="J37" s="26" t="inlineStr">
         <is>
           <t>...................................................</t>
         </is>
@@ -3377,6 +1815,7 @@
   <mergeCells count="13">
     <mergeCell ref="H9:L9"/>
     <mergeCell ref="D9:G9"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="D8:G8"/>
     <mergeCell ref="A8:C8"/>
@@ -3387,7 +1826,6 @@
     <mergeCell ref="A6:L6"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="H8:L8"/>
-    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId1"/>
@@ -3405,32 +1843,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3471,7 +1883,7 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Hồ sơ: Bang_Tham_Dinh_Du_Toan (3) - Bản Mới - Bản Mới | Cập nhật: 10/09/2026 16:18</t>
+          <t>Hồ sơ: Bang_Tham_Dinh_Du_Toan (3) - Bản Mới - Bản Mới | Cập nhật: 09/09/2026 09:12</t>
         </is>
       </c>
     </row>
@@ -3588,13 +2000,13 @@
         <v>54236000</v>
       </c>
       <c r="J5" s="31" t="n">
-        <v>11842500</v>
+        <v>6015000</v>
       </c>
       <c r="K5" s="31" t="n">
-        <v>47370000</v>
+        <v>24060000</v>
       </c>
       <c r="L5" s="23" t="n">
-        <v>6866000</v>
+        <v>30176000</v>
       </c>
       <c r="M5" s="32" t="inlineStr">
         <is>
@@ -4576,62 +2988,62 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="28" t="n">
+      <c r="A21" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C21" s="30" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>Thanh cái đồng V phân phối mạ bạc</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Thanh cái đồng V phân phối mạ bạc
 Kích thước: 28x40x6mm
 Chiều dài: 920mm</t>
         </is>
       </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>Thanh</t>
         </is>
       </c>
-      <c r="G21" s="31" t="n">
+      <c r="G21" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="31" t="n">
+      <c r="H21" s="17" t="n">
         <v>48000000</v>
       </c>
-      <c r="I21" s="31" t="n">
+      <c r="I21" s="17" t="n">
         <v>192000000</v>
       </c>
-      <c r="J21" s="31" t="n">
-        <v>1390909</v>
-      </c>
-      <c r="K21" s="31" t="n">
-        <v>5563636</v>
-      </c>
-      <c r="L21" s="23" t="n">
-        <v>186436364</v>
-      </c>
-      <c r="M21" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N21" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J21" s="17" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="K21" s="17" t="n">
+        <v>192000000</v>
+      </c>
+      <c r="L21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay thế cho vật tư hư hỏng theo BBKT 37/2026/VH-VT4 | Vật tư mua mới, không đề xuất trong KHSXKD 2026</t>
         </is>
       </c>
     </row>
@@ -4755,176 +3167,176 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="28" t="n">
+      <c r="A24" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>2.46.35.019.CHN.00.000</t>
         </is>
       </c>
-      <c r="C24" s="30" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
         </is>
       </c>
-      <c r="D24" s="30" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
         </is>
       </c>
-      <c r="E24" s="29" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>Swagelok/ Đức</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G24" s="31" t="n">
+      <c r="G24" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="31" t="n">
+      <c r="H24" s="17" t="n">
         <v>19000000</v>
       </c>
-      <c r="I24" s="31" t="n">
+      <c r="I24" s="17" t="n">
         <v>38000000</v>
       </c>
-      <c r="J24" s="31" t="n">
-        <v>12350000</v>
-      </c>
-      <c r="K24" s="31" t="n">
-        <v>24700000</v>
-      </c>
-      <c r="L24" s="23" t="n">
-        <v>13300000</v>
-      </c>
-      <c r="M24" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N24" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J24" s="17" t="n">
+        <v>19000000</v>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>2.46.35.019.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="28" t="n">
+      <c r="A25" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>4.82.22.013.USA.00.000</t>
         </is>
       </c>
-      <c r="C25" s="30" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
         </is>
       </c>
-      <c r="D25" s="30" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
         </is>
       </c>
-      <c r="E25" s="29" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Swagelok/ Đức</t>
         </is>
       </c>
-      <c r="F25" s="28" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G25" s="31" t="n">
+      <c r="G25" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="31" t="n">
+      <c r="H25" s="17" t="n">
         <v>1700000</v>
       </c>
-      <c r="I25" s="31" t="n">
+      <c r="I25" s="17" t="n">
         <v>3400000</v>
       </c>
-      <c r="J25" s="31" t="n">
-        <v>1319000</v>
-      </c>
-      <c r="K25" s="31" t="n">
-        <v>2638000</v>
-      </c>
-      <c r="L25" s="23" t="n">
-        <v>762000</v>
-      </c>
-      <c r="M25" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N25" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J25" s="17" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>4.82.22.013.USA.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="28" t="n">
+      <c r="A26" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>4.82.22.025.CHN.00.000</t>
         </is>
       </c>
-      <c r="C26" s="30" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
         </is>
       </c>
-      <c r="D26" s="30" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
         </is>
       </c>
-      <c r="E26" s="29" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>Swagelok/ Đức</t>
         </is>
       </c>
-      <c r="F26" s="28" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G26" s="31" t="n">
+      <c r="G26" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="H26" s="31" t="n">
+      <c r="H26" s="17" t="n">
         <v>2600000</v>
       </c>
-      <c r="I26" s="31" t="n">
+      <c r="I26" s="17" t="n">
         <v>260000000</v>
       </c>
-      <c r="J26" s="31" t="n">
-        <v>644760</v>
-      </c>
-      <c r="K26" s="31" t="n">
-        <v>64476000</v>
-      </c>
-      <c r="L26" s="23" t="n">
-        <v>195524000</v>
-      </c>
-      <c r="M26" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N26" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J26" s="17" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="K26" s="17" t="n">
+        <v>260000000</v>
+      </c>
+      <c r="L26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>4.82.22.025.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
         </is>
       </c>
     </row>
@@ -4987,20 +3399,20 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="28" t="n">
+      <c r="A28" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>5.33.70.184.GER.99.000</t>
         </is>
       </c>
-      <c r="C28" s="30" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001</t>
         </is>
       </c>
-      <c r="D28" s="30" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Bộ điều khiển định vị Positioner:
 - Model: TZIDC-V18345- 2020521001
@@ -5013,60 +3425,60 @@
 -NSX: ABB</t>
         </is>
       </c>
-      <c r="E28" s="29" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>ABB/ Đức</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="F28" s="14" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G28" s="31" t="n">
+      <c r="G28" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="31" t="n">
+      <c r="H28" s="17" t="n">
         <v>85000000</v>
       </c>
-      <c r="I28" s="31" t="n">
+      <c r="I28" s="17" t="n">
         <v>425000000</v>
       </c>
-      <c r="J28" s="31" t="n">
-        <v>83484000</v>
-      </c>
-      <c r="K28" s="31" t="n">
-        <v>417420000</v>
-      </c>
-      <c r="L28" s="23" t="n">
-        <v>7580000</v>
-      </c>
-      <c r="M28" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N28" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J28" s="17" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v>425000000</v>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>5.33.70.184.GER.99.000 | Thay thế các bộ positioner điều khiển damper gió SA bị xì khí nén của tổ máy S2 | Vật tư được đề xuất trong KHSXKD năm 2026,nhưng phát sinh hư hỏng thêm 2 bộ vượt nhu cầu dự kiến, nên đề xuất mua sắm bổ sung. Tên vật tư được đặt lại theo quy tắc chuẩn hóa.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="28" t="n">
+      <c r="A29" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>3.96.13.144.USA.00.000</t>
         </is>
       </c>
-      <c r="C29" s="30" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire</t>
         </is>
       </c>
-      <c r="D29" s="30" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>Cảm biến nhiệt độ - Model: S14405PD3S350B0
 - NSX: MINCO 
@@ -5080,119 +3492,119 @@
 - Range: 0 - 260 °C</t>
         </is>
       </c>
-      <c r="E29" s="29" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>Minco/ Mỹ</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G29" s="31" t="n">
+      <c r="G29" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="31" t="n">
+      <c r="H29" s="17" t="n">
         <v>30000000</v>
       </c>
-      <c r="I29" s="31" t="n">
+      <c r="I29" s="17" t="n">
         <v>30000000</v>
       </c>
-      <c r="J29" s="31" t="n">
-        <v>27923445</v>
-      </c>
-      <c r="K29" s="31" t="n">
-        <v>27923445</v>
-      </c>
-      <c r="L29" s="23" t="n">
-        <v>2076555</v>
-      </c>
-      <c r="M29" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N29" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J29" s="17" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="K29" s="17" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="L29" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>3.96.13.144.USA.00.000 | BBKT- 1008/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến nhiệt độ số 2 gối chặn BFPT B S2 báo lỗi.Vật tư có trong KH SXKD 2026 (mã KH TXBS.26.562). | Mua sắm dự phòng hết tồn kho thiết bị giám sát quan trọng.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>3.96.13.320.USA.00.000</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
         <is>
           <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
 NSX: MERRICK</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E30" s="29" t="inlineStr">
         <is>
           <t>Merrick/ Mỹ</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="F30" s="28" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G30" s="17" t="n">
+      <c r="G30" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="17" t="n">
+      <c r="H30" s="31" t="n">
         <v>56105000</v>
       </c>
-      <c r="I30" s="17" t="n">
+      <c r="I30" s="31" t="n">
         <v>112210000</v>
       </c>
-      <c r="J30" s="17" t="n">
-        <v>56105000</v>
-      </c>
-      <c r="K30" s="17" t="n">
-        <v>112210000</v>
-      </c>
-      <c r="L30" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="14" t="inlineStr">
-        <is>
-          <t>Đang rà soát</t>
-        </is>
-      </c>
-      <c r="N30" s="16" t="inlineStr">
-        <is>
-          <t>3.96.13.320.USA.00.000 | BBKT- 1033/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến khối lượng than – máy cấp A tổ máy S3 báo sai giá trị.Vật tư không có trong KH SXKD 2026. | Mua sắm dự phòng hết tồn kho thiết bị giám sát quan trọng.</t>
+      <c r="J30" s="31" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="K30" s="31" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="L30" s="23" t="n">
+        <v>66210000</v>
+      </c>
+      <c r="M30" s="32" t="inlineStr">
+        <is>
+          <t>ĐÃ CHỐT</t>
+        </is>
+      </c>
+      <c r="N30" s="33" t="inlineStr">
+        <is>
+          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="28" t="n">
+      <c r="A31" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C31" s="30" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm)</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
 Model: LST400 Y0/S15/N1/P6/A1/H1/SC6/B2/CR/M5
@@ -5201,42 +3613,42 @@
 NSX: ABB</t>
         </is>
       </c>
-      <c r="E31" s="29" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>ABB/ Đức</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G31" s="31" t="n">
+      <c r="G31" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="31" t="n">
+      <c r="H31" s="17" t="n">
         <v>189000000</v>
       </c>
-      <c r="I31" s="31" t="n">
+      <c r="I31" s="17" t="n">
         <v>189000000</v>
       </c>
-      <c r="J31" s="31" t="n">
-        <v>58423000</v>
-      </c>
-      <c r="K31" s="31" t="n">
-        <v>58423000</v>
-      </c>
-      <c r="L31" s="23" t="n">
-        <v>130577000</v>
-      </c>
-      <c r="M31" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N31" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J31" s="17" t="n">
+        <v>189000000</v>
+      </c>
+      <c r="K31" s="17" t="n">
+        <v>189000000</v>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>Chưa có mã VT | BBKT- 955/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến báo mức nước tổng kênh tuần hoàn tổ máy S1 báo sai giá trị. | Vật tư không có trong KH SXKD 2026.</t>
         </is>
       </c>
     </row>
@@ -6032,20 +4444,20 @@
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="28" t="n">
+      <c r="A45" s="14" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="29" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C45" s="30" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)</t>
         </is>
       </c>
-      <c r="D45" s="30" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
 Model: MA3145-230-2-R
@@ -6055,42 +4467,42 @@
 NSX: Cooper Crouse-Hinds MTL / Eaton</t>
         </is>
       </c>
-      <c r="E45" s="29" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
         <is>
           <t>Eaton/ Slovenia</t>
         </is>
       </c>
-      <c r="F45" s="28" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G45" s="31" t="n">
+      <c r="G45" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="31" t="n">
+      <c r="H45" s="17" t="n">
         <v>35000000</v>
       </c>
-      <c r="I45" s="31" t="n">
+      <c r="I45" s="17" t="n">
         <v>105000000</v>
       </c>
-      <c r="J45" s="31" t="n">
-        <v>21609600</v>
-      </c>
-      <c r="K45" s="31" t="n">
-        <v>64828800</v>
-      </c>
-      <c r="L45" s="23" t="n">
-        <v>40171200</v>
-      </c>
-      <c r="M45" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N45" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J45" s="17" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="K45" s="17" t="n">
+        <v>105000000</v>
+      </c>
+      <c r="L45" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N45" s="16" t="inlineStr">
+        <is>
+          <t>Chưa có mã VT | BBKT- 1089/2026/VH-VT4_ Kiểm tra, khắc phục các con đo lưu lượng nước biển S3 không. hiển thị. | Vật tư không có trong KH SXKD 2026.</t>
         </is>
       </c>
     </row>
@@ -6155,20 +4567,20 @@
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="28" t="n">
+      <c r="A47" s="14" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="29" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>3.34.40.009.IND.00.000</t>
         </is>
       </c>
-      <c r="C47" s="30" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>Công tắc lưu lượng (Flow Switch)</t>
         </is>
       </c>
-      <c r="D47" s="30" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>Công tắc lưu lượng (Flow Switch)
 Model: WP/FS-25VFL
@@ -6177,42 +4589,42 @@
 NSX: Dag Process Instruments Pvt. Ltd</t>
         </is>
       </c>
-      <c r="E47" s="29" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
         <is>
           <t>Dag Process Instruments Pvt. Ltd/ Ấn Độ</t>
         </is>
       </c>
-      <c r="F47" s="28" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G47" s="31" t="n">
+      <c r="G47" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="31" t="n">
+      <c r="H47" s="17" t="n">
         <v>38000000</v>
       </c>
-      <c r="I47" s="31" t="n">
+      <c r="I47" s="17" t="n">
         <v>38000000</v>
       </c>
-      <c r="J47" s="31" t="n">
-        <v>32500000</v>
-      </c>
-      <c r="K47" s="31" t="n">
-        <v>32500000</v>
-      </c>
-      <c r="L47" s="23" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="M47" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N47" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J47" s="17" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="K47" s="17" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="L47" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N47" s="16" t="inlineStr">
+        <is>
+          <t>Chưa có mã VT | BBKT- 1122/2026/VH-VT4_ Kiểm tra, lỗi tín hiệu lưu lượng gió chèn 1B – ESP -  S1 báo lỗi. | Vật tư không có trong KH SXKD 2026.</t>
         </is>
       </c>
     </row>
@@ -6280,20 +4692,20 @@
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="28" t="n">
+      <c r="A49" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="29" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>3.96.13.165.KOR.00.000</t>
         </is>
       </c>
-      <c r="C49" s="30" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>Cảm biến tiệm cận/proximity sensor</t>
         </is>
       </c>
-      <c r="D49" s="30" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>Cảm biến tiệm cận/proximity sensor
 - Model: PR30-10AC
@@ -6303,60 +4715,60 @@
 - Protection: IP67</t>
         </is>
       </c>
-      <c r="E49" s="29" t="inlineStr">
+      <c r="E49" s="15" t="inlineStr">
         <is>
           <t>Autonics/ China</t>
         </is>
       </c>
-      <c r="F49" s="28" t="inlineStr">
+      <c r="F49" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G49" s="31" t="n">
+      <c r="G49" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="31" t="n">
+      <c r="H49" s="17" t="n">
         <v>1219000</v>
       </c>
-      <c r="I49" s="31" t="n">
+      <c r="I49" s="17" t="n">
         <v>2438000</v>
       </c>
-      <c r="J49" s="31" t="n">
-        <v>911127</v>
-      </c>
-      <c r="K49" s="31" t="n">
-        <v>1822254</v>
-      </c>
-      <c r="L49" s="23" t="n">
-        <v>615746</v>
-      </c>
-      <c r="M49" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N49" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J49" s="17" t="n">
+        <v>1219000</v>
+      </c>
+      <c r="K49" s="17" t="n">
+        <v>2438000</v>
+      </c>
+      <c r="L49" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N49" s="16" t="inlineStr">
+        <is>
+          <t>3.96.13.165.KOR.00.000 | Sửa chữa Tời điện số 15 tấn A Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương, kích thước theo file BBKT đính kèm</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="28" t="n">
+      <c r="A50" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="29" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>3.96.13.114.KOR.99.000</t>
         </is>
       </c>
-      <c r="C50" s="30" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>Cảm biến tiệm cận/proximity sensor</t>
         </is>
       </c>
-      <c r="D50" s="30" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>Cảm biến tiệm cận/proximity sensor
 - Model: PR18-8AO
@@ -6366,42 +4778,42 @@
 - Protection: IP67</t>
         </is>
       </c>
-      <c r="E50" s="29" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>Autonics/ China</t>
         </is>
       </c>
-      <c r="F50" s="28" t="inlineStr">
+      <c r="F50" s="14" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="G50" s="31" t="n">
+      <c r="G50" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="31" t="n">
+      <c r="H50" s="17" t="n">
         <v>1150000</v>
       </c>
-      <c r="I50" s="31" t="n">
+      <c r="I50" s="17" t="n">
         <v>1150000</v>
       </c>
-      <c r="J50" s="31" t="n">
-        <v>577200</v>
-      </c>
-      <c r="K50" s="31" t="n">
-        <v>577200</v>
-      </c>
-      <c r="L50" s="23" t="n">
-        <v>572800</v>
-      </c>
-      <c r="M50" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N50" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J50" s="17" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="K50" s="17" t="n">
+        <v>1150000</v>
+      </c>
+      <c r="L50" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N50" s="16" t="inlineStr">
+        <is>
+          <t>3.96.13.114.KOR.99.000 | Sửa chữa Tời điện số 15 tấn A Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
@@ -6447,10 +4859,10 @@
         <v>597060000</v>
       </c>
       <c r="J51" s="17" t="n">
-        <v>465000</v>
+        <v>535000</v>
       </c>
       <c r="K51" s="17" t="n">
-        <v>597060000</v>
+        <v>686940000</v>
       </c>
       <c r="L51" s="17" t="n">
         <v>0</v>
@@ -6467,62 +4879,62 @@
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="28" t="n">
+      <c r="A52" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="29" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>3.34.20.134.CHN.00.000</t>
         </is>
       </c>
-      <c r="C52" s="30" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>Pendant control station:
 Type: XAC-A12713</t>
         </is>
       </c>
-      <c r="D52" s="30" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Pendant control station:
 Type: XAC-A12713</t>
         </is>
       </c>
-      <c r="E52" s="29" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>Schnerder/ Czech Republic</t>
         </is>
       </c>
-      <c r="F52" s="28" t="inlineStr">
+      <c r="F52" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G52" s="31" t="n">
+      <c r="G52" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="31" t="n">
+      <c r="H52" s="17" t="n">
         <v>5784000</v>
       </c>
-      <c r="I52" s="31" t="n">
+      <c r="I52" s="17" t="n">
         <v>5784000</v>
       </c>
-      <c r="J52" s="31" t="n">
-        <v>420000</v>
-      </c>
-      <c r="K52" s="31" t="n">
-        <v>420000</v>
-      </c>
-      <c r="L52" s="23" t="n">
-        <v>5364000</v>
-      </c>
-      <c r="M52" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N52" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J52" s="17" t="n">
+        <v>5784000</v>
+      </c>
+      <c r="K52" s="17" t="n">
+        <v>5784000</v>
+      </c>
+      <c r="L52" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N52" s="16" t="inlineStr">
+        <is>
+          <t>3.34.20.134.CHN.00.000 | Sửa chữa tời điện Tời điện số 15 tấn B Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
@@ -6589,139 +5001,139 @@
       </c>
     </row>
     <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="28" t="n">
+      <c r="A54" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="29" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>4.90.80.030.KOR.00.000</t>
         </is>
       </c>
-      <c r="C54" s="30" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)</t>
         </is>
       </c>
-      <c r="D54" s="30" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>Joint cover (bao che giữa các khớp nối đường ray cáp điện):
 - Material: PVC
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="E54" s="29" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>Eunchang/ Hàn Quốc</t>
         </is>
       </c>
-      <c r="F54" s="28" t="inlineStr">
+      <c r="F54" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G54" s="31" t="n">
+      <c r="G54" s="17" t="n">
         <v>235</v>
       </c>
-      <c r="H54" s="31" t="n">
+      <c r="H54" s="17" t="n">
         <v>66000</v>
       </c>
-      <c r="I54" s="31" t="n">
+      <c r="I54" s="17" t="n">
         <v>15510000</v>
       </c>
-      <c r="J54" s="31" t="n">
-        <v>26000</v>
-      </c>
-      <c r="K54" s="31" t="n">
-        <v>6110000</v>
-      </c>
-      <c r="L54" s="23" t="n">
-        <v>9400000</v>
-      </c>
-      <c r="M54" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N54" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J54" s="17" t="n">
+        <v>66000</v>
+      </c>
+      <c r="K54" s="17" t="n">
+        <v>15510000</v>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N54" s="16" t="inlineStr">
+        <is>
+          <t>4.90.80.030.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 435/2026/VH-VT4; 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="28" t="n">
+      <c r="A55" s="14" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="29" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>4.90.80.027.KOR.00.000</t>
         </is>
       </c>
-      <c r="C55" s="30" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>Nắp che phía cuối đường ray cáp điện (End cap)</t>
         </is>
       </c>
-      <c r="D55" s="30" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="E55" s="29" t="inlineStr">
+      <c r="E55" s="15" t="inlineStr">
         <is>
           <t>Eunchang/ Hàn Quốc</t>
         </is>
       </c>
-      <c r="F55" s="28" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G55" s="31" t="n">
+      <c r="G55" s="17" t="n">
         <v>32</v>
       </c>
-      <c r="H55" s="31" t="n">
+      <c r="H55" s="17" t="n">
         <v>68000</v>
       </c>
-      <c r="I55" s="31" t="n">
+      <c r="I55" s="17" t="n">
         <v>2176000</v>
       </c>
-      <c r="J55" s="31" t="n">
-        <v>21000</v>
-      </c>
-      <c r="K55" s="31" t="n">
-        <v>672000</v>
-      </c>
-      <c r="L55" s="23" t="n">
-        <v>1504000</v>
-      </c>
-      <c r="M55" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N55" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J55" s="17" t="n">
+        <v>68000</v>
+      </c>
+      <c r="K55" s="17" t="n">
+        <v>2176000</v>
+      </c>
+      <c r="L55" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N55" s="16" t="inlineStr">
+        <is>
+          <t>4.90.80.027.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 435/2026/VH-VT4; 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="28" t="n">
+      <c r="A56" s="14" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="29" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>2.08.37.001.KOR.97.000</t>
         </is>
       </c>
-      <c r="C56" s="30" t="inlineStr">
+      <c r="C56" s="16" t="inlineStr">
         <is>
           <t>Trolley-bar (thanh ray cấp nguồn)</t>
         </is>
       </c>
-      <c r="D56" s="30" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>Trolley-bar (thanh ray cấp nguồn):
 - Iđm: 60A;
@@ -6731,42 +5143,42 @@
 - Maker: EunchangT&amp;C</t>
         </is>
       </c>
-      <c r="E56" s="29" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr">
         <is>
           <t>Eunchang/ Hàn Quốc</t>
         </is>
       </c>
-      <c r="F56" s="28" t="inlineStr">
+      <c r="F56" s="14" t="inlineStr">
         <is>
           <t>Cây</t>
         </is>
       </c>
-      <c r="G56" s="31" t="n">
+      <c r="G56" s="17" t="n">
         <v>28</v>
       </c>
-      <c r="H56" s="31" t="n">
+      <c r="H56" s="17" t="n">
         <v>909000</v>
       </c>
-      <c r="I56" s="31" t="n">
+      <c r="I56" s="17" t="n">
         <v>25452000</v>
       </c>
-      <c r="J56" s="31" t="n">
-        <v>890000</v>
-      </c>
-      <c r="K56" s="31" t="n">
-        <v>24920000</v>
-      </c>
-      <c r="L56" s="23" t="n">
-        <v>532000</v>
-      </c>
-      <c r="M56" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N56" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J56" s="17" t="n">
+        <v>909000</v>
+      </c>
+      <c r="K56" s="17" t="n">
+        <v>25452000</v>
+      </c>
+      <c r="L56" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N56" s="16" t="inlineStr">
+        <is>
+          <t>2.08.37.001.KOR.97.000 | Sửa chữa tời điện Tời điện 15 tấn quạt gió 2B theo BBKT 435/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
@@ -6891,21 +5303,21 @@
       </c>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="28" t="n">
+      <c r="A59" s="14" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="29" t="inlineStr">
+      <c r="B59" s="15" t="inlineStr">
         <is>
           <t>3.34.20.133.CHN.99.000</t>
         </is>
       </c>
-      <c r="C59" s="30" t="inlineStr">
+      <c r="C59" s="16" t="inlineStr">
         <is>
           <t>Pendant control station:
 Type: XAC-A6913</t>
         </is>
       </c>
-      <c r="D59" s="30" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>Pendant control station:
 Type: XAC-A6913
@@ -6915,101 +5327,101 @@
 Color: Yellow</t>
         </is>
       </c>
-      <c r="E59" s="29" t="inlineStr">
+      <c r="E59" s="15" t="inlineStr">
         <is>
           <t>Schnerder/ Czech Republic</t>
         </is>
       </c>
-      <c r="F59" s="28" t="inlineStr">
+      <c r="F59" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G59" s="31" t="n">
+      <c r="G59" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H59" s="31" t="n">
+      <c r="H59" s="17" t="n">
         <v>13319000</v>
       </c>
-      <c r="I59" s="31" t="n">
+      <c r="I59" s="17" t="n">
         <v>13319000</v>
       </c>
-      <c r="J59" s="31" t="n">
-        <v>3290400</v>
-      </c>
-      <c r="K59" s="31" t="n">
-        <v>3290400</v>
-      </c>
-      <c r="L59" s="23" t="n">
-        <v>10028600</v>
-      </c>
-      <c r="M59" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N59" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J59" s="17" t="n">
+        <v>13319000</v>
+      </c>
+      <c r="K59" s="17" t="n">
+        <v>13319000</v>
+      </c>
+      <c r="L59" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 10 tấn quạt khói theo BBKT 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="28" t="n">
+      <c r="A60" s="14" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="29" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C60" s="30" t="inlineStr">
+      <c r="C60" s="16" t="inlineStr">
         <is>
           <t>Lưỡi gà móc cẩu 3 tấn</t>
         </is>
       </c>
-      <c r="D60" s="30" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>Lưỡi gà móc cẩu 3 tấn
 Kích thước: rộng 25mm x dài 60mm</t>
         </is>
       </c>
-      <c r="E60" s="29" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr">
         <is>
           <t>MT/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F60" s="28" t="inlineStr">
+      <c r="F60" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G60" s="31" t="n">
+      <c r="G60" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H60" s="31" t="n">
+      <c r="H60" s="17" t="n">
         <v>610000</v>
       </c>
-      <c r="I60" s="31" t="n">
+      <c r="I60" s="17" t="n">
         <v>610000</v>
       </c>
-      <c r="J60" s="31" t="n">
-        <v>314600</v>
-      </c>
-      <c r="K60" s="31" t="n">
-        <v>314600</v>
-      </c>
-      <c r="L60" s="23" t="n">
-        <v>295400</v>
-      </c>
-      <c r="M60" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N60" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J60" s="17" t="n">
+        <v>610000</v>
+      </c>
+      <c r="K60" s="17" t="n">
+        <v>610000</v>
+      </c>
+      <c r="L60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N60" s="16" t="inlineStr">
+        <is>
+          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
@@ -7131,121 +5543,121 @@
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="28" t="n">
+      <c r="A63" s="14" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="29" t="inlineStr">
+      <c r="B63" s="15" t="inlineStr">
         <is>
           <t>2.50.05.003.CHN.00.000</t>
         </is>
       </c>
-      <c r="C63" s="30" t="inlineStr">
+      <c r="C63" s="16" t="inlineStr">
         <is>
           <t>Cáp inox 304 
 Kích thước: Ø 3 mm</t>
         </is>
       </c>
-      <c r="D63" s="30" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>Cáp inox 304 
 Kích thước: Ø 3 mm</t>
         </is>
       </c>
-      <c r="E63" s="29" t="inlineStr">
+      <c r="E63" s="15" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F63" s="28" t="inlineStr">
+      <c r="F63" s="14" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G63" s="31" t="n">
+      <c r="G63" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="H63" s="31" t="n">
+      <c r="H63" s="17" t="n">
         <v>37000</v>
       </c>
-      <c r="I63" s="31" t="n">
+      <c r="I63" s="17" t="n">
         <v>2220000</v>
       </c>
-      <c r="J63" s="31" t="n">
-        <v>24000</v>
-      </c>
-      <c r="K63" s="31" t="n">
-        <v>1440000</v>
-      </c>
-      <c r="L63" s="23" t="n">
-        <v>780000</v>
-      </c>
-      <c r="M63" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N63" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J63" s="17" t="n">
+        <v>37000</v>
+      </c>
+      <c r="K63" s="17" t="n">
+        <v>2220000</v>
+      </c>
+      <c r="L63" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N63" s="16" t="inlineStr">
+        <is>
+          <t>2.50.05.003.CHN.00.000 | Sửa chữa Tời điện 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="28" t="n">
+      <c r="A64" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="29" t="inlineStr">
+      <c r="B64" s="15" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C64" s="30" t="inlineStr">
+      <c r="C64" s="16" t="inlineStr">
         <is>
           <t>Phe cài trục ngoài cho đường kính 28mm</t>
         </is>
       </c>
-      <c r="D64" s="30" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>Phe cài trục ngoài cho đường kính 28mm.
 Vật liệu: Inox 304</t>
         </is>
       </c>
-      <c r="E64" s="29" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F64" s="28" t="inlineStr">
+      <c r="F64" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G64" s="31" t="n">
+      <c r="G64" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H64" s="31" t="n">
+      <c r="H64" s="17" t="n">
         <v>56000</v>
       </c>
-      <c r="I64" s="31" t="n">
+      <c r="I64" s="17" t="n">
         <v>56000</v>
       </c>
-      <c r="J64" s="31" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K64" s="31" t="n">
-        <v>50000</v>
-      </c>
-      <c r="L64" s="23" t="n">
-        <v>6000</v>
-      </c>
-      <c r="M64" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N64" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J64" s="17" t="n">
+        <v>56000</v>
+      </c>
+      <c r="K64" s="17" t="n">
+        <v>56000</v>
+      </c>
+      <c r="L64" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N64" s="16" t="inlineStr">
+        <is>
+          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
@@ -7566,22 +5978,22 @@
       </c>
     </row>
     <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="28" t="n">
+      <c r="A70" s="14" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="29" t="inlineStr">
+      <c r="B70" s="15" t="inlineStr">
         <is>
           <t>2.06.60.080.TPE.00.000</t>
         </is>
       </c>
-      <c r="C70" s="30" t="inlineStr">
+      <c r="C70" s="16" t="inlineStr">
         <is>
           <t>Kẹp cố định đầu ray
 Loại: CH2260
 Size: 80x51x3mm</t>
         </is>
       </c>
-      <c r="D70" s="30" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>Kẹp cố định đầu ray
 Loại: CH2260
@@ -7590,42 +6002,42 @@
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="E70" s="29" t="inlineStr">
+      <c r="E70" s="15" t="inlineStr">
         <is>
           <t>ITS/ Đài Loan</t>
         </is>
       </c>
-      <c r="F70" s="28" t="inlineStr">
+      <c r="F70" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G70" s="31" t="n">
+      <c r="G70" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="H70" s="31" t="n">
+      <c r="H70" s="17" t="n">
         <v>2254000</v>
       </c>
-      <c r="I70" s="31" t="n">
+      <c r="I70" s="17" t="n">
         <v>4508000</v>
       </c>
-      <c r="J70" s="31" t="n">
-        <v>578078</v>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>1156156</v>
-      </c>
-      <c r="L70" s="23" t="n">
-        <v>3351844</v>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N70" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J70" s="17" t="n">
+        <v>2254000</v>
+      </c>
+      <c r="K70" s="17" t="n">
+        <v>4508000</v>
+      </c>
+      <c r="L70" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N70" s="16" t="inlineStr">
+        <is>
+          <t>2.06.60.080.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
@@ -7692,22 +6104,22 @@
       </c>
     </row>
     <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="28" t="n">
+      <c r="A72" s="14" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="29" t="inlineStr">
+      <c r="B72" s="15" t="inlineStr">
         <is>
           <t>3.15.44.076.CHN.00.000</t>
         </is>
       </c>
-      <c r="C72" s="30" t="inlineStr">
+      <c r="C72" s="16" t="inlineStr">
         <is>
           <t>Cáp điện dẹt cho cầu trục
 Quy cách: 16mm2 x 4C
 Ruột mềm</t>
         </is>
       </c>
-      <c r="D72" s="30" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>Cáp điện dẹt cho cầu trục
 Quy cách: 16mm2 x 4C
@@ -7717,299 +6129,299 @@
 NSX: Imatek</t>
         </is>
       </c>
-      <c r="E72" s="29" t="inlineStr">
+      <c r="E72" s="15" t="inlineStr">
         <is>
           <t>Imatek/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F72" s="28" t="inlineStr">
+      <c r="F72" s="14" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="G72" s="31" t="n">
+      <c r="G72" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="H72" s="31" t="n">
+      <c r="H72" s="17" t="n">
         <v>711000</v>
       </c>
-      <c r="I72" s="31" t="n">
+      <c r="I72" s="17" t="n">
         <v>35550000</v>
       </c>
-      <c r="J72" s="31" t="n">
-        <v>76000</v>
-      </c>
-      <c r="K72" s="31" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="L72" s="23" t="n">
-        <v>31750000</v>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N72" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J72" s="17" t="n">
+        <v>711000</v>
+      </c>
+      <c r="K72" s="17" t="n">
+        <v>35550000</v>
+      </c>
+      <c r="L72" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N72" s="16" t="inlineStr">
+        <is>
+          <t>3.15.44.076.CHN.00.000 | Sửa chữa Tời điện 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="28" t="n">
+      <c r="A73" s="14" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="29" t="inlineStr">
+      <c r="B73" s="15" t="inlineStr">
         <is>
           <t>3.20.22.003.TPE.00.000</t>
         </is>
       </c>
-      <c r="C73" s="30" t="inlineStr">
+      <c r="C73" s="16" t="inlineStr">
         <is>
           <t>Khóa cáp 
 Dùng cho cáp: 3mm</t>
         </is>
       </c>
-      <c r="D73" s="30" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>Khóa cáp 
 Dùng cho cáp: 3mm</t>
         </is>
       </c>
-      <c r="E73" s="29" t="inlineStr">
+      <c r="E73" s="15" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F73" s="28" t="inlineStr">
+      <c r="F73" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G73" s="31" t="n">
+      <c r="G73" s="17" t="n">
         <v>55</v>
       </c>
-      <c r="H73" s="31" t="n">
+      <c r="H73" s="17" t="n">
         <v>20000</v>
       </c>
-      <c r="I73" s="31" t="n">
+      <c r="I73" s="17" t="n">
         <v>1100000</v>
       </c>
-      <c r="J73" s="31" t="n">
-        <v>14000</v>
-      </c>
-      <c r="K73" s="31" t="n">
-        <v>770000</v>
-      </c>
-      <c r="L73" s="23" t="n">
-        <v>330000</v>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N73" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J73" s="17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K73" s="17" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="L73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N73" s="16" t="inlineStr">
+        <is>
+          <t>3.20.22.003.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
     <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="28" t="n">
+      <c r="A74" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="29" t="inlineStr">
+      <c r="B74" s="15" t="inlineStr">
         <is>
           <t>3.34.20.130.CHN.99.000</t>
         </is>
       </c>
-      <c r="C74" s="30" t="inlineStr">
+      <c r="C74" s="16" t="inlineStr">
         <is>
           <t>Pendant control station (Tay bấm điều khiển tời điện): 
 - Type: XAC-A6713</t>
         </is>
       </c>
-      <c r="D74" s="30" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>Pendant control station (Tay bấm điều khiển tời điện): 
 - Type: XAC-A6713
 Control station composition: 06, push buttons + 01 emergency stop</t>
         </is>
       </c>
-      <c r="E74" s="29" t="inlineStr">
+      <c r="E74" s="15" t="inlineStr">
         <is>
           <t>Schnerder/ Czech Republic</t>
         </is>
       </c>
-      <c r="F74" s="28" t="inlineStr">
+      <c r="F74" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G74" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="31" t="n">
+      <c r="H74" s="17" t="n">
         <v>7406000</v>
       </c>
-      <c r="I74" s="31" t="n">
+      <c r="I74" s="17" t="n">
         <v>7406000</v>
       </c>
-      <c r="J74" s="31" t="n">
-        <v>3310185</v>
-      </c>
-      <c r="K74" s="31" t="n">
-        <v>3310185</v>
-      </c>
-      <c r="L74" s="23" t="n">
-        <v>4095815</v>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N74" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J74" s="17" t="n">
+        <v>7406000</v>
+      </c>
+      <c r="K74" s="17" t="n">
+        <v>7406000</v>
+      </c>
+      <c r="L74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N74" s="16" t="inlineStr">
+        <is>
+          <t>3.34.20.130.CHN.99.000 | Sửa chữa Tời điện Tời điện 3 tấn máy nén khí turbine theo BBKT 624/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="28" t="n">
+      <c r="A75" s="14" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="29" t="inlineStr">
+      <c r="B75" s="15" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C75" s="16" t="inlineStr">
         <is>
           <t>Lưỡi gà móc cẩu 7 tấn</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>Lưỡi gà móc cẩu 7 tấn:
  + Kích thước: 60 x 175x 3mm
  + Vật liệu: thép</t>
         </is>
       </c>
-      <c r="E75" s="29" t="inlineStr">
+      <c r="E75" s="15" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F75" s="28" t="inlineStr">
+      <c r="F75" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G75" s="31" t="n">
+      <c r="G75" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="31" t="n">
+      <c r="H75" s="17" t="n">
         <v>656000</v>
       </c>
-      <c r="I75" s="31" t="n">
+      <c r="I75" s="17" t="n">
         <v>656000</v>
       </c>
-      <c r="J75" s="31" t="n">
-        <v>585000</v>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>585000</v>
-      </c>
-      <c r="L75" s="23" t="n">
-        <v>71000</v>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N75" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J75" s="17" t="n">
+        <v>656000</v>
+      </c>
+      <c r="K75" s="17" t="n">
+        <v>656000</v>
+      </c>
+      <c r="L75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N75" s="16" t="inlineStr">
+        <is>
+          <t>Chưa có mã | Sửa chữa tời điên Cầu trục 7 tấn lưới quay rác trạm bơm tuần hoàn theo BBKT 432/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="28" t="n">
+      <c r="A76" s="14" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B76" s="15" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C76" s="16" t="inlineStr">
         <is>
           <t>Sơn dầu Jotun chống sét Green 437</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>Sơn dầu Jotun chống sét Green 437</t>
         </is>
       </c>
-      <c r="E76" s="29" t="inlineStr">
+      <c r="E76" s="15" t="inlineStr">
         <is>
           <t>Kungho/ Trung Quốc</t>
         </is>
       </c>
-      <c r="F76" s="28" t="inlineStr">
+      <c r="F76" s="14" t="inlineStr">
         <is>
           <t>Lít</t>
         </is>
       </c>
-      <c r="G76" s="31" t="n">
+      <c r="G76" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="H76" s="31" t="n">
+      <c r="H76" s="17" t="n">
         <v>625000</v>
       </c>
-      <c r="I76" s="31" t="n">
+      <c r="I76" s="17" t="n">
         <v>12500000</v>
       </c>
-      <c r="J76" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="23" t="n">
+      <c r="J76" s="17" t="n">
+        <v>625000</v>
+      </c>
+      <c r="K76" s="17" t="n">
         <v>12500000</v>
       </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N76" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="L76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N76" s="16" t="inlineStr">
+        <is>
+          <t>Chưa có mã | Sửa chữa tời điên Cầu trục 7 tấn lưới quay rác trạm bơm tuần hoàn theo BBKT 432/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
         </is>
       </c>
     </row>
     <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="28" t="n">
+      <c r="A77" s="14" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B77" s="15" t="inlineStr">
         <is>
           <t>3.82.63.103.LTU.00.000</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C77" s="16" t="inlineStr">
         <is>
           <t>Đế gắn module IO HBS 01 - FPN</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>Đế gắn module IO:
 - Hãng: ABB
@@ -8017,60 +6429,60 @@
 - PR (Product Revision): M</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E77" s="15" t="inlineStr">
         <is>
           <t>ABB/ Lithuania</t>
         </is>
       </c>
-      <c r="F77" s="28" t="inlineStr">
+      <c r="F77" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G77" s="31" t="n">
+      <c r="G77" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="H77" s="31" t="n">
+      <c r="H77" s="17" t="n">
         <v>21120000</v>
       </c>
-      <c r="I77" s="31" t="n">
+      <c r="I77" s="17" t="n">
         <v>633600000</v>
       </c>
-      <c r="J77" s="31" t="n">
-        <v>19360000</v>
-      </c>
-      <c r="K77" s="31" t="n">
-        <v>580800000</v>
-      </c>
-      <c r="L77" s="23" t="n">
-        <v>52800000</v>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N77" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="J77" s="17" t="n">
+        <v>21120000</v>
+      </c>
+      <c r="K77" s="17" t="n">
+        <v>633600000</v>
+      </c>
+      <c r="L77" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N77" s="16" t="inlineStr">
+        <is>
+          <t>3.82.63.103.LTU.00.000 | Dự phòng thay thế cho các đế module IO hệ thống DCS ABB tổ máy S1, S2, S3 và COM suy giảm điện dung  | Vật tư không có trong KHSXKD 2026</t>
         </is>
       </c>
     </row>
     <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="28" t="n">
+      <c r="A78" s="14" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="29" t="inlineStr">
+      <c r="B78" s="15" t="inlineStr">
         <is>
           <t>3.94.00.808.MLT.00.000</t>
         </is>
       </c>
-      <c r="C78" s="30" t="inlineStr">
+      <c r="C78" s="16" t="inlineStr">
         <is>
           <t>Đế gắn module IO HBS01-FPH</t>
         </is>
       </c>
-      <c r="D78" s="30" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>Đế gắn module IO:
 - Hãng: ABB
@@ -8078,42 +6490,42 @@
 - PR (Product Revision): M</t>
         </is>
       </c>
-      <c r="E78" s="29" t="inlineStr">
+      <c r="E78" s="15" t="inlineStr">
         <is>
           <t>ABB/ Lithuania</t>
         </is>
       </c>
-      <c r="F78" s="28" t="inlineStr">
+      <c r="F78" s="14" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="G78" s="31" t="n">
+      <c r="G78" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="H78" s="31" t="n">
+      <c r="H78" s="17" t="n">
         <v>21120000</v>
       </c>
-      <c r="I78" s="31" t="n">
+      <c r="I78" s="17" t="n">
         <v>549120000</v>
       </c>
-      <c r="J78" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="23" t="n">
+      <c r="J78" s="17" t="n">
+        <v>21120000</v>
+      </c>
+      <c r="K78" s="17" t="n">
         <v>549120000</v>
       </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>ĐÃ CHỐT</t>
-        </is>
-      </c>
-      <c r="N78" s="33" t="inlineStr">
-        <is>
-          <t>Chi tiết xem sheet Hồ sơ chứng cứ &amp; Hình ảnh</t>
+      <c r="L78" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="14" t="inlineStr">
+        <is>
+          <t>Đang rà soát</t>
+        </is>
+      </c>
+      <c r="N78" s="16" t="inlineStr">
+        <is>
+          <t>3.94.00.808.MLT.00.000 | Dự phòng thay thế cho các đế module IO hệ thống DCS ABB tổ máy S1, S2, S3 và COM suy giảm điện dung | Vật tư không có trong KHSXKD 2026</t>
         </is>
       </c>
     </row>
@@ -8159,10 +6571,10 @@
         <v>183500000</v>
       </c>
       <c r="J79" s="17" t="n">
-        <v>18350000</v>
+        <v>21120000</v>
       </c>
       <c r="K79" s="17" t="n">
-        <v>183500000</v>
+        <v>211200000</v>
       </c>
       <c r="L79" s="17" t="n">
         <v>0</v>
@@ -8593,13 +7005,13 @@
         <v>5236608000</v>
       </c>
       <c r="J86" s="31" t="n">
-        <v>1845000000</v>
+        <v>1300000</v>
       </c>
       <c r="K86" s="31" t="n">
-        <v>3690000000</v>
+        <v>2600000</v>
       </c>
       <c r="L86" s="23" t="n">
-        <v>1546608000</v>
+        <v>5234008000</v>
       </c>
       <c r="M86" s="32" t="inlineStr">
         <is>
@@ -10409,10 +8821,10 @@
       </c>
       <c r="J117" s="35" t="n"/>
       <c r="K117" s="36" t="n">
-        <v>34779577092.5</v>
+        <v>32385281416.5</v>
       </c>
       <c r="L117" s="37" t="n">
-        <v>3425998907.5</v>
+        <v>5937874583.5</v>
       </c>
       <c r="M117" s="35" t="n"/>
       <c r="N117" s="35" t="n"/>
@@ -10433,36 +8845,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N102" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N102" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10474,7 +8860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10590,12 +8976,12 @@
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đơn giá trình (13,559,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 1). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 16,000,000 </t>
+          <t>Đơn giá trình (13,559,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 1). Ngoài ra còn có: CÔNG TY CỔ PHẦN CÔNG NGHỆ CƠ ĐIỆN EME báo giá 15,592,850 đ (+15.0%)</t>
         </is>
       </c>
       <c r="G5" s="40" t="inlineStr">
         <is>
-          <t>Vật tư có 2 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 11.842.500 đ/Cái (dao động từ 6.015.000 đ đến 17.670.000 đ). Đơn giá trình đợt này là 13.559.000 đ/Cái (+14.5% s</t>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 6.015.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 115/2023. Ttr 2562/KHVT) theo hóa đơn số 00000041. 42. 43. 44. 45. 46 ngày 30.08.2024 ngày 2024-10-31. SL: 117 Cái); Các đợt nhập khác: 17.670.00</t>
         </is>
       </c>
       <c r="H5" s="40" t="inlineStr">
@@ -10611,9 +8997,8 @@
       <c r="J5" s="40" t="inlineStr"/>
       <c r="K5" s="41" t="inlineStr">
         <is>
-          <t>Đơn giá chốt: 11.842.500 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
-(Tiết kiệm: 6.866.000 đ)</t>
+          <t>Đơn giá chốt: 6.015.000 đ
+(Tiết kiệm: 30.176.000 đ)</t>
         </is>
       </c>
     </row>
@@ -10662,7 +9047,6 @@
       <c r="K6" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 7.000.000 đ
-(Cơ sở 2: Lịch sử mua sắm ERP Vĩnh Tân 4 (QĐ 161))
 (Tiết kiệm: 7.208.000 đ)</t>
         </is>
       </c>
@@ -10723,7 +9107,6 @@
       <c r="K7" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 16.491.600 đ
-(Cơ sở 5: Tham khảo TMĐT / Giá Web (Landed Cost DDP VT4))
 (Tiết kiệm: 197.542.000 đ)</t>
         </is>
       </c>
@@ -10785,7 +9168,6 @@
       <c r="K8" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 9.009.300 đ
-(Cơ sở 5: Tham khảo TMĐT / Giá Web)
 (Tiết kiệm: 274.953.500 đ)</t>
         </is>
       </c>
@@ -10843,7 +9225,6 @@
       <c r="K9" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 1.500.000 đ
-(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 0 đ)</t>
         </is>
       </c>
@@ -10901,7 +9282,6 @@
       <c r="K10" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 8.910.000 đ
-(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 52.340.000 đ)</t>
         </is>
       </c>
@@ -10953,7 +9333,7 @@
       </c>
       <c r="I11" s="40" t="inlineStr">
         <is>
-          <t>Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khó</t>
+          <t>Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [KMX], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CS</t>
         </is>
       </c>
       <c r="J11" s="40" t="inlineStr">
@@ -10964,7 +9344,6 @@
       <c r="K11" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 452.147.000 đ
-(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 0 đ)</t>
         </is>
       </c>
@@ -11030,7 +9409,6 @@
       <c r="K12" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 620.000 đ
-(Cơ sở 2: Lịch sử mua sắm ERP Vĩnh Tân 4 (HĐ 03/2022))
 (Tiết kiệm: 3.840.000 đ)</t>
         </is>
       </c>
@@ -11092,7 +9470,6 @@
       <c r="K13" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 1.315.000 đ
-(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 0 đ)</t>
         </is>
       </c>
@@ -11154,7 +9531,6 @@
       <c r="K14" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 1.508.000 đ
-(Cơ sở 1: Báo giá nộp kèm)
 (Tiết kiệm: 0 đ)</t>
         </is>
       </c>
@@ -11224,7 +9600,6 @@
       <c r="K15" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 113.232.916 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
 (Tiết kiệm: 4.367.084 đ)</t>
         </is>
       </c>
@@ -11235,15 +9610,13 @@
       </c>
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t>Chưa có mã vật tư</t>
+          <t>2.46.35.037.CHN.00.000</t>
         </is>
       </c>
       <c r="C16" s="40" t="inlineStr">
         <is>
-          <t>Thanh cái đồng V phân phối mạ bạc
-(Thanh cái đồng V phân phối mạ bạc
-Kích thước: 28x40x6mm
-Chiều dài: 920mm)</t>
+          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m
+(Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m)</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
@@ -11258,34 +9631,33 @@
       </c>
       <c r="F16" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (48,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 3). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 50,200,000 đ (+4.6%)</t>
+          <t>Đơn giá trình (19,300,000 đ) không trùng với báo giá nào. Trong đó đơn giá thấp nhất thu thập được là 18,522,000 đ của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf).</t>
         </is>
       </c>
       <c r="G16" s="40" t="inlineStr">
         <is>
+          <t>Vật tư có 2 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 21.200.000 đ/Cái (dao động từ 17.500.000 đ đến 24.900.000 đ). Đơn giá trình đợt này là 19.300.000 đ/Cái (-9.0% s</t>
+        </is>
+      </c>
+      <c r="H16" s="40" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [28x40x6], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện tron</t>
-        </is>
-      </c>
       <c r="I16" s="40" t="inlineStr">
         <is>
-          <t>Đã tra cứu từ khóa [Thanh cái đồng V phân phối mạ bạc] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:20 ngày 09/09/2026 nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
+          <t>Đã tra cứu từ khóa [SS-T6-S-065-20] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 17:27 ngày 08/09/2026; ghi nhận mức giá trúng thầu tham chiếu là 27.390.000 đ (Mã TBMT: IB2400452305, Bên mời thầu: NHÀ MÁY NHIỆ</t>
         </is>
       </c>
       <c r="J16" s="40" t="inlineStr">
         <is>
-          <t>Đã tra cứu từ khóa [Thanh cái đồng V phân phối mạ bạc] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không n</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K16" s="41" t="inlineStr">
         <is>
-          <t>Đơn giá chốt: 1.390.909 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
-(Tiết kiệm: 186.436.364 đ)</t>
+          <t>Đơn giá chốt: 18.522.000 đ
+(Tiết kiệm: 27.230.000 đ)</t>
         </is>
       </c>
     </row>
@@ -11295,13 +9667,14 @@
       </c>
       <c r="B17" s="39" t="inlineStr">
         <is>
-          <t>2.46.35.037.CHN.00.000</t>
+          <t>3.96.13.320.USA.00.000</t>
         </is>
       </c>
       <c r="C17" s="40" t="inlineStr">
         <is>
-          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m
-(Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m)</t>
+          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
+(Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
+NSX: MERRICK)</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
@@ -11316,22 +9689,22 @@
       </c>
       <c r="F17" s="40" t="inlineStr">
         <is>
-          <t>Đơn giá trình (19,300,000 đ) không trùng với báo giá nào. Trong đó đơn giá thấp nhất thu thập được là 18,522,000 đ của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf).</t>
+          <t>Đơn giá trình (56,105,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 4). Ngoài ra còn có: CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN H</t>
         </is>
       </c>
       <c r="G17" s="40" t="inlineStr">
         <is>
-          <t>Vật tư có 2 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 21.200.000 đ/Cái (dao động từ 17.500.000 đ đến 24.900.000 đ). Đơn giá trình đợt này là 19.300.000 đ/Cái (-9.0% s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H17" s="40" t="inlineStr">
         <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [SS-T6-S-065-20], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát đi</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I17" s="40" t="inlineStr">
         <is>
-          <t>Đã tra cứu từ khóa [SS-T6-S-065-20] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 17:27 ngày 08/09/2026; ghi nhận mức giá trúng thầu tham chiếu là 27.390.000 đ (Mã TBMT: IB2400452305, Bên mời thầu: NHÀ MÁY NHIỆ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" s="40" t="inlineStr">
@@ -11341,9 +9714,8 @@
       </c>
       <c r="K17" s="41" t="inlineStr">
         <is>
-          <t>Đơn giá chốt: 18.522.000 đ
-(Cơ sở 1: Báo giá nộp kèm)
-(Tiết kiệm: 27.230.000 đ)</t>
+          <t>Đơn giá chốt: 23.000.000 đ
+(Tiết kiệm: 66.210.000 đ)</t>
         </is>
       </c>
     </row>
@@ -11353,1448 +9725,10 @@
       </c>
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t>2.46.35.019.CHN.00.000</t>
+          <t>Chưa có mã vật tư</t>
         </is>
       </c>
       <c r="C18" s="40" t="inlineStr">
-        <is>
-          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m
-(Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m)</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E18" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (19,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
-        </is>
-      </c>
-      <c r="G18" s="40" t="inlineStr">
-        <is>
-          <t>Vật tư có 2 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 12.350.000 đ/Cái (dao động từ 5.400.000 đ đến 19.300.000 đ). Đơn giá trình đợt này là 19.000.000 đ/Cái (+53.8% s</t>
-        </is>
-      </c>
-      <c r="H18" s="40" t="inlineStr"/>
-      <c r="I18" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [SS-T8-S-065-20] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:43 ngày 09/09/2026; ghi nhận mức giá trúng thầu tham chiếu là 21.230.000 đ (Mã TBMT: IB2400452305, Bên mời thầu: NHÀ MÁY NHIỆ</t>
-        </is>
-      </c>
-      <c r="J18" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [SS-T8-S-065-20] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thư</t>
-        </is>
-      </c>
-      <c r="K18" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 12.350.000 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
-(Tiết kiệm: 13.300.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t>4.82.22.013.USA.00.000</t>
-        </is>
-      </c>
-      <c r="C19" s="40" t="inlineStr">
-        <is>
-          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6
-(Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6)</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E19" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (1,700,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 2,150,000 đ (+26.</t>
-        </is>
-      </c>
-      <c r="G19" s="40" t="inlineStr">
-        <is>
-          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:03/2022) theo hóa đơn số 00000017 ngày 04.03.2022 (ngày ký 2022-03-07 00:00:00, do Nhập kho vật tư (HĐ:03/2022) theo hóa đơn số 00000017 ngày 04.</t>
-        </is>
-      </c>
-      <c r="H19" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [SS-810-6], vật tư có lịch sử mua sắm tương đương tại Công ty Dịch vụ sửa chữa các nhà máy điện EVNGENCO3 (t</t>
-        </is>
-      </c>
-      <c r="I19" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [SS-810-6] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:46 ngày 09/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 1.319.000 đ (Mã TBMT: IB2600209753, Bên mời thầu: CÔNG TY N</t>
-        </is>
-      </c>
-      <c r="J19" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các t</t>
-        </is>
-      </c>
-      <c r="K19" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 1.319.000 đ
-(Cơ sở 4: Mua Sắm Công e-GP)
-(Tiết kiệm: 762.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="110" customHeight="1">
-      <c r="A20" s="38" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>4.82.22.025.CHN.00.000</t>
-        </is>
-      </c>
-      <c r="C20" s="40" t="inlineStr">
-        <is>
-          <t>Đầu nối - Union Swagelok Model: SS-600-6
-(Đầu nối - Union Swagelok Model: SS-600-6)</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr"/>
-      <c r="E20" s="42" t="inlineStr">
-        <is>
-          <t>Mở liên kết trực tuyến ↗</t>
-        </is>
-      </c>
-      <c r="F20" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (2,600,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LO</t>
-        </is>
-      </c>
-      <c r="G20" s="40" t="inlineStr">
-        <is>
-          <t>Vật tư có lịch sử nhập kho theo Nhập kho vật tư (HĐ: 25/2025) theo hóa đơn số 00000091 ngày 24.06.2025 (ngày ký 2025-07-24 00:00:00) với đơn giá 2.600.000 đ/Cái (Tổng số 6 đợt mua sắm lịch sử có đơn giá dao động từ 630.0</t>
-        </is>
-      </c>
-      <c r="H20" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [SS-600-6], vật tư có lịch sử mua sắm tương đương tại GENCO1 - Công ty Nhiệt Điện Nghi Sơn (thời gian N/A) v</t>
-        </is>
-      </c>
-      <c r="I20" s="40" t="inlineStr"/>
-      <c r="J20" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [Đầu nối - Union Swagelok Model: SS-600-6 - Đầu nối - Union Swagelok Model: SS-600-6] trên thị trường Thương mại điện tử / Website nhà cung cấp (Ảnh chụp màn hình web) tại đường link [https://www.ebay.</t>
-        </is>
-      </c>
-      <c r="K20" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 644.760 đ
-(Cơ sở 3: EVN IMIS)
-(Tiết kiệm: 195.524.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="38" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t>5.33.70.184.GER.99.000</t>
-        </is>
-      </c>
-      <c r="C21" s="40" t="inlineStr">
-        <is>
-          <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001
-(Bộ điều khiển định vị Positioner:
-- Model: TZIDC-V18345- 2020521001
--Type: Double acting 
--Sofw.Rev: 3 
--Supply press: 1,4 ~ 6 bar 
--Input: Analog 4 ~ 20 mA
- -Loss of electric: Fail freeze
-- Option: Analog feedback, FSK, Position indicator 
--NSX: ABB)</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E21" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (85,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 4). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
-        </is>
-      </c>
-      <c r="G21" s="40" t="inlineStr">
-        <is>
-          <t>Vật tư có lịch sử nhập kho gần nhất tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:37/2026) hóa đơn số 00000035 ngày 28.05.2026 (ngày ký 2026-06-03 00:00:00, do Nhập kho vật tư (HĐ:37/2026) hóa đơn số 00000035 ngày 28.05.2</t>
-        </is>
-      </c>
-      <c r="H21" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [TZIDC], vật tư có lịch sử mua sắm tương đương tại Công ty Nhiệt điện Cần Thơ (thời gian N/A) với đơn giá 83</t>
-        </is>
-      </c>
-      <c r="I21" s="40" t="inlineStr"/>
-      <c r="J21" s="40" t="inlineStr"/>
-      <c r="K21" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 83.484.000 đ
-(Cơ sở 3: EVN IMIS)
-(Tiết kiệm: 7.580.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="38" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t>3.96.13.144.USA.00.000</t>
-        </is>
-      </c>
-      <c r="C22" s="40" t="inlineStr">
-        <is>
-          <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire
-(Cảm biến nhiệt độ - Model: S14405PD3S350B0
-- NSX: MINCO 
-- Element: Platinum 
-- Element length: 6.4 mm 
-- Cable dimension "C": 1778 mm 
-- Cable dimension "L": 8890 mm 
-- Single duplex: Duplex 
-- Sheath: 2.9 mm OD 
-- Type: RTD PT100, 3 Wire 
-- Range: 0 - 260 °C)</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E22" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (30,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 5). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
-        </is>
-      </c>
-      <c r="G22" s="40" t="inlineStr">
-        <is>
-          <t>Vật tư có lịch sử nhập kho gần nhất tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:36/2026) theo hóa đơn số 00000842 ngày 15.06.2026 (ngày ký 2026-07-22 00:00:00, do Nhập kho vật tư (HĐ:36/2026) theo hóa đơn số 00000842 ng</t>
-        </is>
-      </c>
-      <c r="H22" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [RTD PT100], vật tư có lịch sử mua sắm tương đương tại Công ty Cổ phần Thủy điện Thác Mơ (thời gian N/A) </t>
-        </is>
-      </c>
-      <c r="I22" s="40" t="inlineStr"/>
-      <c r="J22" s="40" t="inlineStr"/>
-      <c r="K22" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 27.923.445 đ
-(Cơ sở 4: Mua Sắm Công e-GP)
-(Tiết kiệm: 2.076.555 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="110" customHeight="1">
-      <c r="A23" s="38" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C23" s="40" t="inlineStr">
-        <is>
-          <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm)
-(LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
-Model: LST400 Y0/S15/N1/P6/A1/H1/SC6/B2/CR/M5
-Range: 0.5m to 15m Signal: 4 - 20 mA 
-Supply power: 115 to 230 V AC or 24 V DC.
-NSX: ABB)</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr"/>
-      <c r="E23" s="42" t="inlineStr">
-        <is>
-          <t>Mở liên kết trực tuyến ↗</t>
-        </is>
-      </c>
-      <c r="F23" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đơn giá trình (189,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 5). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG </t>
-        </is>
-      </c>
-      <c r="G23" s="40" t="inlineStr">
-        <is>
-          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:233) theo hóa đơn số 0000216 ngày 30.03.2021 (ngày ký 2021-04-28 00:00:00, do Nhập kho vật tư (HĐ:233) theo hóa đơn số 0000216 ngày 30.03.2021 cu</t>
-        </is>
-      </c>
-      <c r="H23" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [LST400], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong</t>
-        </is>
-      </c>
-      <c r="I23" s="40" t="inlineStr"/>
-      <c r="J23" s="40" t="inlineStr"/>
-      <c r="K23" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 58.423.000 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
-(Tiết kiệm: 130.577.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="110" customHeight="1">
-      <c r="A24" s="38" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="39" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C24" s="40" t="inlineStr">
-        <is>
-          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
-(Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
-Model: MA3145-230-2-R
-- Điện áp hoạt động tối đa (Max working voltage): ≥ 270 VAC.
-- Điện áp định mức (Voltage rating): 230 VAC.
-- Dòng cắt sét / Khả năng chịu dòng ngắn mạch (Circuit breaker / Surge capacity): ≥ 40 kA.
-NSX: Cooper Crouse-Hinds MTL / Eaton)</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr"/>
-      <c r="E24" s="42" t="inlineStr">
-        <is>
-          <t>Mở liên kết trực tuyến ↗</t>
-        </is>
-      </c>
-      <c r="F24" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (35,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 7). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
-        </is>
-      </c>
-      <c r="G24" s="40" t="inlineStr">
-        <is>
-          <t>Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4, các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn g</t>
-        </is>
-      </c>
-      <c r="H24" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 09/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [MA3145], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong</t>
-        </is>
-      </c>
-      <c r="I24" s="40" t="inlineStr">
-        <is>
-          <t>Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [MTL], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CS</t>
-        </is>
-      </c>
-      <c r="J24" s="40" t="inlineStr"/>
-      <c r="K24" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 21.609.600 đ
-(Cơ sở 5: Tham khảo TMĐT / Giá Web)
-(Tiết kiệm: 40.171.200 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="38" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="39" t="inlineStr">
-        <is>
-          <t>3.34.40.009.IND.00.000</t>
-        </is>
-      </c>
-      <c r="C25" s="40" t="inlineStr">
-        <is>
-          <t>Công tắc lưu lượng (Flow Switch)
-(Công tắc lưu lượng (Flow Switch)
-Model: WP/FS-25VFL
-Switch : SPDT Snap Acting Micro
-Rating : 5A 250VAC 
-NSX: Dag Process Instruments Pvt. Ltd)</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E25" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (38,000,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO GIÁ An Hiếu fn.pdf, Trang 8). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG L</t>
-        </is>
-      </c>
-      <c r="G25" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 32.500.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 12/2025) theo hóa đơn số 00000036 ngày 24.03.2025 ngày 2025-03-27. SL: 1 Cái)</t>
-        </is>
-      </c>
-      <c r="H25" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu CSDL EVN IMIS theo từ khóa [Công tắc lưu lượng], các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán nên thẩm định viên không áp dụng làm căn cứ thẩm định.</t>
-        </is>
-      </c>
-      <c r="I25" s="40" t="inlineStr"/>
-      <c r="J25" s="40" t="inlineStr"/>
-      <c r="K25" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 32.500.000 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
-(Tiết kiệm: 5.500.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="110" customHeight="1">
-      <c r="A26" s="38" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="39" t="inlineStr">
-        <is>
-          <t>3.96.13.165.KOR.00.000</t>
-        </is>
-      </c>
-      <c r="C26" s="40" t="inlineStr">
-        <is>
-          <t>Cảm biến tiệm cận/proximity sensor
-(Cảm biến tiệm cận/proximity sensor
-- Model: PR30-10AC
-Đường kính cạnh phát hiện: 30mm
-- Điện áp hoạt động: 100-240 Vac
-- Ngõ ra điều khiển: NC
-- Protection: IP67)</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr"/>
-      <c r="E26" s="42" t="inlineStr">
-        <is>
-          <t>Mở liên kết trực tuyến ↗</t>
-        </is>
-      </c>
-      <c r="F26" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (1,219,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 6). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 2,000,000 đ (+64.1%).</t>
-        </is>
-      </c>
-      <c r="G26" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 598.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:123/2022) theo hóa đơn số 993. 994 ngày 26.12.2022 ngày 2022-12-27. SL: 1 Cái)</t>
-        </is>
-      </c>
-      <c r="H26" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 10/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [PR30], vật tư có lịch sử mua sắm tương đương tại Công ty Nhiệt điện Mông Dương (thời gian N/A) với đơn giá </t>
-        </is>
-      </c>
-      <c r="I26" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [Autonics] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 08:23 ngày 10/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 382.320 đ (Mã TBMT: IB2600205775, Bên mời thầu: CÔNG TY THỦ</t>
-        </is>
-      </c>
-      <c r="J26" s="40" t="inlineStr"/>
-      <c r="K26" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 911.127 đ
-(Cơ sở 3: EVN IMIS)
-(Tiết kiệm: 615.746 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="110" customHeight="1">
-      <c r="A27" s="38" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="39" t="inlineStr">
-        <is>
-          <t>3.96.13.114.KOR.99.000</t>
-        </is>
-      </c>
-      <c r="C27" s="40" t="inlineStr">
-        <is>
-          <t>Cảm biến tiệm cận/proximity sensor
-(Cảm biến tiệm cận/proximity sensor
-- Model: PR18-8AO
-- Đường kính đầu dò: 18mm
-- Điện áp hoạt động: 100-240 Vac
-- Ngõ ra điều khiển: NO
-- Protection: IP67)</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr"/>
-      <c r="E27" s="42" t="inlineStr">
-        <is>
-          <t>Mở liên kết trực tuyến ↗</t>
-        </is>
-      </c>
-      <c r="F27" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (1,150,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 1,600,000 đ (+39.1%).</t>
-        </is>
-      </c>
-      <c r="G27" s="40" t="inlineStr">
-        <is>
-          <t>Vật tư có 3 đợt mua sắm lịch sử trên CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 với đơn giá trung bình là 598.667 đ/Cái (dao động từ 528.000 đ đến 740.000 đ). Đơn giá trình đợt này là 1.150.000 đ/Cái (+92.1% so với đơn</t>
-        </is>
-      </c>
-      <c r="H27" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 10/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [PR18], vật tư có lịch sử mua sắm tương đương tại Công ty TNHH MTV Thủy điện Trung Sơn (thời gian N/A) với đ</t>
-        </is>
-      </c>
-      <c r="I27" s="40" t="inlineStr"/>
-      <c r="J27" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [Cảm biến tiệm cận/proximity sensor - Cảm biến tiệm cận/proximity sensor - Model: PR18-8AO - Đường kính đầu dò: 18mm - Điện áp hoạt động: 100-240 Vac - Ngõ ra điều khiển: NO - Protection: IP67] trên th</t>
-        </is>
-      </c>
-      <c r="K27" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 577.200 đ
-(Cơ sở 5: Tham khảo TMĐT / Giá Web)
-(Tiết kiệm: 572.800 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="110" customHeight="1">
-      <c r="A28" s="38" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="39" t="inlineStr">
-        <is>
-          <t>3.34.20.134.CHN.00.000</t>
-        </is>
-      </c>
-      <c r="C28" s="40" t="inlineStr">
-        <is>
-          <t>Pendant control station:
-Type: XAC-A12713
-(Pendant control station:
-Type: XAC-A12713)</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr"/>
-      <c r="E28" s="42" t="inlineStr">
-        <is>
-          <t>Mở liên kết trực tuyến ↗</t>
-        </is>
-      </c>
-      <c r="F28" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đơn giá trình (5,784,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 6,000,000 đ (+3.7%). </t>
-        </is>
-      </c>
-      <c r="G28" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 2.369.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:132/2023) theo hóa đơn số 00000011 ngày 22.01.2024 ngày 2024-02-27. SL: 6 Cái)</t>
-        </is>
-      </c>
-      <c r="H28" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu CSDL EVN IMIS theo từ khóa [XAC-A12713], các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán nên thẩm định viên không áp dụng làm căn cứ thẩm định.</t>
-        </is>
-      </c>
-      <c r="I28" s="40" t="inlineStr"/>
-      <c r="J28" s="40" t="inlineStr"/>
-      <c r="K28" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 420.000 đ
-(Cơ sở 5: Tham khảo TMĐT / Giá Web)
-(Tiết kiệm: 5.364.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="38" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="39" t="inlineStr">
-        <is>
-          <t>4.90.80.030.KOR.00.000</t>
-        </is>
-      </c>
-      <c r="C29" s="40" t="inlineStr">
-        <is>
-          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)
-(Joint cover (bao che giữa các khớp nối đường ray cáp điện):
-- Material: PVC
-- Maker: Eunchang T&amp;C)</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E29" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (66,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 82,000 đ (+24.2%). Đơn g</t>
-        </is>
-      </c>
-      <c r="G29" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 26.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:116/2022) theo hóa đơn số 00000008 ngày 27.02.2023 ngày 2023-02-27. SL: 300 Cái); Các đợt nhập khác: 24.800 đ, 80.000 đ</t>
-        </is>
-      </c>
-      <c r="H29" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Bao che giữa các], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
-        </is>
-      </c>
-      <c r="I29" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [Bao che giữa các khớp nối đường ray cáp điện (Joint cover)] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
-        </is>
-      </c>
-      <c r="J29" s="40" t="inlineStr"/>
-      <c r="K29" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 26.000 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
-(Tiết kiệm: 9.400.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="38" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="39" t="inlineStr">
-        <is>
-          <t>4.90.80.027.KOR.00.000</t>
-        </is>
-      </c>
-      <c r="C30" s="40" t="inlineStr">
-        <is>
-          <t>Nắp che phía cuối đường ray cáp điện (End cap)
-(Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
-- Maker: Eunchang T&amp;C)</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E30" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (68,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 76,000 đ (+11.8%). Đơn g</t>
-        </is>
-      </c>
-      <c r="G30" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 21.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:116/2022) theo hóa đơn số 00000008 ngày 27.02.2023 ngày 2023-02-27. SL: 32 Cái); Các đợt nhập khác: 18.000 đ, 710.000 đ</t>
-        </is>
-      </c>
-      <c r="H30" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Nắp che phía cuối], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
-        </is>
-      </c>
-      <c r="I30" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [Nắp che phía cuối đường ray cáp điện (End cap)] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
-        </is>
-      </c>
-      <c r="J30" s="40" t="inlineStr"/>
-      <c r="K30" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 21.000 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
-(Tiết kiệm: 1.504.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="38" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="39" t="inlineStr">
-        <is>
-          <t>2.08.37.001.KOR.97.000</t>
-        </is>
-      </c>
-      <c r="C31" s="40" t="inlineStr">
-        <is>
-          <t>Trolley-bar (thanh ray cấp nguồn)
-(Trolley-bar (thanh ray cấp nguồn):
-- Iđm: 60A;
-- Uđm: 400VAC;
-- Length: 3m / cây
-- Material: Copper
-- Maker: EunchangT&amp;C)</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E31" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (909,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 1,020,000 đ (+12.2%). Đ</t>
-        </is>
-      </c>
-      <c r="G31" s="40" t="inlineStr">
-        <is>
-          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:62/2023) theo hóa đơn số 00001202 ngày 12.09.2023 (ngày ký 2023-09-25 00:00:00, do Nhập kho vật tư (HĐ:62/2023) theo hóa đơn số 00001202 ngày 12.</t>
-        </is>
-      </c>
-      <c r="H31" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Trolley bar (thanh ray], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
-        </is>
-      </c>
-      <c r="I31" s="40" t="inlineStr">
-        <is>
-          <t>Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [Trolley-bar], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp</t>
-        </is>
-      </c>
-      <c r="J31" s="40" t="inlineStr"/>
-      <c r="K31" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 890.000 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
-(Tiết kiệm: 532.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="38" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="39" t="inlineStr">
-        <is>
-          <t>3.34.20.133.CHN.99.000</t>
-        </is>
-      </c>
-      <c r="C32" s="40" t="inlineStr">
-        <is>
-          <t>Pendant control station:
-Type: XAC-A6913
-(Pendant control station:
-Type: XAC-A6913
-Control station composition: 06 push buttons + 01 emergency stop
-Product compatibility: 
-ZB2BE102 for emergency stop, XEN-G1191 for each direction
-Color: Yellow)</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E32" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (13,319,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 7). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 14,670,000 đ (+10.1%</t>
-        </is>
-      </c>
-      <c r="G32" s="40" t="inlineStr"/>
-      <c r="H32" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến ngày 10/09/2026, qua đối chiếu CSDL EVN IMIS theo từ khóa [A6913], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS của các Đơn vị Phát điện trong </t>
-        </is>
-      </c>
-      <c r="I32" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [XAC] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:08 ngày 10/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 3.290.400 đ (Mã TBMT: IB2600015122, Bên mời thầu: CHI NHÁNH TỔNG</t>
-        </is>
-      </c>
-      <c r="J32" s="40" t="inlineStr"/>
-      <c r="K32" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 3.290.400 đ
-(Cơ sở 4: Mua Sắm Công e-GP)
-(Tiết kiệm: 10.028.600 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="38" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="39" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C33" s="40" t="inlineStr">
-        <is>
-          <t>Lưỡi gà móc cẩu 3 tấn
-(Lưỡi gà móc cẩu 3 tấn
-Kích thước: rộng 25mm x dài 60mm)</t>
-        </is>
-      </c>
-      <c r="D33" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E33" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (610,000 đ) không trùng với báo giá nào. Trong đó đơn giá thấp nhất thu thập được là 716,000 đ của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf).</t>
-        </is>
-      </c>
-      <c r="G33" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ: 57/2024) theo hóa đơn số 615 ngày 27.08.2024 (ngày ký 2024-09-06 00:00:00, do Nhập kho vật tư (HĐ: 57/2024) theo hóa đơn số 615 ngày 27.08.2024 </t>
-        </is>
-      </c>
-      <c r="H33" s="40" t="inlineStr"/>
-      <c r="I33" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [Lưỡi gà móc cẩu] trên Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn) lúc 09:18 ngày 10/09/2026; ghi nhận đơn giá trúng thầu tham chiếu thấp nhất là 314.600 đ (Mã TBMT: IB2300214547, Bên mời thầu: CÔNG</t>
-        </is>
-      </c>
-      <c r="J33" s="40" t="inlineStr"/>
-      <c r="K33" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 314.600 đ
-(Cơ sở 4: Mua Sắm Công e-GP)
-(Tiết kiệm: 295.400 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="38" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="39" t="inlineStr">
-        <is>
-          <t>2.50.05.003.CHN.00.000</t>
-        </is>
-      </c>
-      <c r="C34" s="40" t="inlineStr">
-        <is>
-          <t>Cáp inox 304 
-Kích thước: Ø 3 mm
-(Cáp inox 304 
-Kích thước: Ø 3 mm)</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E34" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (37,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 41,000 đ (+10.8%). Đơn g</t>
-        </is>
-      </c>
-      <c r="G34" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 86.000 đ/Mét (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 90 Mét); Các đợt nhập khác: 67.000 đ, 12.000 đ</t>
-        </is>
-      </c>
-      <c r="H34" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Cáp inox 304 Kích], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
-        </is>
-      </c>
-      <c r="I34" s="40" t="inlineStr">
-        <is>
-          <t>e-GP MSC: 10.000 đ/Cái (Kết quả trúng thầu)</t>
-        </is>
-      </c>
-      <c r="J34" s="40" t="inlineStr"/>
-      <c r="K34" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 24.000 đ
-(Cơ sở 4: Mua Sắm Công e-GP)
-(Tiết kiệm: 780.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="38" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="39" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C35" s="40" t="inlineStr">
-        <is>
-          <t>Phe cài trục ngoài cho đường kính 28mm
-(Phe cài trục ngoài cho đường kính 28mm.
-Vật liệu: Inox 304)</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E35" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (56,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 67,000 đ (+19.6%). Đơn g</t>
-        </is>
-      </c>
-      <c r="G35" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 50.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:43) theo hóa đơn số 0000015 ngày 21.06.2021 ngày 2021-06-26. SL: 201 Cái); Các đợt nhập khác: 48.400 đ, 371.800 đ</t>
-        </is>
-      </c>
-      <c r="H35" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu CSDL EVN IMIS theo từ khóa [Phe cài trục ngoài], các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán nên thẩm định viên không áp dụng làm căn cứ thẩm định.</t>
-        </is>
-      </c>
-      <c r="I35" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [Phe cài trục ngoài cho đường kính 28mm] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
-        </is>
-      </c>
-      <c r="J35" s="40" t="inlineStr"/>
-      <c r="K35" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 50.000 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
-(Tiết kiệm: 6.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="38" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="39" t="inlineStr">
-        <is>
-          <t>2.06.60.080.TPE.00.000</t>
-        </is>
-      </c>
-      <c r="C36" s="40" t="inlineStr">
-        <is>
-          <t>Kẹp cố định đầu ray
-Loại: CH2260
-Size: 80x51x3mm
-(Kẹp cố định đầu ray
-Loại: CH2260
-Size: 80x51x3mm
-Vật liệu: Inox 304
-Hãng: ITS Đài loan)</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E36" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (2,254,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 3,670,000 đ (+62.8%).</t>
-        </is>
-      </c>
-      <c r="G36" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lịch sử nhập kho ERP Vĩnh Tân 4 [Kẹp cố định đầu ray. Loại: CH2260. Size: 80x51x3mm. Vật liệu: Inox 304]: 3.574.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: </t>
-        </is>
-      </c>
-      <c r="H36" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [2.06.60.080.TPE.00.000], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
-        </is>
-      </c>
-      <c r="I36" s="40" t="inlineStr">
-        <is>
-          <t>e-GP MSC: 578.078 đ/Cái (Kết quả trúng thầu)</t>
-        </is>
-      </c>
-      <c r="J36" s="40" t="inlineStr"/>
-      <c r="K36" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 578.078 đ
-(Cơ sở: Tự động/Rà soát nhanh)
-(Tiết kiệm: 3.351.844 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="38" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="39" t="inlineStr">
-        <is>
-          <t>3.15.44.076.CHN.00.000</t>
-        </is>
-      </c>
-      <c r="C37" s="40" t="inlineStr">
-        <is>
-          <t>Cáp điện dẹt cho cầu trục
-Quy cách: 16mm2 x 4C
-Ruột mềm
-(Cáp điện dẹt cho cầu trục
-Quy cách: 16mm2 x 4C
-Ruột mềm
-Điện áp: 450/750V
-Cách điện: PVC, dẻo
-NSX: Imatek)</t>
-        </is>
-      </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E37" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đơn giá trình (711,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 780,000 đ (+9.7%). Đơn </t>
-        </is>
-      </c>
-      <c r="G37" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Cáp điện dẹt cho cầu trục. 16mm2 x 4C]: 1.091.000 đ/Mét (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 99 Mét); Các đợt nhập khác: 730.0</t>
-        </is>
-      </c>
-      <c r="H37" s="40" t="inlineStr">
-        <is>
-          <t>IMIS EVN: 76.000 đ/Cái (Trung tâm Dịch vụ sửa chữa EVN - Chi nhánh Tập đoàn Điện lực Việt Nam)</t>
-        </is>
-      </c>
-      <c r="I37" s="40" t="inlineStr">
-        <is>
-          <t>e-GP MSC: 125.000 đ/Cái (Kết quả trúng thầu)</t>
-        </is>
-      </c>
-      <c r="J37" s="40" t="inlineStr"/>
-      <c r="K37" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 76.000 đ
-(Cơ sở: Tự động/Rà soát nhanh)
-(Tiết kiệm: 31.750.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="38" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="39" t="inlineStr">
-        <is>
-          <t>3.20.22.003.TPE.00.000</t>
-        </is>
-      </c>
-      <c r="C38" s="40" t="inlineStr">
-        <is>
-          <t>Khóa cáp 
-Dùng cho cáp: 3mm
-(Khóa cáp 
-Dùng cho cáp: 3mm)</t>
-        </is>
-      </c>
-      <c r="D38" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E38" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (20,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 8). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 31,000 đ (+55.0%). Đơn g</t>
-        </is>
-      </c>
-      <c r="G38" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Khóa cáp dùng cho cáp 3mm]: 14.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 113/2025) theo hóa đơn số 00000004 ngày 08.01.2026 ngày 2026-01-23. SL: 108 Cái); Các đợt nhập khác: 38.000 đ, 14.000 đ</t>
-        </is>
-      </c>
-      <c r="H38" s="40" t="inlineStr">
-        <is>
-          <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Khóa cáp Dùng cho], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
-        </is>
-      </c>
-      <c r="I38" s="40" t="inlineStr">
-        <is>
-          <t>e-GP MSC: 5.000 đ/Cái (Kết quả trúng thầu)</t>
-        </is>
-      </c>
-      <c r="J38" s="40" t="inlineStr"/>
-      <c r="K38" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 14.000 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
-(Tiết kiệm: 330.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="38" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="39" t="inlineStr">
-        <is>
-          <t>3.34.20.130.CHN.99.000</t>
-        </is>
-      </c>
-      <c r="C39" s="40" t="inlineStr">
-        <is>
-          <t>Pendant control station (Tay bấm điều khiển tời điện): 
-- Type: XAC-A6713
-(Pendant control station (Tay bấm điều khiển tời điện): 
-- Type: XAC-A6713
-Control station composition: 06, push buttons + 01 emergency stop)</t>
-        </is>
-      </c>
-      <c r="D39" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E39" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đơn giá trình (7,406,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 9). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 8,000,000 đ (+8.0%). </t>
-        </is>
-      </c>
-      <c r="G39" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Pendant control station. Type: XACA6713]: 6.600.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 65/2024) theo hóa đơn số 00000031 ngày 18.09.2024 ngày 2024-10-09. SL: 10 Cái); Các đợt nhập khác: 1.71</t>
-        </is>
-      </c>
-      <c r="H39" s="40" t="inlineStr">
-        <is>
-          <t>IMIS EVN: 3.310.185 đ/Cái (Công ty Nhiệt điện Vĩnh Tân)</t>
-        </is>
-      </c>
-      <c r="I39" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu từ khóa [Pendant control station (Tay bấm điều khiển tời điện):] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
-        </is>
-      </c>
-      <c r="J39" s="40" t="inlineStr"/>
-      <c r="K39" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 3.310.185 đ
-(Cơ sở 3: EVN IMIS)
-(Tiết kiệm: 4.095.815 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="38" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="39" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C40" s="40" t="inlineStr">
-        <is>
-          <t>Lưỡi gà móc cẩu 7 tấn
-(Lưỡi gà móc cẩu 7 tấn:
- + Kích thước: 60 x 175x 3mm
- + Vật liệu: thép)</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E40" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đơn giá trình (656,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 9). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 712,000 đ (+8.5%). Đơn </t>
-        </is>
-      </c>
-      <c r="G40" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Lưỡi gà móc cẩu BCD10t. Kích thước (DxR): 120mmx41mm]: 585.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 57/2024) theo hóa đơn số 615 ngày 27.08.2024 ngày 2024-09-06. SL: 1 Cái); Các đợt nhập khác:</t>
-        </is>
-      </c>
-      <c r="H40" s="40" t="inlineStr">
-        <is>
-          <t>Đã tra cứu CSDL EVN IMIS theo từ khóa [Lưỡi gà móc cẩu], các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán nên thẩm định viên không áp dụng làm căn cứ thẩm định.</t>
-        </is>
-      </c>
-      <c r="I40" s="40" t="inlineStr"/>
-      <c r="J40" s="40" t="inlineStr"/>
-      <c r="K40" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 585.000 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
-(Tiết kiệm: 71.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="39" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C41" s="40" t="inlineStr">
-        <is>
-          <t>Sơn dầu Jotun chống sét Green 437
-(Sơn dầu Jotun chống sét Green 437)</t>
-        </is>
-      </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E41" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (625,000 đ) là đơn giá thấp nhất theo Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (file Báo giá thăng long.pdf, Trang 9). Ngoài ra còn có: DTL 19.8.2026. xlsx báo giá 710,000 đ (+13.6%). Đơn</t>
-        </is>
-      </c>
-      <c r="G41" s="40" t="inlineStr">
-        <is>
-          <t>Vật tư có lịch sử nhập kho theo Nhập kho vật tư tổng hợp theo (HĐ:78) theo hóa đơn số 0000043 ngày 11.09.2019 (ngày ký 2019-09-13 00:00:00) với đơn giá 675.000 đ/Cái (Tổng số 20 đợt mua sắm lịch sử có đơn giá dao động từ</t>
-        </is>
-      </c>
-      <c r="H41" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J41" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K41" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 0 đ
-(Cơ sở: Tự động/Rà soát nhanh)
-(Tiết kiệm: 12.500.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" s="38" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="39" t="inlineStr">
-        <is>
-          <t>3.82.63.103.LTU.00.000</t>
-        </is>
-      </c>
-      <c r="C42" s="40" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO HBS 01 - FPN
-(Đế gắn module IO:
-- Hãng: ABB
-- Mã: HBS 01 - FPN
-- PR (Product Revision): M)</t>
-        </is>
-      </c>
-      <c r="D42" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E42" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F42" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đơn giá trình (21,120,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 7). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 25,200,000 </t>
-        </is>
-      </c>
-      <c r="G42" s="40" t="inlineStr">
-        <is>
-          <t>Vật tư đã có lịch sử nhập kho tại NMNĐ Vĩnh Tân 4 theo Nhập kho vật tư (HĐ:118/2021) theo hóa đơn số 00000001 ngày 05.01.2022 (ngày ký 2022-01-05 00:00:00, do Nhập kho vật tư (HĐ:118/2021) theo hóa đơn số 00000001 ngày 0</t>
-        </is>
-      </c>
-      <c r="H42" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J42" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K42" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 19.360.000 đ
-(Cơ sở 2: ERP Vĩnh Tân 4)
-(Tiết kiệm: 52.800.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="38" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="39" t="inlineStr">
-        <is>
-          <t>3.94.00.808.MLT.00.000</t>
-        </is>
-      </c>
-      <c r="C43" s="40" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO HBS01-FPH
-(Đế gắn module IO:
-- Hãng: ABB
-- Mã: HBS 01 - FPH
-- PR (Product Revision): M)</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>[Lưu trong hồ sơ PDF]</t>
-        </is>
-      </c>
-      <c r="E43" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Đơn giá trình (21,120,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 7). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 22,000,000 </t>
-        </is>
-      </c>
-      <c r="G43" s="40" t="inlineStr">
-        <is>
-          <t>Vật tư có lịch sử nhập kho gần nhất theo Nhập kho vật tư (HĐ:88/2025) theo hóa đơn số 00000376 ngày 16.03.2026 (ngày 2026-04-22 00:00:00) với đơn giá 25.000.000 đ/Cái (Tổng số 4 đợt mua sắm lịch sử có đơn giá dao động từ</t>
-        </is>
-      </c>
-      <c r="H43" s="40" t="inlineStr"/>
-      <c r="I43" s="40" t="inlineStr"/>
-      <c r="J43" s="40" t="inlineStr"/>
-      <c r="K43" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 0 đ
-(Cơ sở: Tự động/Rà soát nhanh)
-(Tiết kiệm: 549.120.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="110" customHeight="1">
-      <c r="A44" s="38" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="39" t="inlineStr">
-        <is>
-          <t>Chưa có mã vật tư</t>
-        </is>
-      </c>
-      <c r="C44" s="40" t="inlineStr">
         <is>
           <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than
 (Lining Plate (Compound Armour Plate)
@@ -12810,51 +9744,54 @@
 - Chống mài mòn theo ASTM G65: 0,0060 mm3/m)</t>
         </is>
       </c>
-      <c r="D44" s="14" t="inlineStr"/>
-      <c r="E44" s="40" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>[Lưu trong hồ sơ PDF]</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F44" s="40" t="inlineStr">
-        <is>
-          <t>Đơn giá trình (2,618,304,000 đ) là đơn giá thấp nhất theo Báo giá của DTL 19.8.2026. xlsx (file Báo giá DTL 19.8.2026. xlsx.pdf, Trang 8). Ngoài ra còn có: CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG báo giá 2,716,00</t>
-        </is>
-      </c>
-      <c r="G44" s="40" t="inlineStr">
-        <is>
-          <t>Lịch sử nhập kho ERP Vĩnh Tân 4 [Tấm lót bàn nghiền máy nghiền LM 28.3 D/ Grinding Plate. KT: 125txOD2800xID1510. vật liệu: sintercast]: 1.845.000.000 đ/Bộ (HĐ: Nhập kho vật tư (HĐ: 32/2025) theo hóa đơn số 00000181 ngày</t>
-        </is>
-      </c>
-      <c r="H44" s="40" t="inlineStr">
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>CẢNH BÁO: Đơn giá trình (2,618,304,000 đ) lấy từ Báo giá của DTL 19.8.2026. xlsx nhưng KHÔNG PHẢI là đơn giá thấp nhất! Đơn giá thấp nhất là 1,300,000 đ của CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (file BÁO G</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>Lịch sử nhập kho ERP Vĩnh Tân 4: 1.845.000.000 đ/Bộ (HĐ: Nhập kho vật tư (HĐ: 32/2025) theo hóa đơn số 00000181 ngày 26.11.2025 ngày 2025-12-04. SL: 3 Bộ); Các đợt nhập khác: 1.293.213.000 đ</t>
+        </is>
+      </c>
+      <c r="H18" s="40" t="inlineStr">
         <is>
           <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Lining Plate (Compound Armour], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
         </is>
       </c>
-      <c r="I44" s="40" t="inlineStr">
+      <c r="I18" s="40" t="inlineStr">
         <is>
           <t>Đã tra cứu từ khóa [Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
         </is>
       </c>
-      <c r="J44" s="40" t="inlineStr"/>
-      <c r="K44" s="41" t="inlineStr">
-        <is>
-          <t>Đơn giá chốt: 1.845.000.000 đ
-(Cơ sở 5: Tham khảo TMĐT / Giá Web)
-(Tiết kiệm: 1.546.608.000 đ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" s="38" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="39" t="inlineStr">
+      <c r="J18" s="40" t="inlineStr"/>
+      <c r="K18" s="41" t="inlineStr">
+        <is>
+          <t>Đơn giá chốt: 1.300.000 đ
+(Tiết kiệm: 5.234.008.000 đ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C45" s="40" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW
 (Bơm (SP-Circulation pump):
@@ -12872,41 +9809,40 @@
 IEC60034-1)</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>[Lưu trong hồ sơ PDF]</t>
         </is>
       </c>
-      <c r="E45" s="40" t="inlineStr">
+      <c r="E19" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F45" s="40" t="inlineStr">
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">CẢNH BÁO: Đơn giá trình (770,000,000 đ) lấy từ Báo giá của CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG nhưng KHÔNG PHẢI là đơn giá thấp nhất! Đơn giá thấp nhất là 750,000,000 đ của 08-27-26. BV-VT 4. . 1,620,000,000 </t>
         </is>
       </c>
-      <c r="G45" s="40" t="inlineStr">
+      <c r="G19" s="40" t="inlineStr">
         <is>
           <t>Vật tư chưa có lịch sử mua sắm/nhập kho trong CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4.</t>
         </is>
       </c>
-      <c r="H45" s="40" t="inlineStr">
+      <c r="H19" s="40" t="inlineStr">
         <is>
           <t>Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [TP400 PP], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.</t>
         </is>
       </c>
-      <c r="I45" s="40" t="inlineStr">
+      <c r="I19" s="40" t="inlineStr">
         <is>
           <t>Đã tra cứu từ khóa [Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.</t>
         </is>
       </c>
-      <c r="J45" s="40" t="inlineStr"/>
-      <c r="K45" s="41" t="inlineStr">
+      <c r="J19" s="40" t="inlineStr"/>
+      <c r="K19" s="41" t="inlineStr">
         <is>
           <t>Đơn giá chốt: 750.000.000 đ
-(Cơ sở 1: Đàm phán giảm giá / Báo giá chào)
 (Tiết kiệm: 40.000.000 đ)</t>
         </is>
       </c>
@@ -12915,14 +9851,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
 </file>